--- a/NN/reports/feature_importance_white_solution_color.xlsx
+++ b/NN/reports/feature_importance_white_solution_color.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,25 +501,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3821303127350526</v>
+        <v>0.3424292685068677</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.340136795918765</v>
+        <v>0.3181566287671884</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4053344801629097</v>
+        <v>0.3513435888306793</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1.348991351486901</v>
+        <v>1.433803714952994</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
@@ -538,25 +538,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2349835467230524</v>
+        <v>0.2383658985078753</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2549405745773559</v>
+        <v>0.225245016388724</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3175451473935752</v>
+        <v>0.2759191102277692</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>1.36129558406933</v>
+        <v>1.478740368189571</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -575,31 +575,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1137039771019454</v>
+        <v>0.1331501555978941</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.09719288122166042</v>
+        <v>0.08824288268883339</v>
       </c>
       <c r="F4" t="n">
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06851419197261259</v>
+        <v>0.04750577254953945</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8206497677308695</v>
+        <v>0.952211235371005</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
@@ -608,35 +608,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.111357205947063</v>
+        <v>0.1138727203369802</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2025293146116408</v>
+        <v>0.01315219499276279</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03273356021269584</v>
+        <v>0.03309391811105004</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7485294408411005</v>
+        <v>0.8325968016518011</v>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>4.25</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
@@ -645,32 +645,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.105686326219554</v>
+        <v>0.0925122844997833</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01589029923912289</v>
+        <v>0.211092557003509</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03371629901748831</v>
+        <v>0.02184809894965081</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>0.746755165169334</v>
+        <v>0.7924090046246004</v>
       </c>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K6" t="n">
         <v>5.25</v>
@@ -682,35 +682,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.006164026143775807</v>
+        <v>0.01182290118112469</v>
       </c>
       <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.01198557785307307</v>
+      </c>
+      <c r="F7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.01206627372144521</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.8088540008413529</v>
+      </c>
+      <c r="J7" t="n">
         <v>7</v>
       </c>
-      <c r="E7" t="n">
-        <v>0.05014252289189408</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.001896540205442111</v>
-      </c>
-      <c r="H7" t="n">
-        <v>10</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.8432722674881616</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3</v>
-      </c>
       <c r="K7" t="n">
-        <v>6.25</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="8">
@@ -719,32 +719,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.005072227427154765</v>
+        <v>0.007736709414784072</v>
       </c>
       <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.007045092865230165</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.004806630162510051</v>
+      </c>
+      <c r="H8" t="n">
         <v>8</v>
       </c>
-      <c r="E8" t="n">
-        <v>0.007523776659212974</v>
-      </c>
-      <c r="F8" t="n">
-        <v>7</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.004202180688090374</v>
-      </c>
-      <c r="H8" t="n">
-        <v>6</v>
-      </c>
       <c r="I8" t="n">
-        <v>0.1899232477355577</v>
+        <v>1.107645524286439</v>
       </c>
       <c r="J8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
         <v>7.25</v>
@@ -756,35 +756,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>white_quality_solution_color_1</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.007391783246766201</v>
+        <v>0.005629632018620954</v>
       </c>
       <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0220825936988427</v>
+      </c>
+      <c r="F9" t="n">
         <v>6</v>
       </c>
-      <c r="E9" t="n">
-        <v>0.003541032793133277</v>
-      </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
+        <v>0.00529489991088965</v>
+      </c>
+      <c r="H9" t="n">
+        <v>7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.3373116316724039</v>
+      </c>
+      <c r="J9" t="n">
         <v>10</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.003269389548919888</v>
-      </c>
-      <c r="H9" t="n">
-        <v>8</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.0883991257412613</v>
-      </c>
-      <c r="J9" t="n">
-        <v>15</v>
-      </c>
       <c r="K9" t="n">
-        <v>9.75</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="10">
@@ -793,32 +793,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.002851850519399511</v>
+        <v>0.002882842864139905</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>0.004874115878560938</v>
+        <v>0.0311312153900558</v>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G10" t="n">
-        <v>0.001047831069048322</v>
+        <v>0.0003276991593949123</v>
       </c>
       <c r="H10" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1578088310291892</v>
+        <v>1.296472196351193</v>
       </c>
       <c r="J10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
         <v>10.5</v>
@@ -830,35 +830,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>white_quality_solution_color_2</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.004014770386757912</v>
+        <v>0.003806728156947169</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>0.003783083269463529</v>
+        <v>0.00631140689285436</v>
       </c>
       <c r="F11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001114776098329384</v>
+        <v>0.001018282359692546</v>
       </c>
       <c r="H11" t="n">
         <v>12</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09934044474291781</v>
+        <v>0.2731534068695995</v>
       </c>
       <c r="J11" t="n">
         <v>13</v>
       </c>
       <c r="K11" t="n">
-        <v>11</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="12">
@@ -867,35 +867,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.004040564263570316</v>
+        <v>0.004000760960342559</v>
       </c>
       <c r="D12" t="n">
         <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>0.002422041860555468</v>
+        <v>0.003036778439689963</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G12" t="n">
-        <v>0.004189485745192545</v>
+        <v>0.0002770821278502811</v>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="I12" t="n">
-        <v>0.08823011340388565</v>
+        <v>0.6333921093174082</v>
       </c>
       <c r="J12" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K12" t="n">
-        <v>11.25</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="13">
@@ -904,35 +904,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.002209669264662628</v>
+        <v>0.002277176808020272</v>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
-        <v>0.002773202284686469</v>
+        <v>0.001516273235907318</v>
       </c>
       <c r="F13" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G13" t="n">
-        <v>0.000329412536047069</v>
+        <v>0.001357700694164798</v>
       </c>
       <c r="H13" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I13" t="n">
-        <v>0.20921047266933</v>
+        <v>0.2052719691187259</v>
       </c>
       <c r="J13" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="K13" t="n">
-        <v>13.25</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="14">
@@ -941,35 +941,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.002283599128182627</v>
+        <v>0.001725349766564107</v>
       </c>
       <c r="D14" t="n">
+        <v>19</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.00250354382601708</v>
+      </c>
+      <c r="F14" t="n">
+        <v>17</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.0006983973131602927</v>
+      </c>
+      <c r="H14" t="n">
         <v>14</v>
       </c>
-      <c r="E14" t="n">
-        <v>0.003425050897008127</v>
-      </c>
-      <c r="F14" t="n">
-        <v>11</v>
-      </c>
-      <c r="G14" t="n">
-        <v>5.285113751526405e-05</v>
-      </c>
-      <c r="H14" t="n">
-        <v>21</v>
-      </c>
       <c r="I14" t="n">
-        <v>0.1315837872656744</v>
+        <v>0.229753298447156</v>
       </c>
       <c r="J14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K14" t="n">
-        <v>14</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="15">
@@ -978,35 +978,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.003187695926451202</v>
+        <v>0.002254276794859032</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>0.001583483864149519</v>
+        <v>0.002744408089620847</v>
       </c>
       <c r="F15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001258513509459158</v>
+        <v>0.001072473149984188</v>
       </c>
       <c r="H15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I15" t="n">
-        <v>0.04016129108841815</v>
+        <v>0.159505819969981</v>
       </c>
       <c r="J15" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K15" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="16">
@@ -1015,35 +1015,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.002815958780106201</v>
+        <v>0.002670633776108256</v>
       </c>
       <c r="D16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>0.001317403013450218</v>
+        <v>0.001673063735473772</v>
       </c>
       <c r="F16" t="n">
+        <v>21</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.001059458746909891</v>
+      </c>
+      <c r="H16" t="n">
+        <v>11</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.1776140935255817</v>
+      </c>
+      <c r="J16" t="n">
+        <v>24</v>
+      </c>
+      <c r="K16" t="n">
         <v>17</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.001926320883916788</v>
-      </c>
-      <c r="H16" t="n">
-        <v>9</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.08543097805753064</v>
-      </c>
-      <c r="J16" t="n">
-        <v>17</v>
-      </c>
-      <c r="K16" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -1052,35 +1052,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.002266976735163204</v>
+        <v>0.001776900232282438</v>
       </c>
       <c r="D17" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>0.001260329777325474</v>
+        <v>0.001745766935296882</v>
       </c>
       <c r="F17" t="n">
+        <v>20</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.0004278258866586282</v>
+      </c>
+      <c r="H17" t="n">
+        <v>20</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.2617903996465323</v>
+      </c>
+      <c r="J17" t="n">
+        <v>14</v>
+      </c>
+      <c r="K17" t="n">
         <v>18</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.0005349511386086081</v>
-      </c>
-      <c r="H17" t="n">
-        <v>15</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.107151986964845</v>
-      </c>
-      <c r="J17" t="n">
-        <v>12</v>
-      </c>
-      <c r="K17" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -1089,35 +1089,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.002159487574025568</v>
+        <v>0.002196740586494563</v>
       </c>
       <c r="D18" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E18" t="n">
-        <v>0.001039510138780859</v>
+        <v>0.001460034493748368</v>
       </c>
       <c r="F18" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0004000061330024285</v>
+        <v>0.0005838627476783432</v>
       </c>
       <c r="H18" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1115458931717002</v>
+        <v>0.2005507462162361</v>
       </c>
       <c r="J18" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="K18" t="n">
-        <v>16.25</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="19">
@@ -1126,35 +1126,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.002168518659715427</v>
+        <v>0.001991611778468329</v>
       </c>
       <c r="D19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E19" t="n">
-        <v>0.001364113069725128</v>
+        <v>0.001219912516060806</v>
       </c>
       <c r="F19" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0007273394792266074</v>
+        <v>0.0009180432739566924</v>
       </c>
       <c r="H19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.1414615172091742</v>
       </c>
       <c r="J19" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K19" t="n">
-        <v>17.25</v>
+        <v>20.75</v>
       </c>
     </row>
     <row r="20">
@@ -1163,35 +1163,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0004065740168260178</v>
+        <v>0.0009212352558826193</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>0.001444293841272595</v>
+        <v>0.006942158564037165</v>
       </c>
       <c r="F20" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0005103662499918227</v>
+        <v>0.0001508168303326674</v>
       </c>
       <c r="H20" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="I20" t="n">
-        <v>0.02367048450294096</v>
+        <v>0.2929207431772767</v>
       </c>
       <c r="J20" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="K20" t="n">
-        <v>18.5</v>
+        <v>21.75</v>
       </c>
     </row>
     <row r="21">
@@ -1200,35 +1200,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.001786544780691375</v>
+        <v>0.001981650928159711</v>
       </c>
       <c r="D21" t="n">
+        <v>17</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.0009771219945312779</v>
+      </c>
+      <c r="F21" t="n">
+        <v>29</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.0004154677420654673</v>
+      </c>
+      <c r="H21" t="n">
+        <v>21</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.2057084216457903</v>
+      </c>
+      <c r="J21" t="n">
         <v>20</v>
       </c>
-      <c r="E21" t="n">
-        <v>0.0009160691162719914</v>
-      </c>
-      <c r="F21" t="n">
-        <v>21</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.0002918346372657643</v>
-      </c>
-      <c r="H21" t="n">
-        <v>20</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.08976659956018462</v>
-      </c>
-      <c r="J21" t="n">
-        <v>14</v>
-      </c>
       <c r="K21" t="n">
-        <v>18.75</v>
+        <v>21.75</v>
       </c>
     </row>
     <row r="22">
@@ -1237,35 +1237,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.00180778798393591</v>
+        <v>0.001552321998005159</v>
       </c>
       <c r="D22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0009833419547780897</v>
+        <v>0.001498391733627246</v>
       </c>
       <c r="F22" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0002942146143418256</v>
+        <v>0.0002877783329671813</v>
       </c>
       <c r="H22" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I22" t="n">
-        <v>0.07214471272382861</v>
+        <v>0.1543834728358466</v>
       </c>
       <c r="J22" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="K22" t="n">
-        <v>19</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="23">
@@ -1274,35 +1274,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.001447185240035235</v>
+        <v>0.0004894599256017411</v>
       </c>
       <c r="D23" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0007778008419880633</v>
+        <v>0.01162416261146885</v>
       </c>
       <c r="F23" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="G23" t="n">
-        <v>4.013245133074328e-05</v>
+        <v>0.0001805774039261188</v>
       </c>
       <c r="H23" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="I23" t="n">
-        <v>0.06606132546147458</v>
+        <v>0.2295057870794264</v>
       </c>
       <c r="J23" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K23" t="n">
-        <v>21</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="24">
@@ -1311,35 +1311,1145 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.001294014005523748</v>
+      </c>
+      <c r="D24" t="n">
+        <v>24</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.00197266459610386</v>
+      </c>
+      <c r="F24" t="n">
+        <v>18</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.0002552838898238985</v>
+      </c>
+      <c r="H24" t="n">
+        <v>28</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.1077356270524956</v>
+      </c>
+      <c r="J24" t="n">
+        <v>36</v>
+      </c>
+      <c r="K24" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>boiler_tds</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.001500850875527292</v>
+      </c>
+      <c r="D25" t="n">
+        <v>21</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.001175379803342451</v>
+      </c>
+      <c r="F25" t="n">
+        <v>27</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.0005608043871210388</v>
+      </c>
+      <c r="H25" t="n">
+        <v>16</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.0786731789563766</v>
+      </c>
+      <c r="J25" t="n">
+        <v>43</v>
+      </c>
+      <c r="K25" t="n">
+        <v>26.75</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>report_date_year</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.0005572419416763432</v>
+      </c>
+      <c r="D26" t="n">
+        <v>45</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.003344487827892552</v>
+      </c>
+      <c r="F26" t="n">
+        <v>13</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.0002351742058631312</v>
+      </c>
+      <c r="H26" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2086458278708552</v>
+      </c>
+      <c r="J26" t="n">
+        <v>19</v>
+      </c>
+      <c r="K26" t="n">
+        <v>26.75</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.00135649642937945</v>
+      </c>
+      <c r="D27" t="n">
+        <v>23</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.001750847309758089</v>
+      </c>
+      <c r="F27" t="n">
+        <v>19</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.0001176696373987762</v>
+      </c>
+      <c r="H27" t="n">
+        <v>35</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.1100992902083822</v>
+      </c>
+      <c r="J27" t="n">
+        <v>33</v>
+      </c>
+      <c r="K27" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>raw_syrup_brix</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.000938319440473086</v>
+      </c>
+      <c r="D28" t="n">
+        <v>29</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.0007509547148492584</v>
+      </c>
+      <c r="F28" t="n">
+        <v>34</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.0002798968058276841</v>
+      </c>
+      <c r="H28" t="n">
+        <v>25</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.2014771250067651</v>
+      </c>
+      <c r="J28" t="n">
+        <v>22</v>
+      </c>
+      <c r="K28" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>report_year</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.0002792881493865698</v>
+      </c>
+      <c r="D29" t="n">
+        <v>47</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.003273497853480334</v>
+      </c>
+      <c r="F29" t="n">
+        <v>14</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.0001752374778752896</v>
+      </c>
+      <c r="H29" t="n">
+        <v>32</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.2218485223188855</v>
+      </c>
+      <c r="J29" t="n">
+        <v>17</v>
+      </c>
+      <c r="K29" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>raw_syrup_color</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.0009894049265533594</v>
+      </c>
+      <c r="D30" t="n">
+        <v>28</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.001478413259820412</v>
+      </c>
+      <c r="F30" t="n">
+        <v>24</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-0.0001692251611651874</v>
+      </c>
+      <c r="H30" t="n">
+        <v>51</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.2770263523620402</v>
+      </c>
+      <c r="J30" t="n">
+        <v>12</v>
+      </c>
+      <c r="K30" t="n">
+        <v>28.75</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>standard_liquor_pH</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.001167381262998629</v>
+      </c>
+      <c r="D31" t="n">
+        <v>26</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.0007743703271407873</v>
+      </c>
+      <c r="F31" t="n">
+        <v>33</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.0004499382872577784</v>
+      </c>
+      <c r="H31" t="n">
+        <v>19</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.1043761904758367</v>
+      </c>
+      <c r="J31" t="n">
+        <v>39</v>
+      </c>
+      <c r="K31" t="n">
+        <v>29.25</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>boiler_alkalinity</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.001464101489035468</v>
+      </c>
+      <c r="D32" t="n">
+        <v>22</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.0009065155138097038</v>
+      </c>
+      <c r="F32" t="n">
+        <v>30</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.0004012968385182947</v>
+      </c>
+      <c r="H32" t="n">
+        <v>22</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.04923555457813222</v>
+      </c>
+      <c r="J32" t="n">
+        <v>46</v>
+      </c>
+      <c r="K32" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>boiling_r1_q</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.0008821176283592951</v>
+      </c>
+      <c r="D33" t="n">
+        <v>32</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.0006382026353400602</v>
+      </c>
+      <c r="F33" t="n">
+        <v>40</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.0005440955245589185</v>
+      </c>
+      <c r="H33" t="n">
+        <v>17</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.1081584076742153</v>
+      </c>
+      <c r="J33" t="n">
+        <v>35</v>
+      </c>
+      <c r="K33" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>white_quality_apparent_color_2</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.0008402422651569407</v>
+      </c>
+      <c r="D34" t="n">
+        <v>33</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.0009917240561012892</v>
+      </c>
+      <c r="F34" t="n">
+        <v>28</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-7.825080711114652e-05</v>
+      </c>
+      <c r="H34" t="n">
+        <v>49</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.2207323944761521</v>
+      </c>
+      <c r="J34" t="n">
+        <v>18</v>
+      </c>
+      <c r="K34" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.001206122663108219</v>
+      </c>
+      <c r="D35" t="n">
+        <v>25</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.0008021534403865204</v>
+      </c>
+      <c r="F35" t="n">
+        <v>32</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.0001532927007891982</v>
+      </c>
+      <c r="H35" t="n">
+        <v>33</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.04556853675596395</v>
+      </c>
+      <c r="J35" t="n">
+        <v>47</v>
+      </c>
+      <c r="K35" t="n">
+        <v>34.25</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.0007367385516409864</v>
+      </c>
+      <c r="D36" t="n">
+        <v>41</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.0006669483459338774</v>
+      </c>
+      <c r="F36" t="n">
+        <v>39</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.0002748763353595973</v>
+      </c>
+      <c r="H36" t="n">
+        <v>27</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.1111174670285382</v>
+      </c>
+      <c r="J36" t="n">
+        <v>32</v>
+      </c>
+      <c r="K36" t="n">
+        <v>34.75</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>filtercake_sugar</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.0008132895954746782</v>
+      </c>
+      <c r="D37" t="n">
+        <v>35</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.0004655147573798946</v>
+      </c>
+      <c r="F37" t="n">
+        <v>49</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.0002394229405602966</v>
+      </c>
+      <c r="H37" t="n">
+        <v>29</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.1321623732084736</v>
+      </c>
+      <c r="J37" t="n">
+        <v>29</v>
+      </c>
+      <c r="K37" t="n">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.0008340628663017962</v>
+      </c>
+      <c r="D38" t="n">
+        <v>34</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.0006812942521092414</v>
+      </c>
+      <c r="F38" t="n">
+        <v>37</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-9.313573361979799e-06</v>
+      </c>
+      <c r="H38" t="n">
+        <v>43</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.1193277577675893</v>
+      </c>
+      <c r="J38" t="n">
+        <v>31</v>
+      </c>
+      <c r="K38" t="n">
+        <v>36.25</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.001041035620556295</v>
+      </c>
+      <c r="D39" t="n">
+        <v>27</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.0007083334940501524</v>
+      </c>
+      <c r="F39" t="n">
+        <v>35</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-4.138304986746055e-05</v>
+      </c>
+      <c r="H39" t="n">
+        <v>47</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.09267643000428505</v>
+      </c>
+      <c r="J39" t="n">
+        <v>40</v>
+      </c>
+      <c r="K39" t="n">
+        <v>37.25</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.0007618075063473855</v>
+      </c>
+      <c r="D40" t="n">
+        <v>39</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.0008945082626808689</v>
+      </c>
+      <c r="F40" t="n">
+        <v>31</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-2.071002570160907e-05</v>
+      </c>
+      <c r="H40" t="n">
+        <v>46</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.1083655886876653</v>
+      </c>
+      <c r="J40" t="n">
+        <v>34</v>
+      </c>
+      <c r="K40" t="n">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>carbonated_alkalinity</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.0002618237302263946</v>
+      </c>
+      <c r="D41" t="n">
+        <v>48</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.0006882203627795102</v>
+      </c>
+      <c r="F41" t="n">
+        <v>36</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.0004804459140221318</v>
+      </c>
+      <c r="H41" t="n">
+        <v>18</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.01937812905933955</v>
+      </c>
+      <c r="J41" t="n">
+        <v>49</v>
+      </c>
+      <c r="K41" t="n">
+        <v>37.75</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>sulphited_brix</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.000925923811968918</v>
+      </c>
+      <c r="D42" t="n">
+        <v>30</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.0006748388105316527</v>
+      </c>
+      <c r="F42" t="n">
+        <v>38</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-0.0002161354935916626</v>
+      </c>
+      <c r="H42" t="n">
+        <v>53</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.1306732706335407</v>
+      </c>
+      <c r="J42" t="n">
+        <v>30</v>
+      </c>
+      <c r="K42" t="n">
+        <v>37.75</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>filtercake_moisture</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.0007882969006697734</v>
+      </c>
+      <c r="D43" t="n">
+        <v>37</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.0006364031463430259</v>
+      </c>
+      <c r="F43" t="n">
+        <v>42</v>
+      </c>
+      <c r="G43" t="n">
+        <v>7.232775912602296e-06</v>
+      </c>
+      <c r="H43" t="n">
+        <v>39</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.1054561942143275</v>
+      </c>
+      <c r="J43" t="n">
+        <v>37</v>
+      </c>
+      <c r="K43" t="n">
+        <v>38.75</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.0007059589823853784</v>
+      </c>
+      <c r="D44" t="n">
+        <v>43</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.0005553763241052613</v>
+      </c>
+      <c r="F44" t="n">
+        <v>46</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-7.89463475965313e-06</v>
+      </c>
+      <c r="H44" t="n">
+        <v>42</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.1709834645543058</v>
+      </c>
+      <c r="J44" t="n">
+        <v>25</v>
+      </c>
+      <c r="K44" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>wastewater_r1_pol</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.0007531306730161371</v>
+      </c>
+      <c r="D45" t="n">
+        <v>40</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.0006159301639449595</v>
+      </c>
+      <c r="F45" t="n">
+        <v>43</v>
+      </c>
+      <c r="G45" t="n">
+        <v>8.608242056333815e-05</v>
+      </c>
+      <c r="H45" t="n">
+        <v>36</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.07692667533808129</v>
+      </c>
+      <c r="J45" t="n">
+        <v>44</v>
+      </c>
+      <c r="K45" t="n">
+        <v>40.75</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>boiling_r1_pol</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.0007837207757594585</v>
+      </c>
+      <c r="D46" t="n">
+        <v>38</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.0005928112719898244</v>
+      </c>
+      <c r="F46" t="n">
+        <v>44</v>
+      </c>
+      <c r="G46" t="n">
+        <v>5.880174109140768e-06</v>
+      </c>
+      <c r="H46" t="n">
+        <v>40</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.08120877841116192</v>
+      </c>
+      <c r="J46" t="n">
+        <v>42</v>
+      </c>
+      <c r="K46" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.0007317274373024924</v>
+      </c>
+      <c r="D47" t="n">
+        <v>42</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.0005004626058432648</v>
+      </c>
+      <c r="F47" t="n">
+        <v>48</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-7.116172808396826e-06</v>
+      </c>
+      <c r="H47" t="n">
+        <v>41</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.05888879003301017</v>
+      </c>
+      <c r="J47" t="n">
+        <v>45</v>
+      </c>
+      <c r="K47" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.0007923317385663658</v>
+      </c>
+      <c r="D48" t="n">
+        <v>36</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.0004500689253536527</v>
+      </c>
+      <c r="F48" t="n">
+        <v>50</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-0.0001452977838964698</v>
+      </c>
+      <c r="H48" t="n">
+        <v>50</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.08181546115420524</v>
+      </c>
+      <c r="J48" t="n">
+        <v>41</v>
+      </c>
+      <c r="K48" t="n">
+        <v>44.25</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.000698768824287874</v>
+      </c>
+      <c r="D49" t="n">
+        <v>44</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.0005266185931786459</v>
+      </c>
+      <c r="F49" t="n">
+        <v>47</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-0.0001891751093902161</v>
+      </c>
+      <c r="H49" t="n">
+        <v>52</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.1047131403997339</v>
+      </c>
+      <c r="J49" t="n">
+        <v>38</v>
+      </c>
+      <c r="K49" t="n">
+        <v>45.25</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_2</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.0002578164434175566</v>
+      </c>
+      <c r="D50" t="n">
+        <v>49</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.0006368282214652454</v>
+      </c>
+      <c r="F50" t="n">
+        <v>41</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-1.365397194396101e-05</v>
+      </c>
+      <c r="H50" t="n">
+        <v>44</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.03360896424143878</v>
+      </c>
+      <c r="J50" t="n">
+        <v>48</v>
+      </c>
+      <c r="K50" t="n">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.000252087349012528</v>
+      </c>
+      <c r="D51" t="n">
+        <v>50</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.000422029832543363</v>
+      </c>
+      <c r="F51" t="n">
+        <v>51</v>
+      </c>
+      <c r="G51" t="n">
+        <v>5.83587393926388e-05</v>
+      </c>
+      <c r="H51" t="n">
+        <v>37</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>51</v>
+      </c>
+      <c r="K51" t="n">
+        <v>47.25</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>7.594196436190925e-05</v>
+      </c>
+      <c r="D52" t="n">
+        <v>52</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.0003046341338028613</v>
+      </c>
+      <c r="F52" t="n">
+        <v>52</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1.151763200234468e-05</v>
+      </c>
+      <c r="H52" t="n">
+        <v>38</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>51</v>
+      </c>
+      <c r="K52" t="n">
+        <v>48.25</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_1</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.0002306281107116144</v>
+      </c>
+      <c r="D53" t="n">
+        <v>51</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.0005700067466729396</v>
+      </c>
+      <c r="F53" t="n">
+        <v>45</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-6.309281372750553e-05</v>
+      </c>
+      <c r="H53" t="n">
+        <v>48</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.001182132265124647</v>
+      </c>
+      <c r="J53" t="n">
+        <v>50</v>
+      </c>
+      <c r="K53" t="n">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>shift_name</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>6.341119611288038e-05</v>
-      </c>
-      <c r="D24" t="n">
-        <v>23</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.0001389622791981613</v>
-      </c>
-      <c r="F24" t="n">
-        <v>23</v>
-      </c>
-      <c r="G24" t="n">
-        <v>-4.726614070832413e-05</v>
-      </c>
-      <c r="H24" t="n">
-        <v>23</v>
-      </c>
-      <c r="I24" t="n">
+      <c r="C54" t="n">
+        <v>3.206814500804728e-05</v>
+      </c>
+      <c r="D54" t="n">
+        <v>53</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.0001631776947128911</v>
+      </c>
+      <c r="F54" t="n">
+        <v>53</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-1.952708848380613e-05</v>
+      </c>
+      <c r="H54" t="n">
+        <v>45</v>
+      </c>
+      <c r="I54" t="n">
         <v>0</v>
       </c>
-      <c r="J24" t="n">
-        <v>22</v>
-      </c>
-      <c r="K24" t="n">
-        <v>22.75</v>
+      <c r="J54" t="n">
+        <v>51</v>
+      </c>
+      <c r="K54" t="n">
+        <v>50.5</v>
       </c>
     </row>
   </sheetData>
@@ -1423,25 +2533,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3821303127350526</v>
+        <v>0.3424292685068677</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.340136795918765</v>
+        <v>0.3181566287671884</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4053344801629097</v>
+        <v>0.3513435888306793</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1.348991351486901</v>
+        <v>1.433803714952994</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
@@ -1460,25 +2570,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2349835467230524</v>
+        <v>0.2383658985078753</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2549405745773559</v>
+        <v>0.225245016388724</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3175451473935752</v>
+        <v>0.2759191102277692</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>1.36129558406933</v>
+        <v>1.478740368189571</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -1497,31 +2607,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1137039771019454</v>
+        <v>0.1331501555978941</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.09719288122166042</v>
+        <v>0.08824288268883339</v>
       </c>
       <c r="F4" t="n">
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06851419197261259</v>
+        <v>0.04750577254953945</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8206497677308695</v>
+        <v>0.952211235371005</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
@@ -1530,35 +2640,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.111357205947063</v>
+        <v>0.1138727203369802</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2025293146116408</v>
+        <v>0.01315219499276279</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03273356021269584</v>
+        <v>0.03309391811105004</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7485294408411005</v>
+        <v>0.8325968016518011</v>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>4.25</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
@@ -1567,32 +2677,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.105686326219554</v>
+        <v>0.0925122844997833</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01589029923912289</v>
+        <v>0.211092557003509</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03371629901748831</v>
+        <v>0.02184809894965081</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>0.746755165169334</v>
+        <v>0.7924090046246004</v>
       </c>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K6" t="n">
         <v>5.25</v>
@@ -1604,35 +2714,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.006164026143775807</v>
+        <v>0.01182290118112469</v>
       </c>
       <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.01198557785307307</v>
+      </c>
+      <c r="F7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.01206627372144521</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.8088540008413529</v>
+      </c>
+      <c r="J7" t="n">
         <v>7</v>
       </c>
-      <c r="E7" t="n">
-        <v>0.05014252289189408</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.001896540205442111</v>
-      </c>
-      <c r="H7" t="n">
-        <v>10</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.8432722674881616</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3</v>
-      </c>
       <c r="K7" t="n">
-        <v>6.25</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="8">
@@ -1641,32 +2751,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.005072227427154765</v>
+        <v>0.007736709414784072</v>
       </c>
       <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.007045092865230165</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.004806630162510051</v>
+      </c>
+      <c r="H8" t="n">
         <v>8</v>
       </c>
-      <c r="E8" t="n">
-        <v>0.007523776659212974</v>
-      </c>
-      <c r="F8" t="n">
-        <v>7</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.004202180688090374</v>
-      </c>
-      <c r="H8" t="n">
-        <v>6</v>
-      </c>
       <c r="I8" t="n">
-        <v>0.1899232477355577</v>
+        <v>1.107645524286439</v>
       </c>
       <c r="J8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
         <v>7.25</v>
@@ -1678,35 +2788,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>white_quality_solution_color_1</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.007391783246766201</v>
+        <v>0.005629632018620954</v>
       </c>
       <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0220825936988427</v>
+      </c>
+      <c r="F9" t="n">
         <v>6</v>
       </c>
-      <c r="E9" t="n">
-        <v>0.003541032793133277</v>
-      </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
+        <v>0.00529489991088965</v>
+      </c>
+      <c r="H9" t="n">
+        <v>7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.3373116316724039</v>
+      </c>
+      <c r="J9" t="n">
         <v>10</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.003269389548919888</v>
-      </c>
-      <c r="H9" t="n">
-        <v>8</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.0883991257412613</v>
-      </c>
-      <c r="J9" t="n">
-        <v>15</v>
-      </c>
       <c r="K9" t="n">
-        <v>9.75</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="10">
@@ -1715,32 +2825,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.002851850519399511</v>
+        <v>0.002882842864139905</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>0.004874115878560938</v>
+        <v>0.0311312153900558</v>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G10" t="n">
-        <v>0.001047831069048322</v>
+        <v>0.0003276991593949123</v>
       </c>
       <c r="H10" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1578088310291892</v>
+        <v>1.296472196351193</v>
       </c>
       <c r="J10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
         <v>10.5</v>
@@ -1752,35 +2862,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>white_quality_solution_color_2</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.004014770386757912</v>
+        <v>0.003806728156947169</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>0.003783083269463529</v>
+        <v>0.00631140689285436</v>
       </c>
       <c r="F11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001114776098329384</v>
+        <v>0.001018282359692546</v>
       </c>
       <c r="H11" t="n">
         <v>12</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09934044474291781</v>
+        <v>0.2731534068695995</v>
       </c>
       <c r="J11" t="n">
         <v>13</v>
       </c>
       <c r="K11" t="n">
-        <v>11</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="12">
@@ -1789,35 +2899,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.004040564263570316</v>
+        <v>0.004000760960342559</v>
       </c>
       <c r="D12" t="n">
         <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>0.002422041860555468</v>
+        <v>0.003036778439689963</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G12" t="n">
-        <v>0.004189485745192545</v>
+        <v>0.0002770821278502811</v>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="I12" t="n">
-        <v>0.08823011340388565</v>
+        <v>0.6333921093174082</v>
       </c>
       <c r="J12" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K12" t="n">
-        <v>11.25</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="13">
@@ -1826,35 +2936,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.002209669264662628</v>
+        <v>0.002277176808020272</v>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
-        <v>0.002773202284686469</v>
+        <v>0.001516273235907318</v>
       </c>
       <c r="F13" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G13" t="n">
-        <v>0.000329412536047069</v>
+        <v>0.001357700694164798</v>
       </c>
       <c r="H13" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I13" t="n">
-        <v>0.20921047266933</v>
+        <v>0.2052719691187259</v>
       </c>
       <c r="J13" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="K13" t="n">
-        <v>13.25</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="14">
@@ -1863,35 +2973,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.002283599128182627</v>
+        <v>0.001725349766564107</v>
       </c>
       <c r="D14" t="n">
+        <v>19</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.00250354382601708</v>
+      </c>
+      <c r="F14" t="n">
+        <v>17</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.0006983973131602927</v>
+      </c>
+      <c r="H14" t="n">
         <v>14</v>
       </c>
-      <c r="E14" t="n">
-        <v>0.003425050897008127</v>
-      </c>
-      <c r="F14" t="n">
-        <v>11</v>
-      </c>
-      <c r="G14" t="n">
-        <v>5.285113751526405e-05</v>
-      </c>
-      <c r="H14" t="n">
-        <v>21</v>
-      </c>
       <c r="I14" t="n">
-        <v>0.1315837872656744</v>
+        <v>0.229753298447156</v>
       </c>
       <c r="J14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K14" t="n">
-        <v>14</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="15">
@@ -1900,35 +3010,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.003187695926451202</v>
+        <v>0.002254276794859032</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>0.001583483864149519</v>
+        <v>0.002744408089620847</v>
       </c>
       <c r="F15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001258513509459158</v>
+        <v>0.001072473149984188</v>
       </c>
       <c r="H15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I15" t="n">
-        <v>0.04016129108841815</v>
+        <v>0.159505819969981</v>
       </c>
       <c r="J15" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K15" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="16">
@@ -1937,35 +3047,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.002815958780106201</v>
+        <v>0.002670633776108256</v>
       </c>
       <c r="D16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>0.001317403013450218</v>
+        <v>0.001673063735473772</v>
       </c>
       <c r="F16" t="n">
+        <v>21</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.001059458746909891</v>
+      </c>
+      <c r="H16" t="n">
+        <v>11</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.1776140935255817</v>
+      </c>
+      <c r="J16" t="n">
+        <v>24</v>
+      </c>
+      <c r="K16" t="n">
         <v>17</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.001926320883916788</v>
-      </c>
-      <c r="H16" t="n">
-        <v>9</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.08543097805753064</v>
-      </c>
-      <c r="J16" t="n">
-        <v>17</v>
-      </c>
-      <c r="K16" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -1974,35 +3084,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.002266976735163204</v>
+        <v>0.001776900232282438</v>
       </c>
       <c r="D17" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>0.001260329777325474</v>
+        <v>0.001745766935296882</v>
       </c>
       <c r="F17" t="n">
+        <v>20</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.0004278258866586282</v>
+      </c>
+      <c r="H17" t="n">
+        <v>20</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.2617903996465323</v>
+      </c>
+      <c r="J17" t="n">
+        <v>14</v>
+      </c>
+      <c r="K17" t="n">
         <v>18</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.0005349511386086081</v>
-      </c>
-      <c r="H17" t="n">
-        <v>15</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.107151986964845</v>
-      </c>
-      <c r="J17" t="n">
-        <v>12</v>
-      </c>
-      <c r="K17" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -2011,35 +3121,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.002159487574025568</v>
+        <v>0.002196740586494563</v>
       </c>
       <c r="D18" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E18" t="n">
-        <v>0.001039510138780859</v>
+        <v>0.001460034493748368</v>
       </c>
       <c r="F18" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0004000061330024285</v>
+        <v>0.0005838627476783432</v>
       </c>
       <c r="H18" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1115458931717002</v>
+        <v>0.2005507462162361</v>
       </c>
       <c r="J18" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="K18" t="n">
-        <v>16.25</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="19">
@@ -2048,35 +3158,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.002168518659715427</v>
+        <v>0.001991611778468329</v>
       </c>
       <c r="D19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E19" t="n">
-        <v>0.001364113069725128</v>
+        <v>0.001219912516060806</v>
       </c>
       <c r="F19" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0007273394792266074</v>
+        <v>0.0009180432739566924</v>
       </c>
       <c r="H19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.1414615172091742</v>
       </c>
       <c r="J19" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K19" t="n">
-        <v>17.25</v>
+        <v>20.75</v>
       </c>
     </row>
     <row r="20">
@@ -2085,35 +3195,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0004065740168260178</v>
+        <v>0.0009212352558826193</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>0.001444293841272595</v>
+        <v>0.006942158564037165</v>
       </c>
       <c r="F20" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0005103662499918227</v>
+        <v>0.0001508168303326674</v>
       </c>
       <c r="H20" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="I20" t="n">
-        <v>0.02367048450294096</v>
+        <v>0.2929207431772767</v>
       </c>
       <c r="J20" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="K20" t="n">
-        <v>18.5</v>
+        <v>21.75</v>
       </c>
     </row>
     <row r="21">
@@ -2122,35 +3232,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.001786544780691375</v>
+        <v>0.001981650928159711</v>
       </c>
       <c r="D21" t="n">
+        <v>17</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.0009771219945312779</v>
+      </c>
+      <c r="F21" t="n">
+        <v>29</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.0004154677420654673</v>
+      </c>
+      <c r="H21" t="n">
+        <v>21</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.2057084216457903</v>
+      </c>
+      <c r="J21" t="n">
         <v>20</v>
       </c>
-      <c r="E21" t="n">
-        <v>0.0009160691162719914</v>
-      </c>
-      <c r="F21" t="n">
-        <v>21</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.0002918346372657643</v>
-      </c>
-      <c r="H21" t="n">
-        <v>20</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.08976659956018462</v>
-      </c>
-      <c r="J21" t="n">
-        <v>14</v>
-      </c>
       <c r="K21" t="n">
-        <v>18.75</v>
+        <v>21.75</v>
       </c>
     </row>
   </sheetData>
@@ -2164,7 +3274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2194,7 +3304,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3821303127350526</v>
+        <v>0.3424292685068677</v>
       </c>
     </row>
     <row r="3">
@@ -2207,7 +3317,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2349835467230524</v>
+        <v>0.2383658985078753</v>
       </c>
     </row>
     <row r="4">
@@ -2220,7 +3330,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1137039771019454</v>
+        <v>0.1331501555978941</v>
       </c>
     </row>
     <row r="5">
@@ -2229,11 +3339,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.111357205947063</v>
+        <v>0.1138727203369802</v>
       </c>
     </row>
     <row r="6">
@@ -2242,11 +3352,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.105686326219554</v>
+        <v>0.0925122844997833</v>
       </c>
     </row>
     <row r="7">
@@ -2255,11 +3365,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.007391783246766201</v>
+        <v>0.01182290118112469</v>
       </c>
     </row>
     <row r="8">
@@ -2268,11 +3378,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.006164026143775807</v>
+        <v>0.007736709414784072</v>
       </c>
     </row>
     <row r="9">
@@ -2281,11 +3391,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>white_quality_solution_color_1</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.005072227427154765</v>
+        <v>0.005629632018620954</v>
       </c>
     </row>
     <row r="10">
@@ -2294,11 +3404,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.004040564263570316</v>
+        <v>0.004000760960342559</v>
       </c>
     </row>
     <row r="11">
@@ -2307,11 +3417,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>white_quality_solution_color_2</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.004014770386757912</v>
+        <v>0.003806728156947169</v>
       </c>
     </row>
     <row r="12">
@@ -2320,11 +3430,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.003187695926451202</v>
+        <v>0.002882842864139905</v>
       </c>
     </row>
     <row r="13">
@@ -2333,11 +3443,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.002851850519399511</v>
+        <v>0.002670633776108256</v>
       </c>
     </row>
     <row r="14">
@@ -2346,11 +3456,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.002815958780106201</v>
+        <v>0.002277176808020272</v>
       </c>
     </row>
     <row r="15">
@@ -2359,11 +3469,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.002283599128182627</v>
+        <v>0.002254276794859032</v>
       </c>
     </row>
     <row r="16">
@@ -2372,11 +3482,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.002266976735163204</v>
+        <v>0.002196740586494563</v>
       </c>
     </row>
     <row r="17">
@@ -2385,11 +3495,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.002209669264662628</v>
+        <v>0.001991611778468329</v>
       </c>
     </row>
     <row r="18">
@@ -2398,11 +3508,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.002168518659715427</v>
+        <v>0.001981650928159711</v>
       </c>
     </row>
     <row r="19">
@@ -2411,11 +3521,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.002159487574025568</v>
+        <v>0.001776900232282438</v>
       </c>
     </row>
     <row r="20">
@@ -2424,11 +3534,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.00180778798393591</v>
+        <v>0.001725349766564107</v>
       </c>
     </row>
     <row r="21">
@@ -2437,11 +3547,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.001786544780691375</v>
+        <v>0.001552321998005159</v>
       </c>
     </row>
     <row r="22">
@@ -2450,11 +3560,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.001447185240035235</v>
+        <v>0.001500850875527292</v>
       </c>
     </row>
     <row r="23">
@@ -2463,11 +3573,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0004065740168260178</v>
+        <v>0.001464101489035468</v>
       </c>
     </row>
     <row r="24">
@@ -2476,11 +3586,401 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.00135649642937945</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.001294014005523748</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.001206122663108219</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>standard_liquor_pH</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.001167381262998629</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.001041035620556295</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>raw_syrup_color</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.0009894049265533594</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>raw_syrup_brix</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.000938319440473086</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>sulphited_brix</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.000925923811968918</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>white_quality_apparent_color_1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.0009212352558826193</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>boiling_r1_q</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.0008821176283592951</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>white_quality_apparent_color_2</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.0008402422651569407</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.0008340628663017962</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>filtercake_sugar</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.0008132895954746782</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.0007923317385663658</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>filtercake_moisture</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.0007882969006697734</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>boiling_r1_pol</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.0007837207757594585</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.0007618075063473855</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>wastewater_r1_pol</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.0007531306730161371</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.0007367385516409864</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.0007317274373024924</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.0007059589823853784</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.000698768824287874</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>report_date_year</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.0005572419416763432</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.0004894599256017411</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>report_year</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.0002792881493865698</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>carbonated_alkalinity</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.0002618237302263946</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_2</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.0002578164434175566</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.000252087349012528</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.0002306281107116144</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>7.594196436190925e-05</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>shift_name</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>6.341119611288038e-05</v>
+      <c r="C54" t="n">
+        <v>3.206814500804728e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2494,7 +3994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2524,7 +4024,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.340136795918765</v>
+        <v>0.3181566287671884</v>
       </c>
     </row>
     <row r="3">
@@ -2537,7 +4037,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2549405745773559</v>
+        <v>0.225245016388724</v>
       </c>
     </row>
     <row r="4">
@@ -2550,7 +4050,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.2025293146116408</v>
+        <v>0.211092557003509</v>
       </c>
     </row>
     <row r="5">
@@ -2563,7 +4063,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.09719288122166042</v>
+        <v>0.08824288268883339</v>
       </c>
     </row>
     <row r="6">
@@ -2576,7 +4076,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.05014252289189408</v>
+        <v>0.0311312153900558</v>
       </c>
     </row>
     <row r="7">
@@ -2585,11 +4085,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>white_quality_solution_color_1</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01589029923912289</v>
+        <v>0.0220825936988427</v>
       </c>
     </row>
     <row r="8">
@@ -2598,11 +4098,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.007523776659212974</v>
+        <v>0.01315219499276279</v>
       </c>
     </row>
     <row r="9">
@@ -2611,11 +4111,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.004874115878560938</v>
+        <v>0.01198557785307307</v>
       </c>
     </row>
     <row r="10">
@@ -2624,11 +4124,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.003783083269463529</v>
+        <v>0.01162416261146885</v>
       </c>
     </row>
     <row r="11">
@@ -2637,11 +4137,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.003541032793133277</v>
+        <v>0.007045092865230165</v>
       </c>
     </row>
     <row r="12">
@@ -2650,11 +4150,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.003425050897008127</v>
+        <v>0.006942158564037165</v>
       </c>
     </row>
     <row r="13">
@@ -2663,11 +4163,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>white_quality_solution_color_2</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.002773202284686469</v>
+        <v>0.00631140689285436</v>
       </c>
     </row>
     <row r="14">
@@ -2676,11 +4176,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.002422041860555468</v>
+        <v>0.003344487827892552</v>
       </c>
     </row>
     <row r="15">
@@ -2689,11 +4189,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.001583483864149519</v>
+        <v>0.003273497853480334</v>
       </c>
     </row>
     <row r="16">
@@ -2702,11 +4202,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.001444293841272595</v>
+        <v>0.003036778439689963</v>
       </c>
     </row>
     <row r="17">
@@ -2715,11 +4215,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.001364113069725128</v>
+        <v>0.002744408089620847</v>
       </c>
     </row>
     <row r="18">
@@ -2728,11 +4228,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.001317403013450218</v>
+        <v>0.00250354382601708</v>
       </c>
     </row>
     <row r="19">
@@ -2741,11 +4241,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.001260329777325474</v>
+        <v>0.00197266459610386</v>
       </c>
     </row>
     <row r="20">
@@ -2754,11 +4254,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.001039510138780859</v>
+        <v>0.001750847309758089</v>
       </c>
     </row>
     <row r="21">
@@ -2767,11 +4267,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0009833419547780897</v>
+        <v>0.001745766935296882</v>
       </c>
     </row>
     <row r="22">
@@ -2780,11 +4280,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0009160691162719914</v>
+        <v>0.001673063735473772</v>
       </c>
     </row>
     <row r="23">
@@ -2793,11 +4293,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0007778008419880633</v>
+        <v>0.001516273235907318</v>
       </c>
     </row>
     <row r="24">
@@ -2806,11 +4306,401 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>sweetwater_brix</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.001498391733627246</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>raw_syrup_color</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.001478413259820412</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>standard_liquor_color</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.001460034493748368</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>carbonated_pH</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.001219912516060806</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>boiler_tds</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.001175379803342451</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>white_quality_apparent_color_2</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.0009917240561012892</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>white_quality_ash_1</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.0009771219945312779</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>boiler_alkalinity</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.0009065155138097038</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.0008945082626808689</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.0008021534403865204</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>standard_liquor_pH</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.0007743703271407873</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>raw_syrup_brix</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.0007509547148492584</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.0007083334940501524</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>carbonated_alkalinity</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.0006882203627795102</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.0006812942521092414</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>sulphited_brix</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.0006748388105316527</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.0006669483459338774</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>boiling_r1_q</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.0006382026353400602</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_2</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.0006368282214652454</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>filtercake_moisture</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.0006364031463430259</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>wastewater_r1_pol</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.0006159301639449595</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>boiling_r1_pol</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.0005928112719898244</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_1</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.0005700067466729396</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.0005553763241052613</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.0005266185931786459</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.0005004626058432648</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>filtercake_sugar</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.0004655147573798946</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.0004500689253536527</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.000422029832543363</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.0003046341338028613</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>shift_name</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>0.0001389622791981613</v>
+      <c r="C54" t="n">
+        <v>0.0001631776947128911</v>
       </c>
     </row>
   </sheetData>
@@ -2824,7 +4714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2859,10 +4749,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4053344801629097</v>
+        <v>0.3513435888306793</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03004543567793681</v>
+        <v>0.03053200576697649</v>
       </c>
     </row>
     <row r="3">
@@ -2875,10 +4765,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.3175451473935752</v>
+        <v>0.2759191102277692</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008759112776318502</v>
+        <v>0.01461439317224813</v>
       </c>
     </row>
     <row r="4">
@@ -2891,10 +4781,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.06851419197261259</v>
+        <v>0.04750577254953945</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008666999719624723</v>
+        <v>0.008186002325973784</v>
       </c>
     </row>
     <row r="5">
@@ -2907,10 +4797,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03371629901748831</v>
+        <v>0.03309391811105004</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004811818942386509</v>
+        <v>0.007263898883167043</v>
       </c>
     </row>
     <row r="6">
@@ -2923,10 +4813,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03273356021269584</v>
+        <v>0.02184809894965081</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00502550419585127</v>
+        <v>0.005905270644834208</v>
       </c>
     </row>
     <row r="7">
@@ -2935,14 +4825,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.004202180688090374</v>
+        <v>0.01206627372144521</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001242537409313579</v>
+        <v>0.001336265620391601</v>
       </c>
     </row>
     <row r="8">
@@ -2951,14 +4841,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>white_quality_solution_color_1</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.004189485745192545</v>
+        <v>0.00529489991088965</v>
       </c>
       <c r="D8" t="n">
-        <v>0.000554769026971313</v>
+        <v>0.0003976234763443186</v>
       </c>
     </row>
     <row r="9">
@@ -2967,14 +4857,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.003269389548919888</v>
+        <v>0.004806630162510051</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0004914816337182211</v>
+        <v>0.0004636080255237824</v>
       </c>
     </row>
     <row r="10">
@@ -2983,14 +4873,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.001926320883916788</v>
+        <v>0.001357700694164798</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0005598383895992978</v>
+        <v>0.0004967944824144042</v>
       </c>
     </row>
     <row r="11">
@@ -2999,14 +4889,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.001896540205442111</v>
+        <v>0.001072473149984188</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0002243627269330095</v>
+        <v>0.0002321465188277864</v>
       </c>
     </row>
     <row r="12">
@@ -3015,14 +4905,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.001258513509459158</v>
+        <v>0.001059458746909891</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0004658016981737486</v>
+        <v>0.0005144413411651465</v>
       </c>
     </row>
     <row r="13">
@@ -3031,14 +4921,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>white_quality_solution_color_2</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001114776098329384</v>
+        <v>0.001018282359692546</v>
       </c>
       <c r="D13" t="n">
-        <v>0.001021603776230689</v>
+        <v>0.0003782462059274644</v>
       </c>
     </row>
     <row r="14">
@@ -3047,14 +4937,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.001047831069048322</v>
+        <v>0.0009180432739566924</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0004557772789622885</v>
+        <v>0.000138421386464402</v>
       </c>
     </row>
     <row r="15">
@@ -3063,14 +4953,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0007273394792266074</v>
+        <v>0.0006983973131602927</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0003785758957198074</v>
+        <v>0.0001653996214387366</v>
       </c>
     </row>
     <row r="16">
@@ -3079,14 +4969,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0005349511386086081</v>
+        <v>0.0005838627476783432</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0005320242229684252</v>
+        <v>0.0003567005451877534</v>
       </c>
     </row>
     <row r="17">
@@ -3095,14 +4985,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0005103662499918227</v>
+        <v>0.0005608043871210388</v>
       </c>
       <c r="D17" t="n">
-        <v>1.645205760868189e-05</v>
+        <v>0.0001418110680083998</v>
       </c>
     </row>
     <row r="18">
@@ -3111,14 +5001,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0004000061330024285</v>
+        <v>0.0005440955245589185</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0003228197297543746</v>
+        <v>0.000146711516104157</v>
       </c>
     </row>
     <row r="19">
@@ -3127,14 +5017,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.000329412536047069</v>
+        <v>0.0004804459140221318</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0002735233897933171</v>
+        <v>4.812864682349536e-05</v>
       </c>
     </row>
     <row r="20">
@@ -3143,14 +5033,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0002942146143418256</v>
+        <v>0.0004499382872577784</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0003067412965173731</v>
+        <v>0.0001279895971210851</v>
       </c>
     </row>
     <row r="21">
@@ -3159,14 +5049,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0002918346372657643</v>
+        <v>0.0004278258866586282</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0004919589089306017</v>
+        <v>0.0001641164382686292</v>
       </c>
     </row>
     <row r="22">
@@ -3175,14 +5065,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5.285113751526405e-05</v>
+        <v>0.0004154677420654673</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0004882882099828778</v>
+        <v>0.0001461258018781128</v>
       </c>
     </row>
     <row r="23">
@@ -3191,14 +5081,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4.013245133074328e-05</v>
+        <v>0.0004012968385182947</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0001087013963285067</v>
+        <v>0.0001170437715153523</v>
       </c>
     </row>
     <row r="24">
@@ -3207,14 +5097,494 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.0003276991593949123</v>
+      </c>
+      <c r="D24" t="n">
+        <v>4.135176520778196e-05</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>sweetwater_brix</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.0002877783329671813</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.0002094539787748713</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>raw_syrup_brix</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.0002798968058276841</v>
+      </c>
+      <c r="D26" t="n">
+        <v>5.190638448154603e-05</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>report_date_day</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.0002770821278502811</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.0007012010899998592</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.0002748763353595973</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.0001123196158222344</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.0002552838898238985</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.0001152903528818941</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>filtercake_sugar</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.0002394229405602966</v>
+      </c>
+      <c r="D30" t="n">
+        <v>8.183416016963418e-05</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>report_date_year</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.0002351742058631312</v>
+      </c>
+      <c r="D31" t="n">
+        <v>9.009586389456478e-05</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.0001805774039261188</v>
+      </c>
+      <c r="D32" t="n">
+        <v>4.863074663444317e-05</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>report_year</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.0001752374778752896</v>
+      </c>
+      <c r="D33" t="n">
+        <v>5.471745656656125e-05</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.0001532927007891982</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.0001136504334026771</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>white_quality_apparent_color_1</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.0001508168303326674</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.0001196766785764251</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.0001176696373987762</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.0001041517007083891</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>wastewater_r1_pol</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>8.608242056333815e-05</v>
+      </c>
+      <c r="D37" t="n">
+        <v>6.207840810291382e-05</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>5.83587393926388e-05</v>
+      </c>
+      <c r="D38" t="n">
+        <v>3.338408634509133e-05</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1.151763200234468e-05</v>
+      </c>
+      <c r="D39" t="n">
+        <v>7.348041309156887e-06</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>filtercake_moisture</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>7.232775912602296e-06</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.0001037484509615567</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>boiling_r1_pol</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>5.880174109140768e-06</v>
+      </c>
+      <c r="D41" t="n">
+        <v>3.595079266975626e-05</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>-7.116172808396826e-06</v>
+      </c>
+      <c r="D42" t="n">
+        <v>8.164737659405049e-05</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>-7.89463475965313e-06</v>
+      </c>
+      <c r="D43" t="n">
+        <v>7.923636820170506e-05</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>-9.313573361979799e-06</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.0001416806697803268</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_2</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>-1.365397194396101e-05</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2.896835159465596e-05</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>shift_name</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>-4.726614070832413e-05</v>
-      </c>
-      <c r="D24" t="n">
-        <v>2.158028088579111e-05</v>
+      <c r="C46" t="n">
+        <v>-1.952708848380613e-05</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1.483805947810876e-05</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>-2.071002570160907e-05</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.000104530936645966</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>-4.138304986746055e-05</v>
+      </c>
+      <c r="D48" t="n">
+        <v>9.150149094249704e-05</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_1</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>-6.309281372750553e-05</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2.35450978663644e-05</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>white_quality_apparent_color_2</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>-7.825080711114652e-05</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.0001119340775256389</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.0001452977838964698</v>
+      </c>
+      <c r="D51" t="n">
+        <v>8.59022910601418e-05</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>raw_syrup_color</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>-0.0001692251611651874</v>
+      </c>
+      <c r="D52" t="n">
+        <v>6.592491703886012e-05</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>-0.0001891751093902161</v>
+      </c>
+      <c r="D53" t="n">
+        <v>6.920701365903529e-05</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>sulphited_brix</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.0002161354935916626</v>
+      </c>
+      <c r="D54" t="n">
+        <v>6.411070110731075e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3228,7 +5598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3258,7 +5628,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.36129558406933</v>
+        <v>1.478740368189571</v>
       </c>
     </row>
     <row r="3">
@@ -3271,7 +5641,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.348991351486901</v>
+        <v>1.433803714952994</v>
       </c>
     </row>
     <row r="4">
@@ -3284,7 +5654,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8432722674881616</v>
+        <v>1.296472196351193</v>
       </c>
     </row>
     <row r="5">
@@ -3293,11 +5663,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8206497677308695</v>
+        <v>1.107645524286439</v>
       </c>
     </row>
     <row r="6">
@@ -3306,11 +5676,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.7485294408411005</v>
+        <v>0.952211235371005</v>
       </c>
     </row>
     <row r="7">
@@ -3323,7 +5693,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.746755165169334</v>
+        <v>0.8325968016518011</v>
       </c>
     </row>
     <row r="8">
@@ -3332,11 +5702,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.20921047266933</v>
+        <v>0.8088540008413529</v>
       </c>
     </row>
     <row r="9">
@@ -3345,11 +5715,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.1899232477355577</v>
+        <v>0.7924090046246004</v>
       </c>
     </row>
     <row r="10">
@@ -3358,11 +5728,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.1578088310291892</v>
+        <v>0.6333921093174082</v>
       </c>
     </row>
     <row r="11">
@@ -3371,11 +5741,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>white_quality_solution_color_1</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.1315837872656744</v>
+        <v>0.3373116316724039</v>
       </c>
     </row>
     <row r="12">
@@ -3384,11 +5754,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.1115458931717002</v>
+        <v>0.2929207431772767</v>
       </c>
     </row>
     <row r="13">
@@ -3397,11 +5767,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.107151986964845</v>
+        <v>0.2770263523620402</v>
       </c>
     </row>
     <row r="14">
@@ -3410,11 +5780,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>white_quality_solution_color_2</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.09934044474291781</v>
+        <v>0.2731534068695995</v>
       </c>
     </row>
     <row r="15">
@@ -3423,11 +5793,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.08976659956018462</v>
+        <v>0.2617903996465323</v>
       </c>
     </row>
     <row r="16">
@@ -3436,11 +5806,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0883991257412613</v>
+        <v>0.229753298447156</v>
       </c>
     </row>
     <row r="17">
@@ -3449,11 +5819,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.08823011340388565</v>
+        <v>0.2295057870794264</v>
       </c>
     </row>
     <row r="18">
@@ -3462,11 +5832,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.08543097805753064</v>
+        <v>0.2218485223188855</v>
       </c>
     </row>
     <row r="19">
@@ -3475,11 +5845,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.07214471272382861</v>
+        <v>0.2207323944761521</v>
       </c>
     </row>
     <row r="20">
@@ -3488,11 +5858,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.06606132546147458</v>
+        <v>0.2086458278708552</v>
       </c>
     </row>
     <row r="21">
@@ -3501,11 +5871,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.04016129108841815</v>
+        <v>0.2057084216457903</v>
       </c>
     </row>
     <row r="22">
@@ -3514,11 +5884,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02367048450294096</v>
+        <v>0.2052719691187259</v>
       </c>
     </row>
     <row r="23">
@@ -3527,23 +5897,413 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>shift_name</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.2014771250067651</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>standard_liquor_color</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.2005507462162361</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>sulphited_color</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.1776140935255817</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.1709834645543058</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>lime_alkalinity</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.159505819969981</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>sweetwater_brix</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.1543834728358466</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>carbonated_pH</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.1414615172091742</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>filtercake_sugar</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.1321623732084736</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>sulphited_brix</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.1306732706335407</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.1193277577675893</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.1111174670285382</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.1100992902083822</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.1083655886876653</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>boiling_r1_q</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.1081584076742153</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.1077356270524956</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>filtercake_moisture</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.1054561942143275</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.1047131403997339</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>standard_liquor_pH</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.1043761904758367</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.09267643000428505</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.08181546115420524</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>boiling_r1_pol</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.08120877841116192</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>boiler_tds</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.0786731789563766</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>wastewater_r1_pol</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.07692667533808129</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.05888879003301017</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>boiler_alkalinity</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.04923555457813222</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>sulphited_pH</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C48" t="n">
+        <v>0.04556853675596395</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.03360896424143878</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>carbonated_alkalinity</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.01937812905933955</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_1</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.001182132265124647</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>shift_name</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>51</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3595,17 +6355,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>755</v>
+        <v>788</v>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D2" t="n">
-        <v>400</v>
+        <v>446</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-06-11 04:44:57 UTC</t>
+          <t>2026-06-11 05:04:47 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_solution_color.xlsx
+++ b/NN/reports/feature_importance_white_solution_color.xlsx
@@ -587,7 +587,7 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04750577254953945</v>
+        <v>0.04750577254953946</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -624,7 +624,7 @@
         <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03309391811105004</v>
+        <v>0.03309391811105006</v>
       </c>
       <c r="H5" t="n">
         <v>4</v>
@@ -661,7 +661,7 @@
         <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02184809894965081</v>
+        <v>0.02184809894965078</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -735,7 +735,7 @@
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004806630162510051</v>
+        <v>0.004806630162510062</v>
       </c>
       <c r="H8" t="n">
         <v>8</v>
@@ -772,7 +772,7 @@
         <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00529489991088965</v>
+        <v>0.005294899910889639</v>
       </c>
       <c r="H9" t="n">
         <v>7</v>
@@ -809,7 +809,7 @@
         <v>5</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0003276991593949123</v>
+        <v>0.0003276991593948125</v>
       </c>
       <c r="H10" t="n">
         <v>23</v>
@@ -846,7 +846,7 @@
         <v>12</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001018282359692546</v>
+        <v>0.001018282359692535</v>
       </c>
       <c r="H11" t="n">
         <v>12</v>
@@ -994,7 +994,7 @@
         <v>16</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001072473149984188</v>
+        <v>0.001072473149984199</v>
       </c>
       <c r="H15" t="n">
         <v>10</v>
@@ -1031,7 +1031,7 @@
         <v>21</v>
       </c>
       <c r="G16" t="n">
-        <v>0.001059458746909891</v>
+        <v>0.00105945874690988</v>
       </c>
       <c r="H16" t="n">
         <v>11</v>
@@ -1142,7 +1142,7 @@
         <v>26</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0009180432739566924</v>
+        <v>0.0009180432739566702</v>
       </c>
       <c r="H19" t="n">
         <v>13</v>
@@ -1216,7 +1216,7 @@
         <v>29</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0004154677420654673</v>
+        <v>0.0004154677420655006</v>
       </c>
       <c r="H21" t="n">
         <v>21</v>
@@ -1253,7 +1253,7 @@
         <v>23</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0002877783329671813</v>
+        <v>0.0002877783329671701</v>
       </c>
       <c r="H22" t="n">
         <v>24</v>
@@ -1290,7 +1290,7 @@
         <v>9</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0001805774039261188</v>
+        <v>0.0001805774039261299</v>
       </c>
       <c r="H23" t="n">
         <v>31</v>
@@ -1327,7 +1327,7 @@
         <v>18</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0002552838898238985</v>
+        <v>0.0002552838898238874</v>
       </c>
       <c r="H24" t="n">
         <v>28</v>
@@ -1364,7 +1364,7 @@
         <v>27</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0005608043871210388</v>
+        <v>0.0005608043871210167</v>
       </c>
       <c r="H25" t="n">
         <v>16</v>
@@ -1438,7 +1438,7 @@
         <v>19</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0001176696373987762</v>
+        <v>0.0001176696373987651</v>
       </c>
       <c r="H27" t="n">
         <v>35</v>
@@ -1475,7 +1475,7 @@
         <v>34</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0002798968058276841</v>
+        <v>0.0002798968058276729</v>
       </c>
       <c r="H28" t="n">
         <v>25</v>
@@ -1512,7 +1512,7 @@
         <v>14</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0001752374778752896</v>
+        <v>0.0001752374778752785</v>
       </c>
       <c r="H29" t="n">
         <v>32</v>
@@ -1549,7 +1549,7 @@
         <v>24</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.0001692251611651874</v>
+        <v>-0.0001692251611651985</v>
       </c>
       <c r="H30" t="n">
         <v>51</v>
@@ -1586,7 +1586,7 @@
         <v>33</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0004499382872577784</v>
+        <v>0.0004499382872577451</v>
       </c>
       <c r="H31" t="n">
         <v>19</v>
@@ -1623,7 +1623,7 @@
         <v>30</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0004012968385182947</v>
+        <v>0.0004012968385182836</v>
       </c>
       <c r="H32" t="n">
         <v>22</v>
@@ -1697,7 +1697,7 @@
         <v>28</v>
       </c>
       <c r="G34" t="n">
-        <v>-7.825080711114652e-05</v>
+        <v>-7.825080711113542e-05</v>
       </c>
       <c r="H34" t="n">
         <v>49</v>
@@ -1771,7 +1771,7 @@
         <v>39</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0002748763353595973</v>
+        <v>0.0002748763353596195</v>
       </c>
       <c r="H36" t="n">
         <v>27</v>
@@ -1808,7 +1808,7 @@
         <v>49</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0002394229405602966</v>
+        <v>0.0002394229405603188</v>
       </c>
       <c r="H37" t="n">
         <v>29</v>
@@ -1845,7 +1845,7 @@
         <v>37</v>
       </c>
       <c r="G38" t="n">
-        <v>-9.313573361979799e-06</v>
+        <v>-9.313573361968696e-06</v>
       </c>
       <c r="H38" t="n">
         <v>43</v>
@@ -1882,7 +1882,7 @@
         <v>35</v>
       </c>
       <c r="G39" t="n">
-        <v>-4.138304986746055e-05</v>
+        <v>-4.138304986744945e-05</v>
       </c>
       <c r="H39" t="n">
         <v>47</v>
@@ -1919,7 +1919,7 @@
         <v>31</v>
       </c>
       <c r="G40" t="n">
-        <v>-2.071002570160907e-05</v>
+        <v>-2.071002570162017e-05</v>
       </c>
       <c r="H40" t="n">
         <v>46</v>
@@ -1956,7 +1956,7 @@
         <v>36</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0004804459140221318</v>
+        <v>0.0004804459140221207</v>
       </c>
       <c r="H41" t="n">
         <v>18</v>
@@ -1993,7 +1993,7 @@
         <v>38</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.0002161354935916626</v>
+        <v>-0.0002161354935916515</v>
       </c>
       <c r="H42" t="n">
         <v>53</v>
@@ -2030,7 +2030,7 @@
         <v>42</v>
       </c>
       <c r="G43" t="n">
-        <v>7.232775912602296e-06</v>
+        <v>7.232775912613399e-06</v>
       </c>
       <c r="H43" t="n">
         <v>39</v>
@@ -2067,7 +2067,7 @@
         <v>46</v>
       </c>
       <c r="G44" t="n">
-        <v>-7.89463475965313e-06</v>
+        <v>-7.894634759664232e-06</v>
       </c>
       <c r="H44" t="n">
         <v>42</v>
@@ -2141,7 +2141,7 @@
         <v>44</v>
       </c>
       <c r="G46" t="n">
-        <v>5.880174109140768e-06</v>
+        <v>5.880174109118563e-06</v>
       </c>
       <c r="H46" t="n">
         <v>40</v>
@@ -2252,7 +2252,7 @@
         <v>47</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.0001891751093902161</v>
+        <v>-0.0001891751093902494</v>
       </c>
       <c r="H49" t="n">
         <v>52</v>
@@ -2400,7 +2400,7 @@
         <v>45</v>
       </c>
       <c r="G53" t="n">
-        <v>-6.309281372750553e-05</v>
+        <v>-6.309281372748332e-05</v>
       </c>
       <c r="H53" t="n">
         <v>48</v>
@@ -2619,7 +2619,7 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04750577254953945</v>
+        <v>0.04750577254953946</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -2656,7 +2656,7 @@
         <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03309391811105004</v>
+        <v>0.03309391811105006</v>
       </c>
       <c r="H5" t="n">
         <v>4</v>
@@ -2693,7 +2693,7 @@
         <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02184809894965081</v>
+        <v>0.02184809894965078</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -2767,7 +2767,7 @@
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004806630162510051</v>
+        <v>0.004806630162510062</v>
       </c>
       <c r="H8" t="n">
         <v>8</v>
@@ -2804,7 +2804,7 @@
         <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00529489991088965</v>
+        <v>0.005294899910889639</v>
       </c>
       <c r="H9" t="n">
         <v>7</v>
@@ -2841,7 +2841,7 @@
         <v>5</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0003276991593949123</v>
+        <v>0.0003276991593948125</v>
       </c>
       <c r="H10" t="n">
         <v>23</v>
@@ -2878,7 +2878,7 @@
         <v>12</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001018282359692546</v>
+        <v>0.001018282359692535</v>
       </c>
       <c r="H11" t="n">
         <v>12</v>
@@ -3026,7 +3026,7 @@
         <v>16</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001072473149984188</v>
+        <v>0.001072473149984199</v>
       </c>
       <c r="H15" t="n">
         <v>10</v>
@@ -3063,7 +3063,7 @@
         <v>21</v>
       </c>
       <c r="G16" t="n">
-        <v>0.001059458746909891</v>
+        <v>0.00105945874690988</v>
       </c>
       <c r="H16" t="n">
         <v>11</v>
@@ -3174,7 +3174,7 @@
         <v>26</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0009180432739566924</v>
+        <v>0.0009180432739566702</v>
       </c>
       <c r="H19" t="n">
         <v>13</v>
@@ -3248,7 +3248,7 @@
         <v>29</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0004154677420654673</v>
+        <v>0.0004154677420655006</v>
       </c>
       <c r="H21" t="n">
         <v>21</v>
@@ -4768,7 +4768,7 @@
         <v>0.2759191102277692</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01461439317224813</v>
+        <v>0.01461439317224815</v>
       </c>
     </row>
     <row r="4">
@@ -4781,10 +4781,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.04750577254953945</v>
+        <v>0.04750577254953946</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008186002325973784</v>
+        <v>0.008186002325973791</v>
       </c>
     </row>
     <row r="5">
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03309391811105004</v>
+        <v>0.03309391811105006</v>
       </c>
       <c r="D5" t="n">
-        <v>0.007263898883167043</v>
+        <v>0.007263898883167018</v>
       </c>
     </row>
     <row r="6">
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.02184809894965081</v>
+        <v>0.02184809894965078</v>
       </c>
       <c r="D6" t="n">
-        <v>0.005905270644834208</v>
+        <v>0.005905270644834206</v>
       </c>
     </row>
     <row r="7">
@@ -4832,7 +4832,7 @@
         <v>0.01206627372144521</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001336265620391601</v>
+        <v>0.001336265620391592</v>
       </c>
     </row>
     <row r="8">
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.00529489991088965</v>
+        <v>0.005294899910889639</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0003976234763443186</v>
+        <v>0.0003976234763442932</v>
       </c>
     </row>
     <row r="9">
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.004806630162510051</v>
+        <v>0.004806630162510062</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0004636080255237824</v>
+        <v>0.0004636080255238202</v>
       </c>
     </row>
     <row r="10">
@@ -4880,7 +4880,7 @@
         <v>0.001357700694164798</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0004967944824144042</v>
+        <v>0.0004967944824143995</v>
       </c>
     </row>
     <row r="11">
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.001072473149984188</v>
+        <v>0.001072473149984199</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0002321465188277864</v>
+        <v>0.0002321465188277932</v>
       </c>
     </row>
     <row r="12">
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.001059458746909891</v>
+        <v>0.00105945874690988</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0005144413411651465</v>
+        <v>0.0005144413411651807</v>
       </c>
     </row>
     <row r="13">
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001018282359692546</v>
+        <v>0.001018282359692535</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0003782462059274644</v>
+        <v>0.0003782462059274685</v>
       </c>
     </row>
     <row r="14">
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0009180432739566924</v>
+        <v>0.0009180432739566702</v>
       </c>
       <c r="D14" t="n">
-        <v>0.000138421386464402</v>
+        <v>0.0001384213864644027</v>
       </c>
     </row>
     <row r="15">
@@ -4976,7 +4976,7 @@
         <v>0.0005838627476783432</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0003567005451877534</v>
+        <v>0.0003567005451877216</v>
       </c>
     </row>
     <row r="17">
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0005608043871210388</v>
+        <v>0.0005608043871210167</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0001418110680083998</v>
+        <v>0.0001418110680083992</v>
       </c>
     </row>
     <row r="18">
@@ -5021,10 +5021,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0004804459140221318</v>
+        <v>0.0004804459140221207</v>
       </c>
       <c r="D19" t="n">
-        <v>4.812864682349536e-05</v>
+        <v>4.812864682349979e-05</v>
       </c>
     </row>
     <row r="20">
@@ -5037,10 +5037,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0004499382872577784</v>
+        <v>0.0004499382872577451</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0001279895971210851</v>
+        <v>0.0001279895971210836</v>
       </c>
     </row>
     <row r="21">
@@ -5056,7 +5056,7 @@
         <v>0.0004278258866586282</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0001641164382686292</v>
+        <v>0.0001641164382686324</v>
       </c>
     </row>
     <row r="22">
@@ -5069,10 +5069,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0004154677420654673</v>
+        <v>0.0004154677420655006</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0001461258018781128</v>
+        <v>0.0001461258018780851</v>
       </c>
     </row>
     <row r="23">
@@ -5085,10 +5085,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0004012968385182947</v>
+        <v>0.0004012968385182836</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0001170437715153523</v>
+        <v>0.0001170437715153925</v>
       </c>
     </row>
     <row r="24">
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0003276991593949123</v>
+        <v>0.0003276991593948125</v>
       </c>
       <c r="D24" t="n">
-        <v>4.135176520778196e-05</v>
+        <v>4.135176520778005e-05</v>
       </c>
     </row>
     <row r="25">
@@ -5117,10 +5117,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0002877783329671813</v>
+        <v>0.0002877783329671701</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0002094539787748713</v>
+        <v>0.0002094539787748468</v>
       </c>
     </row>
     <row r="26">
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0002798968058276841</v>
+        <v>0.0002798968058276729</v>
       </c>
       <c r="D26" t="n">
-        <v>5.190638448154603e-05</v>
+        <v>5.190638448151934e-05</v>
       </c>
     </row>
     <row r="27">
@@ -5152,7 +5152,7 @@
         <v>0.0002770821278502811</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0007012010899998592</v>
+        <v>0.0007012010899998666</v>
       </c>
     </row>
     <row r="28">
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0002748763353595973</v>
+        <v>0.0002748763353596195</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0001123196158222344</v>
+        <v>0.0001123196158222657</v>
       </c>
     </row>
     <row r="29">
@@ -5181,10 +5181,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0002552838898238985</v>
+        <v>0.0002552838898238874</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0001152903528818941</v>
+        <v>0.0001152903528818913</v>
       </c>
     </row>
     <row r="30">
@@ -5197,10 +5197,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0002394229405602966</v>
+        <v>0.0002394229405603188</v>
       </c>
       <c r="D30" t="n">
-        <v>8.183416016963418e-05</v>
+        <v>8.183416016965158e-05</v>
       </c>
     </row>
     <row r="31">
@@ -5216,7 +5216,7 @@
         <v>0.0002351742058631312</v>
       </c>
       <c r="D31" t="n">
-        <v>9.009586389456478e-05</v>
+        <v>9.009586389459285e-05</v>
       </c>
     </row>
     <row r="32">
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0001805774039261188</v>
+        <v>0.0001805774039261299</v>
       </c>
       <c r="D32" t="n">
-        <v>4.863074663444317e-05</v>
+        <v>4.863074663440316e-05</v>
       </c>
     </row>
     <row r="33">
@@ -5245,10 +5245,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0001752374778752896</v>
+        <v>0.0001752374778752785</v>
       </c>
       <c r="D33" t="n">
-        <v>5.471745656656125e-05</v>
+        <v>5.471745656656576e-05</v>
       </c>
     </row>
     <row r="34">
@@ -5264,7 +5264,7 @@
         <v>0.0001532927007891982</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0001136504334026771</v>
+        <v>0.0001136504334027028</v>
       </c>
     </row>
     <row r="35">
@@ -5280,7 +5280,7 @@
         <v>0.0001508168303326674</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0001196766785764251</v>
+        <v>0.0001196766785764144</v>
       </c>
     </row>
     <row r="36">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0001176696373987762</v>
+        <v>0.0001176696373987651</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0001041517007083891</v>
+        <v>0.0001041517007083905</v>
       </c>
     </row>
     <row r="37">
@@ -5328,7 +5328,7 @@
         <v>5.83587393926388e-05</v>
       </c>
       <c r="D38" t="n">
-        <v>3.338408634509133e-05</v>
+        <v>3.338408634509426e-05</v>
       </c>
     </row>
     <row r="39">
@@ -5344,7 +5344,7 @@
         <v>1.151763200234468e-05</v>
       </c>
       <c r="D39" t="n">
-        <v>7.348041309156887e-06</v>
+        <v>7.348041309172165e-06</v>
       </c>
     </row>
     <row r="40">
@@ -5357,10 +5357,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>7.232775912602296e-06</v>
+        <v>7.232775912613399e-06</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0001037484509615567</v>
+        <v>0.0001037484509615598</v>
       </c>
     </row>
     <row r="41">
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5.880174109140768e-06</v>
+        <v>5.880174109118563e-06</v>
       </c>
       <c r="D41" t="n">
-        <v>3.595079266975626e-05</v>
+        <v>3.595079266976442e-05</v>
       </c>
     </row>
     <row r="42">
@@ -5392,7 +5392,7 @@
         <v>-7.116172808396826e-06</v>
       </c>
       <c r="D42" t="n">
-        <v>8.164737659405049e-05</v>
+        <v>8.164737659405992e-05</v>
       </c>
     </row>
     <row r="43">
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-7.89463475965313e-06</v>
+        <v>-7.894634759664232e-06</v>
       </c>
       <c r="D43" t="n">
-        <v>7.923636820170506e-05</v>
+        <v>7.923636820170663e-05</v>
       </c>
     </row>
     <row r="44">
@@ -5421,10 +5421,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-9.313573361979799e-06</v>
+        <v>-9.313573361968696e-06</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0001416806697803268</v>
+        <v>0.0001416806697803597</v>
       </c>
     </row>
     <row r="45">
@@ -5440,7 +5440,7 @@
         <v>-1.365397194396101e-05</v>
       </c>
       <c r="D45" t="n">
-        <v>2.896835159465596e-05</v>
+        <v>2.896835159471466e-05</v>
       </c>
     </row>
     <row r="46">
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-2.071002570160907e-05</v>
+        <v>-2.071002570162017e-05</v>
       </c>
       <c r="D47" t="n">
-        <v>0.000104530936645966</v>
+        <v>0.0001045309366459781</v>
       </c>
     </row>
     <row r="48">
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-4.138304986746055e-05</v>
+        <v>-4.138304986744945e-05</v>
       </c>
       <c r="D48" t="n">
-        <v>9.150149094249704e-05</v>
+        <v>9.150149094252794e-05</v>
       </c>
     </row>
     <row r="49">
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-6.309281372750553e-05</v>
+        <v>-6.309281372748332e-05</v>
       </c>
       <c r="D49" t="n">
-        <v>2.35450978663644e-05</v>
+        <v>2.35450978663369e-05</v>
       </c>
     </row>
     <row r="50">
@@ -5517,10 +5517,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-7.825080711114652e-05</v>
+        <v>-7.825080711113542e-05</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0001119340775256389</v>
+        <v>0.0001119340775256447</v>
       </c>
     </row>
     <row r="51">
@@ -5549,10 +5549,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-0.0001692251611651874</v>
+        <v>-0.0001692251611651985</v>
       </c>
       <c r="D52" t="n">
-        <v>6.592491703886012e-05</v>
+        <v>6.592491703884429e-05</v>
       </c>
     </row>
     <row r="53">
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-0.0001891751093902161</v>
+        <v>-0.0001891751093902494</v>
       </c>
       <c r="D53" t="n">
-        <v>6.920701365903529e-05</v>
+        <v>6.920701365905233e-05</v>
       </c>
     </row>
     <row r="54">
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-0.0002161354935916626</v>
+        <v>-0.0002161354935916515</v>
       </c>
       <c r="D54" t="n">
-        <v>6.411070110731075e-05</v>
+        <v>6.41107011072986e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-06-11 05:04:47 UTC</t>
+          <t>2026-06-11 09:45:03 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_solution_color.xlsx
+++ b/NN/reports/feature_importance_white_solution_color.xlsx
@@ -501,25 +501,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3424292685068677</v>
+        <v>0.3509264667099231</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3181566287671884</v>
+        <v>0.3273009785562683</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3513435888306793</v>
+        <v>0.3598793571410549</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1.433803714952994</v>
+        <v>1.197596762489799</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
@@ -538,25 +538,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2383658985078753</v>
+        <v>0.2430083986073938</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.225245016388724</v>
+        <v>0.2341821975658129</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2759191102277692</v>
+        <v>0.2813470101326704</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>1.478740368189571</v>
+        <v>1.220162286626203</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -571,35 +571,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1331501555978941</v>
+        <v>0.1136888176080379</v>
       </c>
       <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.202284502935228</v>
+      </c>
+      <c r="F4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" t="n">
-        <v>0.08824288268883339</v>
-      </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
+        <v>0.03188475108235696</v>
+      </c>
+      <c r="H4" t="n">
         <v>4</v>
       </c>
-      <c r="G4" t="n">
-        <v>0.04750577254953946</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3</v>
-      </c>
       <c r="I4" t="n">
-        <v>0.952211235371005</v>
+        <v>0.6066707781972243</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
@@ -608,35 +608,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.1138727203369802</v>
+        <v>0.1216747028217113</v>
       </c>
       <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.08437781417749506</v>
+      </c>
+      <c r="F5" t="n">
         <v>4</v>
       </c>
-      <c r="E5" t="n">
-        <v>0.01315219499276279</v>
-      </c>
-      <c r="F5" t="n">
-        <v>7</v>
-      </c>
       <c r="G5" t="n">
-        <v>0.03309391811105006</v>
+        <v>0.0416466695227404</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8325968016518011</v>
+        <v>0.595591263334927</v>
       </c>
       <c r="J5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K5" t="n">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
@@ -645,35 +645,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0925122844997833</v>
+        <v>0.09170833013467054</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>0.211092557003509</v>
+        <v>0.01261148354771118</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02184809894965078</v>
+        <v>0.02157996931448751</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7924090046246004</v>
+        <v>0.6149920332849157</v>
       </c>
       <c r="J6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="7">
@@ -686,25 +686,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01182290118112469</v>
+        <v>0.01179176619992063</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01198557785307307</v>
+        <v>0.0125716311096866</v>
       </c>
       <c r="F7" t="n">
         <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01206627372144521</v>
+        <v>0.01200704749597893</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8088540008413529</v>
+        <v>0.6059710037229373</v>
       </c>
       <c r="J7" t="n">
         <v>7</v>
@@ -723,25 +723,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.007736709414784072</v>
+        <v>0.006322868406578661</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>0.007045092865230165</v>
+        <v>0.006797540172290032</v>
       </c>
       <c r="F8" t="n">
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004806630162510062</v>
+        <v>0.004525107807768736</v>
       </c>
       <c r="H8" t="n">
         <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>1.107645524286439</v>
+        <v>0.8723113670408211</v>
       </c>
       <c r="J8" t="n">
         <v>4</v>
@@ -760,25 +760,25 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.005629632018620954</v>
+        <v>0.005621442661865416</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0220825936988427</v>
+        <v>0.01914241201728629</v>
       </c>
       <c r="F9" t="n">
         <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.005294899910889639</v>
+        <v>0.005298272783865276</v>
       </c>
       <c r="H9" t="n">
         <v>7</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3373116316724039</v>
+        <v>0.2717957000954292</v>
       </c>
       <c r="J9" t="n">
         <v>10</v>
@@ -797,25 +797,25 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.002882842864139905</v>
+        <v>0.003044858379230276</v>
       </c>
       <c r="D10" t="n">
         <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0311312153900558</v>
+        <v>0.03151805388149846</v>
       </c>
       <c r="F10" t="n">
         <v>5</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0003276991593948125</v>
+        <v>0.000372539178951691</v>
       </c>
       <c r="H10" t="n">
         <v>23</v>
       </c>
       <c r="I10" t="n">
-        <v>1.296472196351193</v>
+        <v>1.032026958462696</v>
       </c>
       <c r="J10" t="n">
         <v>3</v>
@@ -834,31 +834,31 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.003806728156947169</v>
+        <v>0.003738895770907981</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00631140689285436</v>
+        <v>0.006383871055968616</v>
       </c>
       <c r="F11" t="n">
+        <v>11</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.001006899723146704</v>
+      </c>
+      <c r="H11" t="n">
+        <v>13</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.2636575744571474</v>
+      </c>
+      <c r="J11" t="n">
         <v>12</v>
       </c>
-      <c r="G11" t="n">
-        <v>0.001018282359692535</v>
-      </c>
-      <c r="H11" t="n">
-        <v>12</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.2731534068695995</v>
-      </c>
-      <c r="J11" t="n">
-        <v>13</v>
-      </c>
       <c r="K11" t="n">
-        <v>11.75</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="12">
@@ -867,35 +867,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.004000760960342559</v>
+        <v>0.002699248342943198</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>0.003036778439689963</v>
+        <v>0.001671672701943038</v>
       </c>
       <c r="F12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0002770821278502811</v>
+        <v>0.001066831892333842</v>
       </c>
       <c r="H12" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6333921093174082</v>
+        <v>0.1883237605390065</v>
       </c>
       <c r="J12" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="K12" t="n">
-        <v>14.75</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="13">
@@ -904,32 +904,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.002277176808020272</v>
+        <v>0.001648145579726441</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E13" t="n">
-        <v>0.001516273235907318</v>
+        <v>0.002453077075937192</v>
       </c>
       <c r="F13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G13" t="n">
-        <v>0.001357700694164798</v>
+        <v>0.0005687225825382169</v>
       </c>
       <c r="H13" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2052719691187259</v>
+        <v>0.2125263033038287</v>
       </c>
       <c r="J13" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="K13" t="n">
         <v>16.25</v>
@@ -941,32 +941,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.001725349766564107</v>
+        <v>0.00401375600794517</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>0.00250354382601708</v>
+        <v>0.002790204142766983</v>
       </c>
       <c r="F14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0006983973131602927</v>
+        <v>0.000207213615126034</v>
       </c>
       <c r="H14" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="I14" t="n">
-        <v>0.229753298447156</v>
+        <v>0.4961557840490896</v>
       </c>
       <c r="J14" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K14" t="n">
         <v>16.25</v>
@@ -978,32 +978,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.002254276794859032</v>
+        <v>0.002245715045750216</v>
       </c>
       <c r="D15" t="n">
         <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>0.002744408089620847</v>
+        <v>0.00152358979170372</v>
       </c>
       <c r="F15" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001072473149984199</v>
+        <v>0.001319066452785034</v>
       </c>
       <c r="H15" t="n">
         <v>10</v>
       </c>
       <c r="I15" t="n">
-        <v>0.159505819969981</v>
+        <v>0.1581573980849016</v>
       </c>
       <c r="J15" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="K15" t="n">
         <v>16.5</v>
@@ -1015,35 +1015,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.002670633776108256</v>
+        <v>0.00217139327705321</v>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E16" t="n">
-        <v>0.001673063735473772</v>
+        <v>0.002930754602353963</v>
       </c>
       <c r="F16" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G16" t="n">
-        <v>0.00105945874690988</v>
+        <v>0.001145782448783261</v>
       </c>
       <c r="H16" t="n">
         <v>11</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1776140935255817</v>
+        <v>0.1185070533412098</v>
       </c>
       <c r="J16" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="K16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
@@ -1056,31 +1056,31 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.001776900232282438</v>
+        <v>0.00172816822723828</v>
       </c>
       <c r="D17" t="n">
         <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>0.001745766935296882</v>
+        <v>0.001615668932758181</v>
       </c>
       <c r="F17" t="n">
         <v>20</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0004278258866586282</v>
+        <v>0.0003341763919278318</v>
       </c>
       <c r="H17" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2617903996465323</v>
+        <v>0.2099184335506039</v>
       </c>
       <c r="J17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>18</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="18">
@@ -1089,35 +1089,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.002196740586494563</v>
+        <v>0.001120522902745008</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E18" t="n">
-        <v>0.001460034493748368</v>
+        <v>0.004567903659766977</v>
       </c>
       <c r="F18" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0005838627476783432</v>
+        <v>0.0002236489103919825</v>
       </c>
       <c r="H18" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2005507462162361</v>
+        <v>0.2699523346893602</v>
       </c>
       <c r="J18" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="K18" t="n">
-        <v>19.5</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="19">
@@ -1126,35 +1126,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.001991611778468329</v>
+        <v>0.002098015267490606</v>
       </c>
       <c r="D19" t="n">
         <v>16</v>
       </c>
       <c r="E19" t="n">
-        <v>0.001219912516060806</v>
+        <v>0.001007405018429065</v>
       </c>
       <c r="F19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0009180432739566702</v>
+        <v>0.0005098336434349981</v>
       </c>
       <c r="H19" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1414615172091742</v>
+        <v>0.1970921910273393</v>
       </c>
       <c r="J19" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="K19" t="n">
-        <v>20.75</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="20">
@@ -1163,35 +1163,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0009212352558826193</v>
+        <v>0.002304380354737607</v>
       </c>
       <c r="D20" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="E20" t="n">
-        <v>0.006942158564037165</v>
+        <v>0.001390887528241558</v>
       </c>
       <c r="F20" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0001508168303326674</v>
+        <v>0.001391474375185364</v>
       </c>
       <c r="H20" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2929207431772767</v>
+        <v>0.1162677246604455</v>
       </c>
       <c r="J20" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="K20" t="n">
-        <v>21.75</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -1200,35 +1200,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.001981650928159711</v>
+        <v>0.002070767412814615</v>
       </c>
       <c r="D21" t="n">
         <v>17</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0009771219945312779</v>
+        <v>0.001507996316891902</v>
       </c>
       <c r="F21" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0004154677420655006</v>
+        <v>0.0003862927800955651</v>
       </c>
       <c r="H21" t="n">
         <v>21</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2057084216457903</v>
+        <v>0.1497267572983745</v>
       </c>
       <c r="J21" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K21" t="n">
-        <v>21.75</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="22">
@@ -1237,35 +1237,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.001552321998005159</v>
+        <v>0.0005362323470610934</v>
       </c>
       <c r="D22" t="n">
+        <v>45</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.01125009811016086</v>
+      </c>
+      <c r="F22" t="n">
+        <v>9</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.0002159719791945736</v>
+      </c>
+      <c r="H22" t="n">
+        <v>28</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.164502853842124</v>
+      </c>
+      <c r="J22" t="n">
         <v>20</v>
       </c>
-      <c r="E22" t="n">
-        <v>0.001498391733627246</v>
-      </c>
-      <c r="F22" t="n">
-        <v>23</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.0002877783329671701</v>
-      </c>
-      <c r="H22" t="n">
-        <v>24</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.1543834728358466</v>
-      </c>
-      <c r="J22" t="n">
-        <v>27</v>
-      </c>
       <c r="K22" t="n">
-        <v>23.5</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="23">
@@ -1274,35 +1274,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0004894599256017411</v>
+        <v>0.001513857969896613</v>
       </c>
       <c r="D23" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="E23" t="n">
-        <v>0.01162416261146885</v>
+        <v>0.001187015199766706</v>
       </c>
       <c r="F23" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0001805774039261299</v>
+        <v>0.0005605871611487178</v>
       </c>
       <c r="H23" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2295057870794264</v>
+        <v>0.08158316046622227</v>
       </c>
       <c r="J23" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="K23" t="n">
-        <v>25.5</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="24">
@@ -1311,35 +1311,35 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.001294014005523748</v>
+        <v>0.0004363512307099286</v>
       </c>
       <c r="D24" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00197266459610386</v>
+        <v>0.003702193952719148</v>
       </c>
       <c r="F24" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0002552838898238874</v>
+        <v>0.0002414067048767232</v>
       </c>
       <c r="H24" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1077356270524956</v>
+        <v>0.1565064608513327</v>
       </c>
       <c r="J24" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="K24" t="n">
-        <v>26.5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25">
@@ -1348,35 +1348,35 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.001500850875527292</v>
+        <v>0.00150882294158987</v>
       </c>
       <c r="D25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E25" t="n">
-        <v>0.001175379803342451</v>
+        <v>0.0008062156514389453</v>
       </c>
       <c r="F25" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0005608043871210167</v>
+        <v>0.0002136535776239623</v>
       </c>
       <c r="H25" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0786731789563766</v>
+        <v>0.1298072021325805</v>
       </c>
       <c r="J25" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="K25" t="n">
-        <v>26.75</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="26">
@@ -1385,35 +1385,35 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0005572419416763432</v>
+        <v>0.0009522636881491705</v>
       </c>
       <c r="D26" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E26" t="n">
-        <v>0.003344487827892552</v>
+        <v>0.0006732612970896623</v>
       </c>
       <c r="F26" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0002351742058631312</v>
+        <v>0.0002883913801753901</v>
       </c>
       <c r="H26" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2086458278708552</v>
+        <v>0.1856278187338714</v>
       </c>
       <c r="J26" t="n">
         <v>19</v>
       </c>
       <c r="K26" t="n">
-        <v>26.75</v>
+        <v>27.75</v>
       </c>
     </row>
     <row r="27">
@@ -1422,35 +1422,35 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.00135649642937945</v>
+        <v>0.001515130979630339</v>
       </c>
       <c r="D27" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E27" t="n">
-        <v>0.001750847309758089</v>
+        <v>0.001520091012321579</v>
       </c>
       <c r="F27" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0001176696373987651</v>
+        <v>0.0002084405193223504</v>
       </c>
       <c r="H27" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1100992902083822</v>
+        <v>0.08252037876710538</v>
       </c>
       <c r="J27" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="K27" t="n">
-        <v>27.5</v>
+        <v>28.25</v>
       </c>
     </row>
     <row r="28">
@@ -1459,35 +1459,35 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.000938319440473086</v>
+        <v>0.001341357539773777</v>
       </c>
       <c r="D28" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0007509547148492584</v>
+        <v>0.002163976082863802</v>
       </c>
       <c r="F28" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0002798968058276729</v>
+        <v>0.0001532722460016789</v>
       </c>
       <c r="H28" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2014771250067651</v>
+        <v>0.08700539601290069</v>
       </c>
       <c r="J28" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="K28" t="n">
-        <v>27.5</v>
+        <v>28.75</v>
       </c>
     </row>
     <row r="29">
@@ -1496,35 +1496,35 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0002792881493865698</v>
+        <v>0.001057008366663852</v>
       </c>
       <c r="D29" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="E29" t="n">
-        <v>0.003273497853480334</v>
+        <v>0.001314113320092398</v>
       </c>
       <c r="F29" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0001752374778752785</v>
+        <v>-0.0001482043522033183</v>
       </c>
       <c r="H29" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2218485223188855</v>
+        <v>0.2445728104993856</v>
       </c>
       <c r="J29" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K29" t="n">
-        <v>27.5</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="30">
@@ -1533,35 +1533,35 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0009894049265533594</v>
+        <v>0.000377705185052018</v>
       </c>
       <c r="D30" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="E30" t="n">
-        <v>0.001478413259820412</v>
+        <v>0.003742085099515727</v>
       </c>
       <c r="F30" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.0001692251611651985</v>
+        <v>0.0001380282076580475</v>
       </c>
       <c r="H30" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2770263523620402</v>
+        <v>0.1528703251648047</v>
       </c>
       <c r="J30" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="K30" t="n">
-        <v>28.75</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="31">
@@ -1570,35 +1570,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.001167381262998629</v>
+        <v>0.001454772416828421</v>
       </c>
       <c r="D31" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0007743703271407873</v>
+        <v>0.0008447516085020126</v>
       </c>
       <c r="F31" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0004499382872577451</v>
+        <v>0.0003850525447718689</v>
       </c>
       <c r="H31" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1043761904758367</v>
+        <v>0.05192730137918167</v>
       </c>
       <c r="J31" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="K31" t="n">
-        <v>29.25</v>
+        <v>29.75</v>
       </c>
     </row>
     <row r="32">
@@ -1607,32 +1607,32 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.001464101489035468</v>
+        <v>0.000916513161122735</v>
       </c>
       <c r="D32" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0009065155138097038</v>
+        <v>0.0005541881264318136</v>
       </c>
       <c r="F32" t="n">
+        <v>45</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.0005800150786270831</v>
+      </c>
+      <c r="H32" t="n">
+        <v>14</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.1206952753538957</v>
+      </c>
+      <c r="J32" t="n">
         <v>30</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.0004012968385182836</v>
-      </c>
-      <c r="H32" t="n">
-        <v>22</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.04923555457813222</v>
-      </c>
-      <c r="J32" t="n">
-        <v>46</v>
       </c>
       <c r="K32" t="n">
         <v>30</v>
@@ -1644,32 +1644,32 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0008821176283592951</v>
+        <v>0.0008008563505270567</v>
       </c>
       <c r="D33" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0006382026353400602</v>
+        <v>0.00150957324182963</v>
       </c>
       <c r="F33" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0005440955245589185</v>
+        <v>-4.068710041975621e-05</v>
       </c>
       <c r="H33" t="n">
+        <v>47</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.1922289003748792</v>
+      </c>
+      <c r="J33" t="n">
         <v>17</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.1081584076742153</v>
-      </c>
-      <c r="J33" t="n">
-        <v>35</v>
       </c>
       <c r="K33" t="n">
         <v>31</v>
@@ -1681,35 +1681,35 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0008402422651569407</v>
+        <v>0.0008702463468832406</v>
       </c>
       <c r="D34" t="n">
         <v>33</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0009917240561012892</v>
+        <v>0.0006517038630517026</v>
       </c>
       <c r="F34" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="G34" t="n">
-        <v>-7.825080711113542e-05</v>
+        <v>0.0005449226424683595</v>
       </c>
       <c r="H34" t="n">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2207323944761521</v>
+        <v>0.1085555176625839</v>
       </c>
       <c r="J34" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="K34" t="n">
-        <v>32</v>
+        <v>31.25</v>
       </c>
     </row>
     <row r="35">
@@ -1718,35 +1718,35 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.001206122663108219</v>
+        <v>0.001138417740080813</v>
       </c>
       <c r="D35" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0008021534403865204</v>
+        <v>0.0007635461142474171</v>
       </c>
       <c r="F35" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0001532927007891982</v>
+        <v>0.0004150406246041682</v>
       </c>
       <c r="H35" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="I35" t="n">
-        <v>0.04556853675596395</v>
+        <v>0.02854832884313652</v>
       </c>
       <c r="J35" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K35" t="n">
-        <v>34.25</v>
+        <v>31.75</v>
       </c>
     </row>
     <row r="36">
@@ -1755,35 +1755,35 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0007367385516409864</v>
+        <v>0.001181690860545219</v>
       </c>
       <c r="D36" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0006669483459338774</v>
+        <v>0.0008055574988482754</v>
       </c>
       <c r="F36" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0002748763353596195</v>
+        <v>0.000173194622588313</v>
       </c>
       <c r="H36" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1111174670285382</v>
+        <v>0.05864846358770226</v>
       </c>
       <c r="J36" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="K36" t="n">
-        <v>34.75</v>
+        <v>33.25</v>
       </c>
     </row>
     <row r="37">
@@ -1792,35 +1792,35 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.0008132895954746782</v>
+        <v>0.0008376408666977825</v>
       </c>
       <c r="D37" t="n">
         <v>35</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0004655147573798946</v>
+        <v>0.0007696003419973514</v>
       </c>
       <c r="F37" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0002394229405603188</v>
+        <v>3.591056691276684e-05</v>
       </c>
       <c r="H37" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1321623732084736</v>
+        <v>0.1047114309968094</v>
       </c>
       <c r="J37" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="K37" t="n">
-        <v>35.5</v>
+        <v>36.25</v>
       </c>
     </row>
     <row r="38">
@@ -1833,31 +1833,31 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.0008340628663017962</v>
+        <v>0.0007810272148245259</v>
       </c>
       <c r="D38" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0006812942521092414</v>
+        <v>0.0008084613405911065</v>
       </c>
       <c r="F38" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G38" t="n">
-        <v>-9.313573361968696e-06</v>
+        <v>5.232347753792998e-05</v>
       </c>
       <c r="H38" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1193277577675893</v>
+        <v>0.09661113621317829</v>
       </c>
       <c r="J38" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="K38" t="n">
-        <v>36.25</v>
+        <v>36.75</v>
       </c>
     </row>
     <row r="39">
@@ -1866,35 +1866,35 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.001041035620556295</v>
+        <v>0.0007886382891927533</v>
       </c>
       <c r="D39" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0007083334940501524</v>
+        <v>0.000473285230597837</v>
       </c>
       <c r="F39" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="G39" t="n">
-        <v>-4.138304986744945e-05</v>
+        <v>0.0001203639689924652</v>
       </c>
       <c r="H39" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="I39" t="n">
-        <v>0.09267643000428505</v>
+        <v>0.1483923472772828</v>
       </c>
       <c r="J39" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="K39" t="n">
-        <v>37.25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40">
@@ -1903,35 +1903,35 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0007618075063473855</v>
+        <v>0.0007627874299100361</v>
       </c>
       <c r="D40" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0008945082626808689</v>
+        <v>0.0005991046630545348</v>
       </c>
       <c r="F40" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G40" t="n">
-        <v>-2.071002570162017e-05</v>
+        <v>0.0001509396737493618</v>
       </c>
       <c r="H40" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1083655886876653</v>
+        <v>0.1133977684273755</v>
       </c>
       <c r="J40" t="n">
         <v>34</v>
       </c>
       <c r="K40" t="n">
-        <v>37.5</v>
+        <v>37.75</v>
       </c>
     </row>
     <row r="41">
@@ -1944,31 +1944,31 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.0002618237302263946</v>
+        <v>0.0002408052716201546</v>
       </c>
       <c r="D41" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0006882203627795102</v>
+        <v>0.0007577331771416256</v>
       </c>
       <c r="F41" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0004804459140221207</v>
+        <v>0.0003921249062824983</v>
       </c>
       <c r="H41" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I41" t="n">
-        <v>0.01937812905933955</v>
+        <v>0.03575821798885048</v>
       </c>
       <c r="J41" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="K41" t="n">
-        <v>37.75</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42">
@@ -1977,35 +1977,35 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.000925923811968918</v>
+        <v>0.0008520993791585219</v>
       </c>
       <c r="D42" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0006748388105316527</v>
+        <v>0.0006693908937211823</v>
       </c>
       <c r="F42" t="n">
         <v>38</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.0002161354935916515</v>
+        <v>-3.912405583600398e-05</v>
       </c>
       <c r="H42" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1306732706335407</v>
+        <v>0.1105996765571509</v>
       </c>
       <c r="J42" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K42" t="n">
-        <v>37.75</v>
+        <v>38.25</v>
       </c>
     </row>
     <row r="43">
@@ -2018,31 +2018,31 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.0007882969006697734</v>
+        <v>0.0008210796582656164</v>
       </c>
       <c r="D43" t="n">
+        <v>36</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.0006060443852796497</v>
+      </c>
+      <c r="F43" t="n">
+        <v>41</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.0001046023916772998</v>
+      </c>
+      <c r="H43" t="n">
         <v>37</v>
       </c>
-      <c r="E43" t="n">
-        <v>0.0006364031463430259</v>
-      </c>
-      <c r="F43" t="n">
-        <v>42</v>
-      </c>
-      <c r="G43" t="n">
-        <v>7.232775912613399e-06</v>
-      </c>
-      <c r="H43" t="n">
+      <c r="I43" t="n">
+        <v>0.08866143799683179</v>
+      </c>
+      <c r="J43" t="n">
         <v>39</v>
       </c>
-      <c r="I43" t="n">
-        <v>0.1054561942143275</v>
-      </c>
-      <c r="J43" t="n">
-        <v>37</v>
-      </c>
       <c r="K43" t="n">
-        <v>38.75</v>
+        <v>38.25</v>
       </c>
     </row>
     <row r="44">
@@ -2051,35 +2051,35 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.0007059589823853784</v>
+        <v>0.001008763431202688</v>
       </c>
       <c r="D44" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0005553763241052613</v>
+        <v>0.000678486272436789</v>
       </c>
       <c r="F44" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G44" t="n">
-        <v>-7.894634759664232e-06</v>
+        <v>-5.288512301215853e-06</v>
       </c>
       <c r="H44" t="n">
         <v>42</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1709834645543058</v>
+        <v>0.04812936651390975</v>
       </c>
       <c r="J44" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="K44" t="n">
-        <v>39</v>
+        <v>38.25</v>
       </c>
     </row>
     <row r="45">
@@ -2088,35 +2088,35 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.0007531306730161371</v>
+        <v>0.0008945854852691556</v>
       </c>
       <c r="D45" t="n">
+        <v>32</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.0006152696280402195</v>
+      </c>
+      <c r="F45" t="n">
         <v>40</v>
       </c>
-      <c r="E45" t="n">
-        <v>0.0006159301639449595</v>
-      </c>
-      <c r="F45" t="n">
-        <v>43</v>
-      </c>
       <c r="G45" t="n">
-        <v>8.608242056333815e-05</v>
+        <v>-9.690869983747241e-05</v>
       </c>
       <c r="H45" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="I45" t="n">
-        <v>0.07692667533808129</v>
+        <v>0.1163760253988069</v>
       </c>
       <c r="J45" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="K45" t="n">
-        <v>40.75</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="46">
@@ -2125,35 +2125,35 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.0007837207757594585</v>
+        <v>0.0007010385881878948</v>
       </c>
       <c r="D46" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0005928112719898244</v>
+        <v>0.0005032273324813749</v>
       </c>
       <c r="F46" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G46" t="n">
-        <v>5.880174109118563e-06</v>
+        <v>-3.656031711283258e-05</v>
       </c>
       <c r="H46" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I46" t="n">
-        <v>0.08120877841116192</v>
+        <v>0.1465052836719529</v>
       </c>
       <c r="J46" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="K46" t="n">
-        <v>41</v>
+        <v>40.25</v>
       </c>
     </row>
     <row r="47">
@@ -2162,35 +2162,35 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.0007317274373024924</v>
+        <v>0.0007860913800429601</v>
       </c>
       <c r="D47" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0005004626058432648</v>
+        <v>0.0004350090070727275</v>
       </c>
       <c r="F47" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G47" t="n">
-        <v>-7.116172808396826e-06</v>
+        <v>-0.0001800433885696839</v>
       </c>
       <c r="H47" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="I47" t="n">
-        <v>0.05888879003301017</v>
+        <v>0.1250352999412252</v>
       </c>
       <c r="J47" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="K47" t="n">
-        <v>44</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="48">
@@ -2199,35 +2199,35 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.0007923317385663658</v>
+        <v>0.0006956934320526728</v>
       </c>
       <c r="D48" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0004500689253536527</v>
+        <v>0.0005465299748814707</v>
       </c>
       <c r="F48" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.0001452977838964698</v>
+        <v>-0.0003104006152105487</v>
       </c>
       <c r="H48" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I48" t="n">
-        <v>0.08181546115420524</v>
+        <v>0.1328690731507498</v>
       </c>
       <c r="J48" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="K48" t="n">
-        <v>44.25</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="49">
@@ -2236,35 +2236,35 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.000698768824287874</v>
+        <v>0.0007534038063470834</v>
       </c>
       <c r="D49" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0005266185931786459</v>
+        <v>0.0004753247668537219</v>
       </c>
       <c r="F49" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.0001891751093902494</v>
+        <v>-5.153761794967071e-05</v>
       </c>
       <c r="H49" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1047131403997339</v>
+        <v>0.07873252507831374</v>
       </c>
       <c r="J49" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="K49" t="n">
-        <v>45.25</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="50">
@@ -2277,31 +2277,31 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.0002578164434175566</v>
+        <v>0.0002750096584171437</v>
       </c>
       <c r="D50" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0006368282214652454</v>
+        <v>0.0005657369744712369</v>
       </c>
       <c r="F50" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G50" t="n">
-        <v>-1.365397194396101e-05</v>
+        <v>-1.62630332425584e-05</v>
       </c>
       <c r="H50" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I50" t="n">
-        <v>0.03360896424143878</v>
+        <v>0.0006290865065095019</v>
       </c>
       <c r="J50" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K50" t="n">
-        <v>45.5</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="51">
@@ -2314,28 +2314,28 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.000252087349012528</v>
+        <v>0.0002447343960500336</v>
       </c>
       <c r="D51" t="n">
+        <v>49</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.000252947062030458</v>
+      </c>
+      <c r="F51" t="n">
+        <v>52</v>
+      </c>
+      <c r="G51" t="n">
+        <v>6.202459662529858e-05</v>
+      </c>
+      <c r="H51" t="n">
+        <v>38</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.004620886376301314</v>
+      </c>
+      <c r="J51" t="n">
         <v>50</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0.000422029832543363</v>
-      </c>
-      <c r="F51" t="n">
-        <v>51</v>
-      </c>
-      <c r="G51" t="n">
-        <v>5.83587393926388e-05</v>
-      </c>
-      <c r="H51" t="n">
-        <v>37</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="n">
-        <v>51</v>
       </c>
       <c r="K51" t="n">
         <v>47.25</v>
@@ -2347,35 +2347,35 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>boiler_hardness</t>
+          <t>white_quality_moisture_1</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>7.594196436190925e-05</v>
+        <v>0.0002253675461468919</v>
       </c>
       <c r="D52" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0003046341338028613</v>
+        <v>0.0005806074086627955</v>
       </c>
       <c r="F52" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="G52" t="n">
-        <v>1.151763200234468e-05</v>
+        <v>-4.815492907939145e-05</v>
       </c>
       <c r="H52" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>0.01525040081228823</v>
       </c>
       <c r="J52" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K52" t="n">
-        <v>48.25</v>
+        <v>47.75</v>
       </c>
     </row>
     <row r="53">
@@ -2384,35 +2384,35 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.0002306281107116144</v>
+        <v>6.689902203393797e-05</v>
       </c>
       <c r="D53" t="n">
+        <v>52</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.0003763646132431509</v>
+      </c>
+      <c r="F53" t="n">
         <v>51</v>
       </c>
-      <c r="E53" t="n">
-        <v>0.0005700067466729396</v>
-      </c>
-      <c r="F53" t="n">
-        <v>45</v>
-      </c>
       <c r="G53" t="n">
-        <v>-6.309281372748332e-05</v>
+        <v>1.240458790952026e-05</v>
       </c>
       <c r="H53" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="I53" t="n">
-        <v>0.001182132265124647</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K53" t="n">
-        <v>48.5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="54">
@@ -2425,28 +2425,28 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3.206814500804728e-05</v>
+        <v>3.644830138190724e-05</v>
       </c>
       <c r="D54" t="n">
         <v>53</v>
       </c>
       <c r="E54" t="n">
-        <v>0.0001631776947128911</v>
+        <v>0.0001688619585249289</v>
       </c>
       <c r="F54" t="n">
         <v>53</v>
       </c>
       <c r="G54" t="n">
-        <v>-1.952708848380613e-05</v>
+        <v>-2.786894234019233e-05</v>
       </c>
       <c r="H54" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K54" t="n">
         <v>50.5</v>
@@ -2533,25 +2533,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3424292685068677</v>
+        <v>0.3509264667099231</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3181566287671884</v>
+        <v>0.3273009785562683</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3513435888306793</v>
+        <v>0.3598793571410549</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1.433803714952994</v>
+        <v>1.197596762489799</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
@@ -2570,25 +2570,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2383658985078753</v>
+        <v>0.2430083986073938</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.225245016388724</v>
+        <v>0.2341821975658129</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2759191102277692</v>
+        <v>0.2813470101326704</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>1.478740368189571</v>
+        <v>1.220162286626203</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -2603,35 +2603,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1331501555978941</v>
+        <v>0.1136888176080379</v>
       </c>
       <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.202284502935228</v>
+      </c>
+      <c r="F4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" t="n">
-        <v>0.08824288268883339</v>
-      </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
+        <v>0.03188475108235696</v>
+      </c>
+      <c r="H4" t="n">
         <v>4</v>
       </c>
-      <c r="G4" t="n">
-        <v>0.04750577254953946</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3</v>
-      </c>
       <c r="I4" t="n">
-        <v>0.952211235371005</v>
+        <v>0.6066707781972243</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
@@ -2640,35 +2640,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.1138727203369802</v>
+        <v>0.1216747028217113</v>
       </c>
       <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.08437781417749506</v>
+      </c>
+      <c r="F5" t="n">
         <v>4</v>
       </c>
-      <c r="E5" t="n">
-        <v>0.01315219499276279</v>
-      </c>
-      <c r="F5" t="n">
-        <v>7</v>
-      </c>
       <c r="G5" t="n">
-        <v>0.03309391811105006</v>
+        <v>0.0416466695227404</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8325968016518011</v>
+        <v>0.595591263334927</v>
       </c>
       <c r="J5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K5" t="n">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
@@ -2677,35 +2677,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0925122844997833</v>
+        <v>0.09170833013467054</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>0.211092557003509</v>
+        <v>0.01261148354771118</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02184809894965078</v>
+        <v>0.02157996931448751</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7924090046246004</v>
+        <v>0.6149920332849157</v>
       </c>
       <c r="J6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="7">
@@ -2718,25 +2718,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01182290118112469</v>
+        <v>0.01179176619992063</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01198557785307307</v>
+        <v>0.0125716311096866</v>
       </c>
       <c r="F7" t="n">
         <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01206627372144521</v>
+        <v>0.01200704749597893</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8088540008413529</v>
+        <v>0.6059710037229373</v>
       </c>
       <c r="J7" t="n">
         <v>7</v>
@@ -2755,25 +2755,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.007736709414784072</v>
+        <v>0.006322868406578661</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>0.007045092865230165</v>
+        <v>0.006797540172290032</v>
       </c>
       <c r="F8" t="n">
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004806630162510062</v>
+        <v>0.004525107807768736</v>
       </c>
       <c r="H8" t="n">
         <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>1.107645524286439</v>
+        <v>0.8723113670408211</v>
       </c>
       <c r="J8" t="n">
         <v>4</v>
@@ -2792,25 +2792,25 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.005629632018620954</v>
+        <v>0.005621442661865416</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0220825936988427</v>
+        <v>0.01914241201728629</v>
       </c>
       <c r="F9" t="n">
         <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.005294899910889639</v>
+        <v>0.005298272783865276</v>
       </c>
       <c r="H9" t="n">
         <v>7</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3373116316724039</v>
+        <v>0.2717957000954292</v>
       </c>
       <c r="J9" t="n">
         <v>10</v>
@@ -2829,25 +2829,25 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.002882842864139905</v>
+        <v>0.003044858379230276</v>
       </c>
       <c r="D10" t="n">
         <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0311312153900558</v>
+        <v>0.03151805388149846</v>
       </c>
       <c r="F10" t="n">
         <v>5</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0003276991593948125</v>
+        <v>0.000372539178951691</v>
       </c>
       <c r="H10" t="n">
         <v>23</v>
       </c>
       <c r="I10" t="n">
-        <v>1.296472196351193</v>
+        <v>1.032026958462696</v>
       </c>
       <c r="J10" t="n">
         <v>3</v>
@@ -2866,31 +2866,31 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.003806728156947169</v>
+        <v>0.003738895770907981</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00631140689285436</v>
+        <v>0.006383871055968616</v>
       </c>
       <c r="F11" t="n">
+        <v>11</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.001006899723146704</v>
+      </c>
+      <c r="H11" t="n">
+        <v>13</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.2636575744571474</v>
+      </c>
+      <c r="J11" t="n">
         <v>12</v>
       </c>
-      <c r="G11" t="n">
-        <v>0.001018282359692535</v>
-      </c>
-      <c r="H11" t="n">
-        <v>12</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.2731534068695995</v>
-      </c>
-      <c r="J11" t="n">
-        <v>13</v>
-      </c>
       <c r="K11" t="n">
-        <v>11.75</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="12">
@@ -2899,35 +2899,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.004000760960342559</v>
+        <v>0.002699248342943198</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>0.003036778439689963</v>
+        <v>0.001671672701943038</v>
       </c>
       <c r="F12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0002770821278502811</v>
+        <v>0.001066831892333842</v>
       </c>
       <c r="H12" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6333921093174082</v>
+        <v>0.1883237605390065</v>
       </c>
       <c r="J12" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="K12" t="n">
-        <v>14.75</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="13">
@@ -2936,32 +2936,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.002277176808020272</v>
+        <v>0.001648145579726441</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E13" t="n">
-        <v>0.001516273235907318</v>
+        <v>0.002453077075937192</v>
       </c>
       <c r="F13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G13" t="n">
-        <v>0.001357700694164798</v>
+        <v>0.0005687225825382169</v>
       </c>
       <c r="H13" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2052719691187259</v>
+        <v>0.2125263033038287</v>
       </c>
       <c r="J13" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="K13" t="n">
         <v>16.25</v>
@@ -2973,32 +2973,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.001725349766564107</v>
+        <v>0.00401375600794517</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>0.00250354382601708</v>
+        <v>0.002790204142766983</v>
       </c>
       <c r="F14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0006983973131602927</v>
+        <v>0.000207213615126034</v>
       </c>
       <c r="H14" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="I14" t="n">
-        <v>0.229753298447156</v>
+        <v>0.4961557840490896</v>
       </c>
       <c r="J14" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K14" t="n">
         <v>16.25</v>
@@ -3010,32 +3010,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.002254276794859032</v>
+        <v>0.002245715045750216</v>
       </c>
       <c r="D15" t="n">
         <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>0.002744408089620847</v>
+        <v>0.00152358979170372</v>
       </c>
       <c r="F15" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001072473149984199</v>
+        <v>0.001319066452785034</v>
       </c>
       <c r="H15" t="n">
         <v>10</v>
       </c>
       <c r="I15" t="n">
-        <v>0.159505819969981</v>
+        <v>0.1581573980849016</v>
       </c>
       <c r="J15" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="K15" t="n">
         <v>16.5</v>
@@ -3047,35 +3047,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.002670633776108256</v>
+        <v>0.00217139327705321</v>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E16" t="n">
-        <v>0.001673063735473772</v>
+        <v>0.002930754602353963</v>
       </c>
       <c r="F16" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G16" t="n">
-        <v>0.00105945874690988</v>
+        <v>0.001145782448783261</v>
       </c>
       <c r="H16" t="n">
         <v>11</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1776140935255817</v>
+        <v>0.1185070533412098</v>
       </c>
       <c r="J16" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="K16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
@@ -3088,31 +3088,31 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.001776900232282438</v>
+        <v>0.00172816822723828</v>
       </c>
       <c r="D17" t="n">
         <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>0.001745766935296882</v>
+        <v>0.001615668932758181</v>
       </c>
       <c r="F17" t="n">
         <v>20</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0004278258866586282</v>
+        <v>0.0003341763919278318</v>
       </c>
       <c r="H17" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2617903996465323</v>
+        <v>0.2099184335506039</v>
       </c>
       <c r="J17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>18</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="18">
@@ -3121,35 +3121,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.002196740586494563</v>
+        <v>0.001120522902745008</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E18" t="n">
-        <v>0.001460034493748368</v>
+        <v>0.004567903659766977</v>
       </c>
       <c r="F18" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0005838627476783432</v>
+        <v>0.0002236489103919825</v>
       </c>
       <c r="H18" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2005507462162361</v>
+        <v>0.2699523346893602</v>
       </c>
       <c r="J18" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="K18" t="n">
-        <v>19.5</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="19">
@@ -3158,35 +3158,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.001991611778468329</v>
+        <v>0.002098015267490606</v>
       </c>
       <c r="D19" t="n">
         <v>16</v>
       </c>
       <c r="E19" t="n">
-        <v>0.001219912516060806</v>
+        <v>0.001007405018429065</v>
       </c>
       <c r="F19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0009180432739566702</v>
+        <v>0.0005098336434349981</v>
       </c>
       <c r="H19" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1414615172091742</v>
+        <v>0.1970921910273393</v>
       </c>
       <c r="J19" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="K19" t="n">
-        <v>20.75</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="20">
@@ -3195,35 +3195,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0009212352558826193</v>
+        <v>0.002304380354737607</v>
       </c>
       <c r="D20" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="E20" t="n">
-        <v>0.006942158564037165</v>
+        <v>0.001390887528241558</v>
       </c>
       <c r="F20" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0001508168303326674</v>
+        <v>0.001391474375185364</v>
       </c>
       <c r="H20" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2929207431772767</v>
+        <v>0.1162677246604455</v>
       </c>
       <c r="J20" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="K20" t="n">
-        <v>21.75</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -3232,35 +3232,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.001981650928159711</v>
+        <v>0.002070767412814615</v>
       </c>
       <c r="D21" t="n">
         <v>17</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0009771219945312779</v>
+        <v>0.001507996316891902</v>
       </c>
       <c r="F21" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0004154677420655006</v>
+        <v>0.0003862927800955651</v>
       </c>
       <c r="H21" t="n">
         <v>21</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2057084216457903</v>
+        <v>0.1497267572983745</v>
       </c>
       <c r="J21" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K21" t="n">
-        <v>21.75</v>
+        <v>21.5</v>
       </c>
     </row>
   </sheetData>
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3424292685068677</v>
+        <v>0.3509264667099231</v>
       </c>
     </row>
     <row r="3">
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2383658985078753</v>
+        <v>0.2430083986073938</v>
       </c>
     </row>
     <row r="4">
@@ -3330,7 +3330,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1331501555978941</v>
+        <v>0.1216747028217113</v>
       </c>
     </row>
     <row r="5">
@@ -3339,11 +3339,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.1138727203369802</v>
+        <v>0.1136888176080379</v>
       </c>
     </row>
     <row r="6">
@@ -3352,11 +3352,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0925122844997833</v>
+        <v>0.09170833013467054</v>
       </c>
     </row>
     <row r="7">
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01182290118112469</v>
+        <v>0.01179176619992063</v>
       </c>
     </row>
     <row r="8">
@@ -3382,7 +3382,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.007736709414784072</v>
+        <v>0.006322868406578661</v>
       </c>
     </row>
     <row r="9">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.005629632018620954</v>
+        <v>0.005621442661865416</v>
       </c>
     </row>
     <row r="10">
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.004000760960342559</v>
+        <v>0.00401375600794517</v>
       </c>
     </row>
     <row r="11">
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.003806728156947169</v>
+        <v>0.003738895770907981</v>
       </c>
     </row>
     <row r="12">
@@ -3434,7 +3434,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.002882842864139905</v>
+        <v>0.003044858379230276</v>
       </c>
     </row>
     <row r="13">
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.002670633776108256</v>
+        <v>0.002699248342943198</v>
       </c>
     </row>
     <row r="14">
@@ -3456,11 +3456,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.002277176808020272</v>
+        <v>0.002304380354737607</v>
       </c>
     </row>
     <row r="15">
@@ -3469,11 +3469,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.002254276794859032</v>
+        <v>0.002245715045750216</v>
       </c>
     </row>
     <row r="16">
@@ -3482,11 +3482,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.002196740586494563</v>
+        <v>0.00217139327705321</v>
       </c>
     </row>
     <row r="17">
@@ -3495,11 +3495,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.001991611778468329</v>
+        <v>0.002098015267490606</v>
       </c>
     </row>
     <row r="18">
@@ -3508,11 +3508,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.001981650928159711</v>
+        <v>0.002070767412814615</v>
       </c>
     </row>
     <row r="19">
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.001776900232282438</v>
+        <v>0.00172816822723828</v>
       </c>
     </row>
     <row r="20">
@@ -3538,7 +3538,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.001725349766564107</v>
+        <v>0.001648145579726441</v>
       </c>
     </row>
     <row r="21">
@@ -3547,11 +3547,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.001552321998005159</v>
+        <v>0.001515130979630339</v>
       </c>
     </row>
     <row r="22">
@@ -3564,7 +3564,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.001500850875527292</v>
+        <v>0.001513857969896613</v>
       </c>
     </row>
     <row r="23">
@@ -3573,11 +3573,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.001464101489035468</v>
+        <v>0.00150882294158987</v>
       </c>
     </row>
     <row r="24">
@@ -3586,11 +3586,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.00135649642937945</v>
+        <v>0.001454772416828421</v>
       </c>
     </row>
     <row r="25">
@@ -3599,11 +3599,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.001294014005523748</v>
+        <v>0.001341357539773777</v>
       </c>
     </row>
     <row r="26">
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.001206122663108219</v>
+        <v>0.001181690860545219</v>
       </c>
     </row>
     <row r="27">
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.001167381262998629</v>
+        <v>0.001138417740080813</v>
       </c>
     </row>
     <row r="28">
@@ -3638,11 +3638,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.001041035620556295</v>
+        <v>0.001120522902745008</v>
       </c>
     </row>
     <row r="29">
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0009894049265533594</v>
+        <v>0.001057008366663852</v>
       </c>
     </row>
     <row r="30">
@@ -3664,11 +3664,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.000938319440473086</v>
+        <v>0.001008763431202688</v>
       </c>
     </row>
     <row r="31">
@@ -3677,11 +3677,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.000925923811968918</v>
+        <v>0.0009522636881491705</v>
       </c>
     </row>
     <row r="32">
@@ -3690,11 +3690,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0009212352558826193</v>
+        <v>0.000916513161122735</v>
       </c>
     </row>
     <row r="33">
@@ -3703,11 +3703,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0008821176283592951</v>
+        <v>0.0008945854852691556</v>
       </c>
     </row>
     <row r="34">
@@ -3716,11 +3716,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0008402422651569407</v>
+        <v>0.0008702463468832406</v>
       </c>
     </row>
     <row r="35">
@@ -3729,11 +3729,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0008340628663017962</v>
+        <v>0.0008520993791585219</v>
       </c>
     </row>
     <row r="36">
@@ -3742,11 +3742,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0008132895954746782</v>
+        <v>0.0008376408666977825</v>
       </c>
     </row>
     <row r="37">
@@ -3755,11 +3755,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.0007923317385663658</v>
+        <v>0.0008210796582656164</v>
       </c>
     </row>
     <row r="38">
@@ -3768,11 +3768,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.0007882969006697734</v>
+        <v>0.0008008563505270567</v>
       </c>
     </row>
     <row r="39">
@@ -3781,11 +3781,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.0007837207757594585</v>
+        <v>0.0007886382891927533</v>
       </c>
     </row>
     <row r="40">
@@ -3794,11 +3794,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0007618075063473855</v>
+        <v>0.0007860913800429601</v>
       </c>
     </row>
     <row r="41">
@@ -3807,11 +3807,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.0007531306730161371</v>
+        <v>0.0007810272148245259</v>
       </c>
     </row>
     <row r="42">
@@ -3820,11 +3820,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.0007367385516409864</v>
+        <v>0.0007627874299100361</v>
       </c>
     </row>
     <row r="43">
@@ -3837,7 +3837,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.0007317274373024924</v>
+        <v>0.0007534038063470834</v>
       </c>
     </row>
     <row r="44">
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.0007059589823853784</v>
+        <v>0.0007010385881878948</v>
       </c>
     </row>
     <row r="45">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.000698768824287874</v>
+        <v>0.0006956934320526728</v>
       </c>
     </row>
     <row r="46">
@@ -3872,11 +3872,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.0005572419416763432</v>
+        <v>0.0005362323470610934</v>
       </c>
     </row>
     <row r="47">
@@ -3885,11 +3885,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.0004894599256017411</v>
+        <v>0.0004363512307099286</v>
       </c>
     </row>
     <row r="48">
@@ -3902,7 +3902,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.0002792881493865698</v>
+        <v>0.000377705185052018</v>
       </c>
     </row>
     <row r="49">
@@ -3911,11 +3911,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>white_quality_moisture_2</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.0002618237302263946</v>
+        <v>0.0002750096584171437</v>
       </c>
     </row>
     <row r="50">
@@ -3924,11 +3924,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>white_quality_moisture_2</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.0002578164434175566</v>
+        <v>0.0002447343960500336</v>
       </c>
     </row>
     <row r="51">
@@ -3937,11 +3937,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.000252087349012528</v>
+        <v>0.0002408052716201546</v>
       </c>
     </row>
     <row r="52">
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.0002306281107116144</v>
+        <v>0.0002253675461468919</v>
       </c>
     </row>
     <row r="53">
@@ -3967,7 +3967,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>7.594196436190925e-05</v>
+        <v>6.689902203393797e-05</v>
       </c>
     </row>
     <row r="54">
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3.206814500804728e-05</v>
+        <v>3.644830138190724e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4024,7 +4024,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3181566287671884</v>
+        <v>0.3273009785562683</v>
       </c>
     </row>
     <row r="3">
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.225245016388724</v>
+        <v>0.2341821975658129</v>
       </c>
     </row>
     <row r="4">
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.211092557003509</v>
+        <v>0.202284502935228</v>
       </c>
     </row>
     <row r="5">
@@ -4063,7 +4063,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.08824288268883339</v>
+        <v>0.08437781417749506</v>
       </c>
     </row>
     <row r="6">
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0311312153900558</v>
+        <v>0.03151805388149846</v>
       </c>
     </row>
     <row r="7">
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0220825936988427</v>
+        <v>0.01914241201728629</v>
       </c>
     </row>
     <row r="8">
@@ -4102,7 +4102,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.01315219499276279</v>
+        <v>0.01261148354771118</v>
       </c>
     </row>
     <row r="9">
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.01198557785307307</v>
+        <v>0.0125716311096866</v>
       </c>
     </row>
     <row r="10">
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.01162416261146885</v>
+        <v>0.01125009811016086</v>
       </c>
     </row>
     <row r="11">
@@ -4141,7 +4141,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.007045092865230165</v>
+        <v>0.006797540172290032</v>
       </c>
     </row>
     <row r="12">
@@ -4150,11 +4150,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>white_quality_solution_color_2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.006942158564037165</v>
+        <v>0.006383871055968616</v>
       </c>
     </row>
     <row r="13">
@@ -4163,11 +4163,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.00631140689285436</v>
+        <v>0.004567903659766977</v>
       </c>
     </row>
     <row r="14">
@@ -4176,11 +4176,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.003344487827892552</v>
+        <v>0.003742085099515727</v>
       </c>
     </row>
     <row r="15">
@@ -4189,11 +4189,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.003273497853480334</v>
+        <v>0.003702193952719148</v>
       </c>
     </row>
     <row r="16">
@@ -4202,11 +4202,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.003036778439689963</v>
+        <v>0.002930754602353963</v>
       </c>
     </row>
     <row r="17">
@@ -4215,11 +4215,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.002744408089620847</v>
+        <v>0.002790204142766983</v>
       </c>
     </row>
     <row r="18">
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.00250354382601708</v>
+        <v>0.002453077075937192</v>
       </c>
     </row>
     <row r="19">
@@ -4241,11 +4241,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.00197266459610386</v>
+        <v>0.002163976082863802</v>
       </c>
     </row>
     <row r="20">
@@ -4254,11 +4254,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.001750847309758089</v>
+        <v>0.001671672701943038</v>
       </c>
     </row>
     <row r="21">
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.001745766935296882</v>
+        <v>0.001615668932758181</v>
       </c>
     </row>
     <row r="22">
@@ -4280,11 +4280,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.001673063735473772</v>
+        <v>0.00152358979170372</v>
       </c>
     </row>
     <row r="23">
@@ -4293,11 +4293,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.001516273235907318</v>
+        <v>0.001520091012321579</v>
       </c>
     </row>
     <row r="24">
@@ -4306,11 +4306,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.001498391733627246</v>
+        <v>0.00150957324182963</v>
       </c>
     </row>
     <row r="25">
@@ -4319,11 +4319,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.001478413259820412</v>
+        <v>0.001507996316891902</v>
       </c>
     </row>
     <row r="26">
@@ -4332,11 +4332,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.001460034493748368</v>
+        <v>0.001390887528241558</v>
       </c>
     </row>
     <row r="27">
@@ -4345,11 +4345,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.001219912516060806</v>
+        <v>0.001314113320092398</v>
       </c>
     </row>
     <row r="28">
@@ -4362,7 +4362,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.001175379803342451</v>
+        <v>0.001187015199766706</v>
       </c>
     </row>
     <row r="29">
@@ -4371,11 +4371,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0009917240561012892</v>
+        <v>0.001007405018429065</v>
       </c>
     </row>
     <row r="30">
@@ -4384,11 +4384,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0009771219945312779</v>
+        <v>0.0008447516085020126</v>
       </c>
     </row>
     <row r="31">
@@ -4397,11 +4397,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0009065155138097038</v>
+        <v>0.0008084613405911065</v>
       </c>
     </row>
     <row r="32">
@@ -4410,11 +4410,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0008945082626808689</v>
+        <v>0.0008062156514389453</v>
       </c>
     </row>
     <row r="33">
@@ -4427,7 +4427,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0008021534403865204</v>
+        <v>0.0008055574988482754</v>
       </c>
     </row>
     <row r="34">
@@ -4436,11 +4436,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0007743703271407873</v>
+        <v>0.0007696003419973514</v>
       </c>
     </row>
     <row r="35">
@@ -4449,11 +4449,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0007509547148492584</v>
+        <v>0.0007635461142474171</v>
       </c>
     </row>
     <row r="36">
@@ -4462,11 +4462,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0007083334940501524</v>
+        <v>0.0007577331771416256</v>
       </c>
     </row>
     <row r="37">
@@ -4475,11 +4475,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.0006882203627795102</v>
+        <v>0.000678486272436789</v>
       </c>
     </row>
     <row r="38">
@@ -4488,11 +4488,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.0006812942521092414</v>
+        <v>0.0006732612970896623</v>
       </c>
     </row>
     <row r="39">
@@ -4501,11 +4501,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.0006748388105316527</v>
+        <v>0.0006693908937211823</v>
       </c>
     </row>
     <row r="40">
@@ -4514,11 +4514,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0006669483459338774</v>
+        <v>0.0006517038630517026</v>
       </c>
     </row>
     <row r="41">
@@ -4527,11 +4527,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.0006382026353400602</v>
+        <v>0.0006152696280402195</v>
       </c>
     </row>
     <row r="42">
@@ -4540,11 +4540,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>white_quality_moisture_2</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.0006368282214652454</v>
+        <v>0.0006060443852796497</v>
       </c>
     </row>
     <row r="43">
@@ -4553,11 +4553,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.0006364031463430259</v>
+        <v>0.0005991046630545348</v>
       </c>
     </row>
     <row r="44">
@@ -4566,11 +4566,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>white_quality_moisture_1</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.0006159301639449595</v>
+        <v>0.0005806074086627955</v>
       </c>
     </row>
     <row r="45">
@@ -4579,11 +4579,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>white_quality_moisture_2</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.0005928112719898244</v>
+        <v>0.0005657369744712369</v>
       </c>
     </row>
     <row r="46">
@@ -4592,11 +4592,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.0005700067466729396</v>
+        <v>0.0005541881264318136</v>
       </c>
     </row>
     <row r="47">
@@ -4605,11 +4605,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.0005553763241052613</v>
+        <v>0.0005465299748814707</v>
       </c>
     </row>
     <row r="48">
@@ -4618,11 +4618,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.0005266185931786459</v>
+        <v>0.0005032273324813749</v>
       </c>
     </row>
     <row r="49">
@@ -4635,7 +4635,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.0005004626058432648</v>
+        <v>0.0004753247668537219</v>
       </c>
     </row>
     <row r="50">
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.0004655147573798946</v>
+        <v>0.000473285230597837</v>
       </c>
     </row>
     <row r="51">
@@ -4661,7 +4661,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.0004500689253536527</v>
+        <v>0.0004350090070727275</v>
       </c>
     </row>
     <row r="52">
@@ -4670,11 +4670,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.000422029832543363</v>
+        <v>0.0003763646132431509</v>
       </c>
     </row>
     <row r="53">
@@ -4683,11 +4683,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>boiler_hardness</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.0003046341338028613</v>
+        <v>0.000252947062030458</v>
       </c>
     </row>
     <row r="54">
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.0001631776947128911</v>
+        <v>0.0001688619585249289</v>
       </c>
     </row>
   </sheetData>
@@ -4749,10 +4749,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3513435888306793</v>
+        <v>0.3598793571410549</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03053200576697649</v>
+        <v>0.03041445669921597</v>
       </c>
     </row>
     <row r="3">
@@ -4765,10 +4765,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2759191102277692</v>
+        <v>0.2813470101326704</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01461439317224815</v>
+        <v>0.01524823488966109</v>
       </c>
     </row>
     <row r="4">
@@ -4781,10 +4781,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.04750577254953946</v>
+        <v>0.0416466695227404</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008186002325973791</v>
+        <v>0.007157943070708389</v>
       </c>
     </row>
     <row r="5">
@@ -4793,14 +4793,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03309391811105006</v>
+        <v>0.03188475108235696</v>
       </c>
       <c r="D5" t="n">
-        <v>0.007263898883167018</v>
+        <v>0.007600139502350577</v>
       </c>
     </row>
     <row r="6">
@@ -4809,14 +4809,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.02184809894965078</v>
+        <v>0.02157996931448751</v>
       </c>
       <c r="D6" t="n">
-        <v>0.005905270644834206</v>
+        <v>0.005562400201518326</v>
       </c>
     </row>
     <row r="7">
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01206627372144521</v>
+        <v>0.01200704749597893</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001336265620391592</v>
+        <v>0.001327194475607478</v>
       </c>
     </row>
     <row r="8">
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.005294899910889639</v>
+        <v>0.005298272783865276</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0003976234763442932</v>
+        <v>0.0004053558587745954</v>
       </c>
     </row>
     <row r="9">
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.004806630162510062</v>
+        <v>0.004525107807768736</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0004636080255238202</v>
+        <v>0.0004560717475661853</v>
       </c>
     </row>
     <row r="10">
@@ -4873,14 +4873,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.001357700694164798</v>
+        <v>0.001391474375185364</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0004967944824143995</v>
+        <v>0.0001591010685670372</v>
       </c>
     </row>
     <row r="11">
@@ -4889,14 +4889,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.001072473149984199</v>
+        <v>0.001319066452785034</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0002321465188277932</v>
+        <v>0.0005414674602246542</v>
       </c>
     </row>
     <row r="12">
@@ -4905,14 +4905,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.00105945874690988</v>
+        <v>0.001145782448783261</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0005144413411651807</v>
+        <v>0.0002168212391677222</v>
       </c>
     </row>
     <row r="13">
@@ -4921,14 +4921,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001018282359692535</v>
+        <v>0.001066831892333842</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0003782462059274685</v>
+        <v>0.0005048358098471679</v>
       </c>
     </row>
     <row r="14">
@@ -4937,14 +4937,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>white_quality_solution_color_2</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0009180432739566702</v>
+        <v>0.001006899723146704</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0001384213864644027</v>
+        <v>0.000355095111806079</v>
       </c>
     </row>
     <row r="15">
@@ -4953,14 +4953,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0006983973131602927</v>
+        <v>0.0005800150786270831</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0001653996214387366</v>
+        <v>0.0001644582744382722</v>
       </c>
     </row>
     <row r="16">
@@ -4969,14 +4969,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0005838627476783432</v>
+        <v>0.0005687225825382169</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0003567005451877216</v>
+        <v>0.0001283287493608244</v>
       </c>
     </row>
     <row r="17">
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0005608043871210167</v>
+        <v>0.0005605871611487178</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0001418110680083992</v>
+        <v>0.0001436236424471595</v>
       </c>
     </row>
     <row r="18">
@@ -5005,10 +5005,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0005440955245589185</v>
+        <v>0.0005449226424683595</v>
       </c>
       <c r="D18" t="n">
-        <v>0.000146711516104157</v>
+        <v>0.0001626794654960903</v>
       </c>
     </row>
     <row r="19">
@@ -5017,14 +5017,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0004804459140221207</v>
+        <v>0.0005098336434349981</v>
       </c>
       <c r="D19" t="n">
-        <v>4.812864682349979e-05</v>
+        <v>0.0001447292561736676</v>
       </c>
     </row>
     <row r="20">
@@ -5037,10 +5037,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0004499382872577451</v>
+        <v>0.0004150406246041682</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0001279895971210836</v>
+        <v>0.0001287384004968305</v>
       </c>
     </row>
     <row r="21">
@@ -5049,14 +5049,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0004278258866586282</v>
+        <v>0.0003921249062824983</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0001641164382686324</v>
+        <v>4.256663542581737e-05</v>
       </c>
     </row>
     <row r="22">
@@ -5065,14 +5065,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0004154677420655006</v>
+        <v>0.0003862927800955651</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0001461258018780851</v>
+        <v>0.0003116897519392526</v>
       </c>
     </row>
     <row r="23">
@@ -5085,10 +5085,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0004012968385182836</v>
+        <v>0.0003850525447718689</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0001170437715153925</v>
+        <v>7.169897241367991e-05</v>
       </c>
     </row>
     <row r="24">
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0003276991593948125</v>
+        <v>0.000372539178951691</v>
       </c>
       <c r="D24" t="n">
-        <v>4.135176520778005e-05</v>
+        <v>4.731016319563441e-05</v>
       </c>
     </row>
     <row r="25">
@@ -5113,14 +5113,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0002877783329671701</v>
+        <v>0.0003341763919278318</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0002094539787748468</v>
+        <v>0.0001281307850932167</v>
       </c>
     </row>
     <row r="26">
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0002798968058276729</v>
+        <v>0.0002883913801753901</v>
       </c>
       <c r="D26" t="n">
-        <v>5.190638448151934e-05</v>
+        <v>6.261256938241649e-05</v>
       </c>
     </row>
     <row r="27">
@@ -5145,14 +5145,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0002770821278502811</v>
+        <v>0.0002414067048767232</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0007012010899998666</v>
+        <v>6.713344377306386e-05</v>
       </c>
     </row>
     <row r="28">
@@ -5161,14 +5161,14 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0002748763353596195</v>
+        <v>0.0002236489103919825</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0001123196158222657</v>
+        <v>0.0001163251040838036</v>
       </c>
     </row>
     <row r="29">
@@ -5177,14 +5177,14 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0002552838898238874</v>
+        <v>0.0002159719791945736</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0001152903528818913</v>
+        <v>6.71142060242558e-05</v>
       </c>
     </row>
     <row r="30">
@@ -5193,14 +5193,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0002394229405603188</v>
+        <v>0.0002136535776239623</v>
       </c>
       <c r="D30" t="n">
-        <v>8.183416016965158e-05</v>
+        <v>0.0001950049485494441</v>
       </c>
     </row>
     <row r="31">
@@ -5209,14 +5209,14 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0002351742058631312</v>
+        <v>0.0002084405193223504</v>
       </c>
       <c r="D31" t="n">
-        <v>9.009586389459285e-05</v>
+        <v>0.0001183540964854371</v>
       </c>
     </row>
     <row r="32">
@@ -5225,14 +5225,14 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0001805774039261299</v>
+        <v>0.000207213615126034</v>
       </c>
       <c r="D32" t="n">
-        <v>4.863074663440316e-05</v>
+        <v>0.0007383849116093184</v>
       </c>
     </row>
     <row r="33">
@@ -5241,14 +5241,14 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0001752374778752785</v>
+        <v>0.000173194622588313</v>
       </c>
       <c r="D33" t="n">
-        <v>5.471745656656576e-05</v>
+        <v>0.0001044216602020246</v>
       </c>
     </row>
     <row r="34">
@@ -5257,14 +5257,14 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0001532927007891982</v>
+        <v>0.0001532722460016789</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0001136504334027028</v>
+        <v>0.0001221877296913883</v>
       </c>
     </row>
     <row r="35">
@@ -5273,14 +5273,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0001508168303326674</v>
+        <v>0.0001509396737493618</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0001196766785764144</v>
+        <v>7.09691553413078e-05</v>
       </c>
     </row>
     <row r="36">
@@ -5289,14 +5289,14 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0001176696373987651</v>
+        <v>0.0001380282076580475</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0001041517007083905</v>
+        <v>7.290849629907503e-05</v>
       </c>
     </row>
     <row r="37">
@@ -5305,14 +5305,14 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>8.608242056333815e-05</v>
+        <v>0.0001203639689924652</v>
       </c>
       <c r="D37" t="n">
-        <v>6.207840810291382e-05</v>
+        <v>8.059860407535291e-05</v>
       </c>
     </row>
     <row r="38">
@@ -5321,14 +5321,14 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>5.83587393926388e-05</v>
+        <v>0.0001046023916772998</v>
       </c>
       <c r="D38" t="n">
-        <v>3.338408634509426e-05</v>
+        <v>0.0001087672521161095</v>
       </c>
     </row>
     <row r="39">
@@ -5337,14 +5337,14 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>boiler_hardness</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1.151763200234468e-05</v>
+        <v>6.202459662529858e-05</v>
       </c>
       <c r="D39" t="n">
-        <v>7.348041309172165e-06</v>
+        <v>2.874274511499105e-05</v>
       </c>
     </row>
     <row r="40">
@@ -5353,14 +5353,14 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>7.232775912613399e-06</v>
+        <v>5.232347753792998e-05</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0001037484509615598</v>
+        <v>0.0001120303628327273</v>
       </c>
     </row>
     <row r="41">
@@ -5369,14 +5369,14 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5.880174109118563e-06</v>
+        <v>3.591056691276684e-05</v>
       </c>
       <c r="D41" t="n">
-        <v>3.595079266976442e-05</v>
+        <v>0.0001434684123433035</v>
       </c>
     </row>
     <row r="42">
@@ -5385,14 +5385,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-7.116172808396826e-06</v>
+        <v>1.240458790952026e-05</v>
       </c>
       <c r="D42" t="n">
-        <v>8.164737659405992e-05</v>
+        <v>4.605546486457779e-06</v>
       </c>
     </row>
     <row r="43">
@@ -5401,14 +5401,14 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-7.894634759664232e-06</v>
+        <v>-5.288512301215853e-06</v>
       </c>
       <c r="D43" t="n">
-        <v>7.923636820170663e-05</v>
+        <v>8.119598861249887e-05</v>
       </c>
     </row>
     <row r="44">
@@ -5417,14 +5417,14 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>white_quality_moisture_2</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-9.313573361968696e-06</v>
+        <v>-1.62630332425584e-05</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0001416806697803597</v>
+        <v>3.726211982360197e-05</v>
       </c>
     </row>
     <row r="45">
@@ -5433,14 +5433,14 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>white_quality_moisture_2</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-1.365397194396101e-05</v>
+        <v>-2.786894234019233e-05</v>
       </c>
       <c r="D45" t="n">
-        <v>2.896835159471466e-05</v>
+        <v>1.777214842172435e-05</v>
       </c>
     </row>
     <row r="46">
@@ -5449,14 +5449,14 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>shift_name</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-1.952708848380613e-05</v>
+        <v>-3.656031711283258e-05</v>
       </c>
       <c r="D46" t="n">
-        <v>1.483805947810876e-05</v>
+        <v>4.499235083519608e-05</v>
       </c>
     </row>
     <row r="47">
@@ -5465,14 +5465,14 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-2.071002570162017e-05</v>
+        <v>-3.912405583600398e-05</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0001045309366459781</v>
+        <v>6.675099540998198e-05</v>
       </c>
     </row>
     <row r="48">
@@ -5481,14 +5481,14 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-4.138304986744945e-05</v>
+        <v>-4.068710041975621e-05</v>
       </c>
       <c r="D48" t="n">
-        <v>9.150149094252794e-05</v>
+        <v>0.0001025101141063102</v>
       </c>
     </row>
     <row r="49">
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-6.309281372748332e-05</v>
+        <v>-4.815492907939145e-05</v>
       </c>
       <c r="D49" t="n">
-        <v>2.35450978663369e-05</v>
+        <v>2.803255978632049e-05</v>
       </c>
     </row>
     <row r="50">
@@ -5513,14 +5513,14 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-7.825080711113542e-05</v>
+        <v>-5.153761794967071e-05</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0001119340775256447</v>
+        <v>8.442209553245845e-05</v>
       </c>
     </row>
     <row r="51">
@@ -5529,14 +5529,14 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-0.0001452977838964698</v>
+        <v>-9.690869983747241e-05</v>
       </c>
       <c r="D51" t="n">
-        <v>8.59022910601418e-05</v>
+        <v>5.406300750381862e-05</v>
       </c>
     </row>
     <row r="52">
@@ -5549,10 +5549,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-0.0001692251611651985</v>
+        <v>-0.0001482043522033183</v>
       </c>
       <c r="D52" t="n">
-        <v>6.592491703884429e-05</v>
+        <v>9.671752472189063e-05</v>
       </c>
     </row>
     <row r="53">
@@ -5561,14 +5561,14 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-0.0001891751093902494</v>
+        <v>-0.0001800433885696839</v>
       </c>
       <c r="D53" t="n">
-        <v>6.920701365905233e-05</v>
+        <v>9.325461665867935e-05</v>
       </c>
     </row>
     <row r="54">
@@ -5577,14 +5577,14 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-0.0002161354935916515</v>
+        <v>-0.0003104006152105487</v>
       </c>
       <c r="D54" t="n">
-        <v>6.41107011072986e-05</v>
+        <v>9.910782854720545e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5628,7 +5628,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.478740368189571</v>
+        <v>1.220162286626203</v>
       </c>
     </row>
     <row r="3">
@@ -5641,7 +5641,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.433803714952994</v>
+        <v>1.197596762489799</v>
       </c>
     </row>
     <row r="4">
@@ -5654,7 +5654,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.296472196351193</v>
+        <v>1.032026958462696</v>
       </c>
     </row>
     <row r="5">
@@ -5667,7 +5667,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.107645524286439</v>
+        <v>0.8723113670408211</v>
       </c>
     </row>
     <row r="6">
@@ -5676,11 +5676,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.952211235371005</v>
+        <v>0.6149920332849157</v>
       </c>
     </row>
     <row r="7">
@@ -5689,11 +5689,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.8325968016518011</v>
+        <v>0.6066707781972243</v>
       </c>
     </row>
     <row r="8">
@@ -5706,7 +5706,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.8088540008413529</v>
+        <v>0.6059710037229373</v>
       </c>
     </row>
     <row r="9">
@@ -5715,11 +5715,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.7924090046246004</v>
+        <v>0.595591263334927</v>
       </c>
     </row>
     <row r="10">
@@ -5732,7 +5732,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.6333921093174082</v>
+        <v>0.4961557840490896</v>
       </c>
     </row>
     <row r="11">
@@ -5745,7 +5745,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.3373116316724039</v>
+        <v>0.2717957000954292</v>
       </c>
     </row>
     <row r="12">
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.2929207431772767</v>
+        <v>0.2699523346893602</v>
       </c>
     </row>
     <row r="13">
@@ -5767,11 +5767,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>white_quality_solution_color_2</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.2770263523620402</v>
+        <v>0.2636575744571474</v>
       </c>
     </row>
     <row r="14">
@@ -5780,11 +5780,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.2731534068695995</v>
+        <v>0.2445728104993856</v>
       </c>
     </row>
     <row r="15">
@@ -5793,11 +5793,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.2617903996465323</v>
+        <v>0.2125263033038287</v>
       </c>
     </row>
     <row r="16">
@@ -5806,11 +5806,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.229753298447156</v>
+        <v>0.2099184335506039</v>
       </c>
     </row>
     <row r="17">
@@ -5819,11 +5819,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.2295057870794264</v>
+        <v>0.1970921910273393</v>
       </c>
     </row>
     <row r="18">
@@ -5832,11 +5832,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.2218485223188855</v>
+        <v>0.1922289003748792</v>
       </c>
     </row>
     <row r="19">
@@ -5845,11 +5845,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.2207323944761521</v>
+        <v>0.1883237605390065</v>
       </c>
     </row>
     <row r="20">
@@ -5858,11 +5858,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.2086458278708552</v>
+        <v>0.1856278187338714</v>
       </c>
     </row>
     <row r="21">
@@ -5871,11 +5871,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.2057084216457903</v>
+        <v>0.164502853842124</v>
       </c>
     </row>
     <row r="22">
@@ -5888,7 +5888,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.2052719691187259</v>
+        <v>0.1581573980849016</v>
       </c>
     </row>
     <row r="23">
@@ -5897,11 +5897,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.2014771250067651</v>
+        <v>0.1565064608513327</v>
       </c>
     </row>
     <row r="24">
@@ -5910,11 +5910,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.2005507462162361</v>
+        <v>0.1528703251648047</v>
       </c>
     </row>
     <row r="25">
@@ -5923,11 +5923,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.1776140935255817</v>
+        <v>0.1497267572983745</v>
       </c>
     </row>
     <row r="26">
@@ -5936,11 +5936,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.1709834645543058</v>
+        <v>0.1483923472772828</v>
       </c>
     </row>
     <row r="27">
@@ -5949,11 +5949,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.159505819969981</v>
+        <v>0.1465052836719529</v>
       </c>
     </row>
     <row r="28">
@@ -5962,11 +5962,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.1543834728358466</v>
+        <v>0.1328690731507498</v>
       </c>
     </row>
     <row r="29">
@@ -5975,11 +5975,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.1414615172091742</v>
+        <v>0.1298072021325805</v>
       </c>
     </row>
     <row r="30">
@@ -5988,11 +5988,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.1321623732084736</v>
+        <v>0.1250352999412252</v>
       </c>
     </row>
     <row r="31">
@@ -6001,11 +6001,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.1306732706335407</v>
+        <v>0.1206952753538957</v>
       </c>
     </row>
     <row r="32">
@@ -6014,11 +6014,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.1193277577675893</v>
+        <v>0.1185070533412098</v>
       </c>
     </row>
     <row r="33">
@@ -6027,11 +6027,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.1111174670285382</v>
+        <v>0.1163760253988069</v>
       </c>
     </row>
     <row r="34">
@@ -6040,11 +6040,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.1100992902083822</v>
+        <v>0.1162677246604455</v>
       </c>
     </row>
     <row r="35">
@@ -6053,11 +6053,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.1083655886876653</v>
+        <v>0.1133977684273755</v>
       </c>
     </row>
     <row r="36">
@@ -6066,11 +6066,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.1081584076742153</v>
+        <v>0.1105996765571509</v>
       </c>
     </row>
     <row r="37">
@@ -6079,11 +6079,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.1077356270524956</v>
+        <v>0.1085555176625839</v>
       </c>
     </row>
     <row r="38">
@@ -6092,11 +6092,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.1054561942143275</v>
+        <v>0.1047114309968094</v>
       </c>
     </row>
     <row r="39">
@@ -6105,11 +6105,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.1047131403997339</v>
+        <v>0.09661113621317829</v>
       </c>
     </row>
     <row r="40">
@@ -6118,11 +6118,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.1043761904758367</v>
+        <v>0.08866143799683179</v>
       </c>
     </row>
     <row r="41">
@@ -6131,11 +6131,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.09267643000428505</v>
+        <v>0.08700539601290069</v>
       </c>
     </row>
     <row r="42">
@@ -6144,11 +6144,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.08181546115420524</v>
+        <v>0.08252037876710538</v>
       </c>
     </row>
     <row r="43">
@@ -6157,11 +6157,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.08120877841116192</v>
+        <v>0.08158316046622227</v>
       </c>
     </row>
     <row r="44">
@@ -6170,11 +6170,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.0786731789563766</v>
+        <v>0.07873252507831374</v>
       </c>
     </row>
     <row r="45">
@@ -6183,11 +6183,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.07692667533808129</v>
+        <v>0.05864846358770226</v>
       </c>
     </row>
     <row r="46">
@@ -6196,11 +6196,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.05888879003301017</v>
+        <v>0.05192730137918167</v>
       </c>
     </row>
     <row r="47">
@@ -6209,11 +6209,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.04923555457813222</v>
+        <v>0.04812936651390975</v>
       </c>
     </row>
     <row r="48">
@@ -6222,11 +6222,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.04556853675596395</v>
+        <v>0.03575821798885048</v>
       </c>
     </row>
     <row r="49">
@@ -6235,11 +6235,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>white_quality_moisture_2</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.03360896424143878</v>
+        <v>0.02854832884313652</v>
       </c>
     </row>
     <row r="50">
@@ -6248,11 +6248,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>white_quality_moisture_1</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.01937812905933955</v>
+        <v>0.01525040081228823</v>
       </c>
     </row>
     <row r="51">
@@ -6261,11 +6261,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.001182132265124647</v>
+        <v>0.004620886376301314</v>
       </c>
     </row>
     <row r="52">
@@ -6274,20 +6274,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>shift_name</t>
+          <t>white_quality_moisture_2</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>0.0006290865065095019</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6296,7 +6296,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6334,15 +6334,30 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>training_rows_used</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>permutation_rows_used</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>source_variables_ranked</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>encoded_feature_count</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>preprocessing_scope</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>created_at_utc</t>
         </is>
@@ -6358,14 +6373,25 @@
         <v>788</v>
       </c>
       <c r="C2" t="n">
+        <v>591</v>
+      </c>
+      <c r="D2" t="n">
+        <v>197</v>
+      </c>
+      <c r="E2" t="n">
         <v>53</v>
       </c>
-      <c r="D2" t="n">
-        <v>446</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-06-11 09:45:03 UTC</t>
+      <c r="F2" t="n">
+        <v>414</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>fit_on_training_split_only</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-06-14 21:56:19 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_solution_color.xlsx
+++ b/NN/reports/feature_importance_white_solution_color.xlsx
@@ -513,7 +513,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3598793571410549</v>
+        <v>0.3598793571410547</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -550,7 +550,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2813470101326704</v>
+        <v>0.2813470101326703</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -587,7 +587,7 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03188475108235696</v>
+        <v>0.03188475108235687</v>
       </c>
       <c r="H4" t="n">
         <v>4</v>
@@ -624,7 +624,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0416466695227404</v>
+        <v>0.04164666952274031</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
@@ -661,7 +661,7 @@
         <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02157996931448751</v>
+        <v>0.02157996931448739</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -698,7 +698,7 @@
         <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01200704749597893</v>
+        <v>0.01200704749597883</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
@@ -735,7 +735,7 @@
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004525107807768736</v>
+        <v>0.004525107807768625</v>
       </c>
       <c r="H8" t="n">
         <v>8</v>
@@ -772,7 +772,7 @@
         <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.005298272783865276</v>
+        <v>0.005298272783865155</v>
       </c>
       <c r="H9" t="n">
         <v>7</v>
@@ -809,7 +809,7 @@
         <v>5</v>
       </c>
       <c r="G10" t="n">
-        <v>0.000372539178951691</v>
+        <v>0.0003725391789113563</v>
       </c>
       <c r="H10" t="n">
         <v>23</v>
@@ -846,7 +846,7 @@
         <v>11</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001006899723146704</v>
+        <v>0.001006899723146582</v>
       </c>
       <c r="H11" t="n">
         <v>13</v>
@@ -883,7 +883,7 @@
         <v>19</v>
       </c>
       <c r="G12" t="n">
-        <v>0.001066831892333842</v>
+        <v>0.001066831892333719</v>
       </c>
       <c r="H12" t="n">
         <v>12</v>
@@ -920,7 +920,7 @@
         <v>17</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0005687225825382169</v>
+        <v>0.0005687225825380838</v>
       </c>
       <c r="H13" t="n">
         <v>15</v>
@@ -957,7 +957,7 @@
         <v>16</v>
       </c>
       <c r="G14" t="n">
-        <v>0.000207213615126034</v>
+        <v>0.0002072136151259229</v>
       </c>
       <c r="H14" t="n">
         <v>31</v>
@@ -994,7 +994,7 @@
         <v>21</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001319066452785034</v>
+        <v>0.001319066452784934</v>
       </c>
       <c r="H15" t="n">
         <v>10</v>
@@ -1031,7 +1031,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="n">
-        <v>0.001145782448783261</v>
+        <v>0.001145782448783172</v>
       </c>
       <c r="H16" t="n">
         <v>11</v>
@@ -1068,7 +1068,7 @@
         <v>20</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0003341763919278318</v>
+        <v>0.0003341763919277096</v>
       </c>
       <c r="H17" t="n">
         <v>24</v>
@@ -1105,7 +1105,7 @@
         <v>12</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0002236489103919825</v>
+        <v>0.0002236489103918382</v>
       </c>
       <c r="H18" t="n">
         <v>27</v>
@@ -1142,7 +1142,7 @@
         <v>28</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0005098336434349981</v>
+        <v>0.0005098336434348871</v>
       </c>
       <c r="H19" t="n">
         <v>18</v>
@@ -1179,7 +1179,7 @@
         <v>25</v>
       </c>
       <c r="G20" t="n">
-        <v>0.001391474375185364</v>
+        <v>0.001391474375185242</v>
       </c>
       <c r="H20" t="n">
         <v>9</v>
@@ -1216,7 +1216,7 @@
         <v>24</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0003862927800955651</v>
+        <v>0.0003862927800954319</v>
       </c>
       <c r="H21" t="n">
         <v>21</v>
@@ -1253,7 +1253,7 @@
         <v>9</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0002159719791945736</v>
+        <v>0.0002159719791944514</v>
       </c>
       <c r="H22" t="n">
         <v>28</v>
@@ -1290,7 +1290,7 @@
         <v>27</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0005605871611487178</v>
+        <v>0.0005605871611486068</v>
       </c>
       <c r="H23" t="n">
         <v>16</v>
@@ -1327,7 +1327,7 @@
         <v>14</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0002414067048767232</v>
+        <v>0.0002414067048766122</v>
       </c>
       <c r="H24" t="n">
         <v>26</v>
@@ -1364,7 +1364,7 @@
         <v>31</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0002136535776239623</v>
+        <v>0.0002136535776238402</v>
       </c>
       <c r="H25" t="n">
         <v>29</v>
@@ -1401,7 +1401,7 @@
         <v>37</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0002883913801753901</v>
+        <v>0.0002883913801752902</v>
       </c>
       <c r="H26" t="n">
         <v>25</v>
@@ -1438,7 +1438,7 @@
         <v>22</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0002084405193223504</v>
+        <v>0.0002084405193222505</v>
       </c>
       <c r="H27" t="n">
         <v>30</v>
@@ -1475,7 +1475,7 @@
         <v>18</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0001532722460016789</v>
+        <v>0.0001532722460015789</v>
       </c>
       <c r="H28" t="n">
         <v>33</v>
@@ -1512,7 +1512,7 @@
         <v>26</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.0001482043522033183</v>
+        <v>-0.0001482043522034182</v>
       </c>
       <c r="H29" t="n">
         <v>51</v>
@@ -1549,7 +1549,7 @@
         <v>13</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0001380282076580475</v>
+        <v>0.0001380282076579475</v>
       </c>
       <c r="H30" t="n">
         <v>35</v>
@@ -1586,7 +1586,7 @@
         <v>29</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0003850525447718689</v>
+        <v>0.0003850525447717357</v>
       </c>
       <c r="H31" t="n">
         <v>22</v>
@@ -1623,7 +1623,7 @@
         <v>45</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0005800150786270831</v>
+        <v>0.0005800150786269609</v>
       </c>
       <c r="H32" t="n">
         <v>14</v>
@@ -1660,7 +1660,7 @@
         <v>23</v>
       </c>
       <c r="G33" t="n">
-        <v>-4.068710041975621e-05</v>
+        <v>-4.068710041987833e-05</v>
       </c>
       <c r="H33" t="n">
         <v>47</v>
@@ -1697,7 +1697,7 @@
         <v>39</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0005449226424683595</v>
+        <v>0.0005449226424682596</v>
       </c>
       <c r="H34" t="n">
         <v>17</v>
@@ -1734,7 +1734,7 @@
         <v>34</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0004150406246041682</v>
+        <v>0.0004150406246040683</v>
       </c>
       <c r="H35" t="n">
         <v>19</v>
@@ -1771,7 +1771,7 @@
         <v>32</v>
       </c>
       <c r="G36" t="n">
-        <v>0.000173194622588313</v>
+        <v>0.0001731946225882352</v>
       </c>
       <c r="H36" t="n">
         <v>32</v>
@@ -1808,7 +1808,7 @@
         <v>33</v>
       </c>
       <c r="G37" t="n">
-        <v>3.591056691276684e-05</v>
+        <v>3.591056691265582e-05</v>
       </c>
       <c r="H37" t="n">
         <v>40</v>
@@ -1845,7 +1845,7 @@
         <v>30</v>
       </c>
       <c r="G38" t="n">
-        <v>5.232347753792998e-05</v>
+        <v>5.232347753778566e-05</v>
       </c>
       <c r="H38" t="n">
         <v>39</v>
@@ -1882,7 +1882,7 @@
         <v>49</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0001203639689924652</v>
+        <v>0.000120363968992343</v>
       </c>
       <c r="H39" t="n">
         <v>36</v>
@@ -1919,7 +1919,7 @@
         <v>42</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0001509396737493618</v>
+        <v>0.0001509396737492619</v>
       </c>
       <c r="H40" t="n">
         <v>34</v>
@@ -1956,7 +1956,7 @@
         <v>35</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0003921249062824983</v>
+        <v>0.0003921249062823762</v>
       </c>
       <c r="H41" t="n">
         <v>20</v>
@@ -1993,7 +1993,7 @@
         <v>38</v>
       </c>
       <c r="G42" t="n">
-        <v>-3.912405583600398e-05</v>
+        <v>-3.91240558361261e-05</v>
       </c>
       <c r="H42" t="n">
         <v>46</v>
@@ -2030,7 +2030,7 @@
         <v>41</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0001046023916772998</v>
+        <v>0.000104602391677211</v>
       </c>
       <c r="H43" t="n">
         <v>37</v>
@@ -2067,7 +2067,7 @@
         <v>36</v>
       </c>
       <c r="G44" t="n">
-        <v>-5.288512301215853e-06</v>
+        <v>-5.288512301337978e-06</v>
       </c>
       <c r="H44" t="n">
         <v>42</v>
@@ -2104,7 +2104,7 @@
         <v>40</v>
       </c>
       <c r="G45" t="n">
-        <v>-9.690869983747241e-05</v>
+        <v>-9.690869983760563e-05</v>
       </c>
       <c r="H45" t="n">
         <v>50</v>
@@ -2141,7 +2141,7 @@
         <v>47</v>
       </c>
       <c r="G46" t="n">
-        <v>-3.656031711283258e-05</v>
+        <v>-3.656031711293251e-05</v>
       </c>
       <c r="H46" t="n">
         <v>45</v>
@@ -2178,7 +2178,7 @@
         <v>50</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.0001800433885696839</v>
+        <v>-0.0001800433885698061</v>
       </c>
       <c r="H47" t="n">
         <v>52</v>
@@ -2215,7 +2215,7 @@
         <v>46</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.0003104006152105487</v>
+        <v>-0.0003104006152106375</v>
       </c>
       <c r="H48" t="n">
         <v>53</v>
@@ -2252,7 +2252,7 @@
         <v>48</v>
       </c>
       <c r="G49" t="n">
-        <v>-5.153761794967071e-05</v>
+        <v>-5.153761794980394e-05</v>
       </c>
       <c r="H49" t="n">
         <v>49</v>
@@ -2289,7 +2289,7 @@
         <v>44</v>
       </c>
       <c r="G50" t="n">
-        <v>-1.62630332425584e-05</v>
+        <v>-1.626303324265832e-05</v>
       </c>
       <c r="H50" t="n">
         <v>43</v>
@@ -2326,7 +2326,7 @@
         <v>52</v>
       </c>
       <c r="G51" t="n">
-        <v>6.202459662529858e-05</v>
+        <v>6.202459662519866e-05</v>
       </c>
       <c r="H51" t="n">
         <v>38</v>
@@ -2363,7 +2363,7 @@
         <v>43</v>
       </c>
       <c r="G52" t="n">
-        <v>-4.815492907939145e-05</v>
+        <v>-4.815492907950247e-05</v>
       </c>
       <c r="H52" t="n">
         <v>48</v>
@@ -2400,7 +2400,7 @@
         <v>51</v>
       </c>
       <c r="G53" t="n">
-        <v>1.240458790952026e-05</v>
+        <v>1.240458790938703e-05</v>
       </c>
       <c r="H53" t="n">
         <v>41</v>
@@ -2437,7 +2437,7 @@
         <v>53</v>
       </c>
       <c r="G54" t="n">
-        <v>-2.786894234019233e-05</v>
+        <v>-2.786894234031445e-05</v>
       </c>
       <c r="H54" t="n">
         <v>44</v>
@@ -2545,7 +2545,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3598793571410549</v>
+        <v>0.3598793571410547</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -2582,7 +2582,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2813470101326704</v>
+        <v>0.2813470101326703</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -2619,7 +2619,7 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03188475108235696</v>
+        <v>0.03188475108235687</v>
       </c>
       <c r="H4" t="n">
         <v>4</v>
@@ -2656,7 +2656,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0416466695227404</v>
+        <v>0.04164666952274031</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
@@ -2693,7 +2693,7 @@
         <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02157996931448751</v>
+        <v>0.02157996931448739</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -2730,7 +2730,7 @@
         <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01200704749597893</v>
+        <v>0.01200704749597883</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
@@ -2767,7 +2767,7 @@
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004525107807768736</v>
+        <v>0.004525107807768625</v>
       </c>
       <c r="H8" t="n">
         <v>8</v>
@@ -2804,7 +2804,7 @@
         <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.005298272783865276</v>
+        <v>0.005298272783865155</v>
       </c>
       <c r="H9" t="n">
         <v>7</v>
@@ -2841,7 +2841,7 @@
         <v>5</v>
       </c>
       <c r="G10" t="n">
-        <v>0.000372539178951691</v>
+        <v>0.0003725391789113563</v>
       </c>
       <c r="H10" t="n">
         <v>23</v>
@@ -2878,7 +2878,7 @@
         <v>11</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001006899723146704</v>
+        <v>0.001006899723146582</v>
       </c>
       <c r="H11" t="n">
         <v>13</v>
@@ -2915,7 +2915,7 @@
         <v>19</v>
       </c>
       <c r="G12" t="n">
-        <v>0.001066831892333842</v>
+        <v>0.001066831892333719</v>
       </c>
       <c r="H12" t="n">
         <v>12</v>
@@ -2952,7 +2952,7 @@
         <v>17</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0005687225825382169</v>
+        <v>0.0005687225825380838</v>
       </c>
       <c r="H13" t="n">
         <v>15</v>
@@ -2989,7 +2989,7 @@
         <v>16</v>
       </c>
       <c r="G14" t="n">
-        <v>0.000207213615126034</v>
+        <v>0.0002072136151259229</v>
       </c>
       <c r="H14" t="n">
         <v>31</v>
@@ -3026,7 +3026,7 @@
         <v>21</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001319066452785034</v>
+        <v>0.001319066452784934</v>
       </c>
       <c r="H15" t="n">
         <v>10</v>
@@ -3063,7 +3063,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="n">
-        <v>0.001145782448783261</v>
+        <v>0.001145782448783172</v>
       </c>
       <c r="H16" t="n">
         <v>11</v>
@@ -3100,7 +3100,7 @@
         <v>20</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0003341763919278318</v>
+        <v>0.0003341763919277096</v>
       </c>
       <c r="H17" t="n">
         <v>24</v>
@@ -3137,7 +3137,7 @@
         <v>12</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0002236489103919825</v>
+        <v>0.0002236489103918382</v>
       </c>
       <c r="H18" t="n">
         <v>27</v>
@@ -3174,7 +3174,7 @@
         <v>28</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0005098336434349981</v>
+        <v>0.0005098336434348871</v>
       </c>
       <c r="H19" t="n">
         <v>18</v>
@@ -3211,7 +3211,7 @@
         <v>25</v>
       </c>
       <c r="G20" t="n">
-        <v>0.001391474375185364</v>
+        <v>0.001391474375185242</v>
       </c>
       <c r="H20" t="n">
         <v>9</v>
@@ -3248,7 +3248,7 @@
         <v>24</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0003862927800955651</v>
+        <v>0.0003862927800954319</v>
       </c>
       <c r="H21" t="n">
         <v>21</v>
@@ -4749,10 +4749,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3598793571410549</v>
+        <v>0.3598793571410547</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03041445669921597</v>
+        <v>0.03041445669921594</v>
       </c>
     </row>
     <row r="3">
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2813470101326704</v>
+        <v>0.2813470101326703</v>
       </c>
       <c r="D3" t="n">
         <v>0.01524823488966109</v>
@@ -4781,10 +4781,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0416466695227404</v>
+        <v>0.04164666952274031</v>
       </c>
       <c r="D4" t="n">
-        <v>0.007157943070708389</v>
+        <v>0.007157943070708386</v>
       </c>
     </row>
     <row r="5">
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03188475108235696</v>
+        <v>0.03188475108235687</v>
       </c>
       <c r="D5" t="n">
-        <v>0.007600139502350577</v>
+        <v>0.007600139502350598</v>
       </c>
     </row>
     <row r="6">
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.02157996931448751</v>
+        <v>0.02157996931448739</v>
       </c>
       <c r="D6" t="n">
-        <v>0.005562400201518326</v>
+        <v>0.005562400201518328</v>
       </c>
     </row>
     <row r="7">
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01200704749597893</v>
+        <v>0.01200704749597883</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001327194475607478</v>
+        <v>0.001327194475607489</v>
       </c>
     </row>
     <row r="8">
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.005298272783865276</v>
+        <v>0.005298272783865155</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0004053558587745954</v>
+        <v>0.0004053558587746051</v>
       </c>
     </row>
     <row r="9">
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.004525107807768736</v>
+        <v>0.004525107807768625</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0004560717475661853</v>
+        <v>0.0004560717475661921</v>
       </c>
     </row>
     <row r="10">
@@ -4877,10 +4877,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.001391474375185364</v>
+        <v>0.001391474375185242</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0001591010685670372</v>
+        <v>0.0001591010685670374</v>
       </c>
     </row>
     <row r="11">
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.001319066452785034</v>
+        <v>0.001319066452784934</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0005414674602246542</v>
+        <v>0.0005414674602246384</v>
       </c>
     </row>
     <row r="12">
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.001145782448783261</v>
+        <v>0.001145782448783172</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0002168212391677222</v>
+        <v>0.0002168212391676837</v>
       </c>
     </row>
     <row r="13">
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001066831892333842</v>
+        <v>0.001066831892333719</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0005048358098471679</v>
+        <v>0.0005048358098471721</v>
       </c>
     </row>
     <row r="14">
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.001006899723146704</v>
+        <v>0.001006899723146582</v>
       </c>
       <c r="D14" t="n">
-        <v>0.000355095111806079</v>
+        <v>0.0003550951118060907</v>
       </c>
     </row>
     <row r="15">
@@ -4957,10 +4957,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0005800150786270831</v>
+        <v>0.0005800150786269609</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0001644582744382722</v>
+        <v>0.0001644582744382503</v>
       </c>
     </row>
     <row r="16">
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0005687225825382169</v>
+        <v>0.0005687225825380838</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0001283287493608244</v>
+        <v>0.0001283287493608198</v>
       </c>
     </row>
     <row r="17">
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0005605871611487178</v>
+        <v>0.0005605871611486068</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0001436236424471595</v>
+        <v>0.0001436236424471791</v>
       </c>
     </row>
     <row r="18">
@@ -5005,10 +5005,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0005449226424683595</v>
+        <v>0.0005449226424682596</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0001626794654960903</v>
+        <v>0.0001626794654960852</v>
       </c>
     </row>
     <row r="19">
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0005098336434349981</v>
+        <v>0.0005098336434348871</v>
       </c>
       <c r="D19" t="n">
         <v>0.0001447292561736676</v>
@@ -5037,10 +5037,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0004150406246041682</v>
+        <v>0.0004150406246040683</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0001287384004968305</v>
+        <v>0.0001287384004968077</v>
       </c>
     </row>
     <row r="21">
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0003921249062824983</v>
+        <v>0.0003921249062823762</v>
       </c>
       <c r="D21" t="n">
-        <v>4.256663542581737e-05</v>
+        <v>4.256663542582924e-05</v>
       </c>
     </row>
     <row r="22">
@@ -5069,10 +5069,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0003862927800955651</v>
+        <v>0.0003862927800954319</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0003116897519392526</v>
+        <v>0.0003116897519392233</v>
       </c>
     </row>
     <row r="23">
@@ -5085,10 +5085,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0003850525447718689</v>
+        <v>0.0003850525447717357</v>
       </c>
       <c r="D23" t="n">
-        <v>7.169897241367991e-05</v>
+        <v>7.169897241367817e-05</v>
       </c>
     </row>
     <row r="24">
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.000372539178951691</v>
+        <v>0.0003725391789113563</v>
       </c>
       <c r="D24" t="n">
-        <v>4.731016319563441e-05</v>
+        <v>4.731016319609135e-05</v>
       </c>
     </row>
     <row r="25">
@@ -5117,10 +5117,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0003341763919278318</v>
+        <v>0.0003341763919277096</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0001281307850932167</v>
+        <v>0.0001281307850931933</v>
       </c>
     </row>
     <row r="26">
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0002883913801753901</v>
+        <v>0.0002883913801752902</v>
       </c>
       <c r="D26" t="n">
-        <v>6.261256938241649e-05</v>
+        <v>6.2612569382424e-05</v>
       </c>
     </row>
     <row r="27">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0002414067048767232</v>
+        <v>0.0002414067048766122</v>
       </c>
       <c r="D27" t="n">
         <v>6.713344377306386e-05</v>
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0002236489103919825</v>
+        <v>0.0002236489103918382</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0001163251040838036</v>
+        <v>0.0001163251040837829</v>
       </c>
     </row>
     <row r="29">
@@ -5181,10 +5181,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0002159719791945736</v>
+        <v>0.0002159719791944514</v>
       </c>
       <c r="D29" t="n">
-        <v>6.71142060242558e-05</v>
+        <v>6.711420602428067e-05</v>
       </c>
     </row>
     <row r="30">
@@ -5197,10 +5197,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0002136535776239623</v>
+        <v>0.0002136535776238402</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0001950049485494441</v>
+        <v>0.0001950049485494445</v>
       </c>
     </row>
     <row r="31">
@@ -5213,10 +5213,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0002084405193223504</v>
+        <v>0.0002084405193222505</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0001183540964854371</v>
+        <v>0.0001183540964854376</v>
       </c>
     </row>
     <row r="32">
@@ -5229,7 +5229,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.000207213615126034</v>
+        <v>0.0002072136151259229</v>
       </c>
       <c r="D32" t="n">
         <v>0.0007383849116093184</v>
@@ -5245,10 +5245,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.000173194622588313</v>
+        <v>0.0001731946225882352</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0001044216602020246</v>
+        <v>0.000104421660202034</v>
       </c>
     </row>
     <row r="34">
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0001532722460016789</v>
+        <v>0.0001532722460015789</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0001221877296913883</v>
+        <v>0.0001221877296913792</v>
       </c>
     </row>
     <row r="35">
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0001509396737493618</v>
+        <v>0.0001509396737492619</v>
       </c>
       <c r="D35" t="n">
-        <v>7.09691553413078e-05</v>
+        <v>7.096915534128307e-05</v>
       </c>
     </row>
     <row r="36">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0001380282076580475</v>
+        <v>0.0001380282076579475</v>
       </c>
       <c r="D36" t="n">
-        <v>7.290849629907503e-05</v>
+        <v>7.290849629909114e-05</v>
       </c>
     </row>
     <row r="37">
@@ -5309,10 +5309,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.0001203639689924652</v>
+        <v>0.000120363968992343</v>
       </c>
       <c r="D37" t="n">
-        <v>8.059860407535291e-05</v>
+        <v>8.059860407533205e-05</v>
       </c>
     </row>
     <row r="38">
@@ -5325,10 +5325,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.0001046023916772998</v>
+        <v>0.000104602391677211</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0001087672521161095</v>
+        <v>0.0001087672521161225</v>
       </c>
     </row>
     <row r="39">
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>6.202459662529858e-05</v>
+        <v>6.202459662519866e-05</v>
       </c>
       <c r="D39" t="n">
-        <v>2.874274511499105e-05</v>
+        <v>2.874274511499008e-05</v>
       </c>
     </row>
     <row r="40">
@@ -5357,10 +5357,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5.232347753792998e-05</v>
+        <v>5.232347753778566e-05</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0001120303628327273</v>
+        <v>0.000112030362832724</v>
       </c>
     </row>
     <row r="41">
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3.591056691276684e-05</v>
+        <v>3.591056691265582e-05</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0001434684123433035</v>
+        <v>0.0001434684123433031</v>
       </c>
     </row>
     <row r="42">
@@ -5389,10 +5389,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1.240458790952026e-05</v>
+        <v>1.240458790938703e-05</v>
       </c>
       <c r="D42" t="n">
-        <v>4.605546486457779e-06</v>
+        <v>4.605546486449173e-06</v>
       </c>
     </row>
     <row r="43">
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-5.288512301215853e-06</v>
+        <v>-5.288512301337978e-06</v>
       </c>
       <c r="D43" t="n">
-        <v>8.119598861249887e-05</v>
+        <v>8.11959886125023e-05</v>
       </c>
     </row>
     <row r="44">
@@ -5421,10 +5421,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-1.62630332425584e-05</v>
+        <v>-1.626303324265832e-05</v>
       </c>
       <c r="D44" t="n">
-        <v>3.726211982360197e-05</v>
+        <v>3.726211982361448e-05</v>
       </c>
     </row>
     <row r="45">
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-2.786894234019233e-05</v>
+        <v>-2.786894234031445e-05</v>
       </c>
       <c r="D45" t="n">
-        <v>1.777214842172435e-05</v>
+        <v>1.777214842172522e-05</v>
       </c>
     </row>
     <row r="46">
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-3.656031711283258e-05</v>
+        <v>-3.656031711293251e-05</v>
       </c>
       <c r="D46" t="n">
-        <v>4.499235083519608e-05</v>
+        <v>4.49923508352163e-05</v>
       </c>
     </row>
     <row r="47">
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-3.912405583600398e-05</v>
+        <v>-3.91240558361261e-05</v>
       </c>
       <c r="D47" t="n">
-        <v>6.675099540998198e-05</v>
+        <v>6.675099540998126e-05</v>
       </c>
     </row>
     <row r="48">
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-4.068710041975621e-05</v>
+        <v>-4.068710041987833e-05</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0001025101141063102</v>
+        <v>0.0001025101141062979</v>
       </c>
     </row>
     <row r="49">
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-4.815492907939145e-05</v>
+        <v>-4.815492907950247e-05</v>
       </c>
       <c r="D49" t="n">
         <v>2.803255978632049e-05</v>
@@ -5517,10 +5517,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-5.153761794967071e-05</v>
+        <v>-5.153761794980394e-05</v>
       </c>
       <c r="D50" t="n">
-        <v>8.442209553245845e-05</v>
+        <v>8.442209553244266e-05</v>
       </c>
     </row>
     <row r="51">
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-9.690869983747241e-05</v>
+        <v>-9.690869983760563e-05</v>
       </c>
       <c r="D51" t="n">
-        <v>5.406300750381862e-05</v>
+        <v>5.406300750380171e-05</v>
       </c>
     </row>
     <row r="52">
@@ -5549,10 +5549,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-0.0001482043522033183</v>
+        <v>-0.0001482043522034182</v>
       </c>
       <c r="D52" t="n">
-        <v>9.671752472189063e-05</v>
+        <v>9.671752472188728e-05</v>
       </c>
     </row>
     <row r="53">
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-0.0001800433885696839</v>
+        <v>-0.0001800433885698061</v>
       </c>
       <c r="D53" t="n">
-        <v>9.325461665867935e-05</v>
+        <v>9.325461665870275e-05</v>
       </c>
     </row>
     <row r="54">
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-0.0003104006152105487</v>
+        <v>-0.0003104006152106375</v>
       </c>
       <c r="D54" t="n">
-        <v>9.910782854720545e-05</v>
+        <v>9.910782854718644e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-14 21:56:19 UTC</t>
+          <t>2026-06-15 07:19:38 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_solution_color.xlsx
+++ b/NN/reports/feature_importance_white_solution_color.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,31 +501,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3509264667099231</v>
+        <v>0.4631551263978727</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3273009785562683</v>
+        <v>0.4354256942335763</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3598793571410547</v>
+        <v>0.7224825652776311</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1.197596762489799</v>
+        <v>1.197226875819409</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -534,35 +534,35 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2430083986073938</v>
+        <v>0.1448121411127521</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2341821975658129</v>
+        <v>0.1013739829994583</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2813470101326703</v>
+        <v>0.05593059693425771</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>1.220162286626203</v>
+        <v>0.6036619723165955</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
-        <v>1.75</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="4">
@@ -571,32 +571,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1136888176080379</v>
+        <v>0.1396444272155124</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.202284502935228</v>
+        <v>0.01913738835731541</v>
       </c>
       <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.04754782163519602</v>
+      </c>
+      <c r="H4" t="n">
         <v>3</v>
       </c>
-      <c r="G4" t="n">
-        <v>0.03188475108235687</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4</v>
-      </c>
       <c r="I4" t="n">
-        <v>0.6066707781972243</v>
+        <v>0.6141018072778577</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
         <v>4.25</v>
@@ -608,32 +608,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.1216747028217113</v>
+        <v>0.02636596662579262</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08437781417749506</v>
+        <v>0.01990592942979598</v>
       </c>
       <c r="F5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.04493023010480252</v>
+      </c>
+      <c r="H5" t="n">
         <v>4</v>
       </c>
-      <c r="G5" t="n">
-        <v>0.04164666952274031</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3</v>
-      </c>
       <c r="I5" t="n">
-        <v>0.595591263334927</v>
+        <v>0.6246955590411227</v>
       </c>
       <c r="J5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
         <v>4.5</v>
@@ -645,35 +645,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.09170833013467054</v>
+        <v>0.1331106287933128</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01261148354771118</v>
+        <v>0.2879053195239505</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02157996931448739</v>
+        <v>0.04450525608057554</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6149920332849157</v>
+        <v>0.6022214060763087</v>
       </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="7">
@@ -682,35 +682,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01179176619992063</v>
+        <v>0.00828411418578723</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0125716311096866</v>
+        <v>0.009696906563716166</v>
       </c>
       <c r="F7" t="n">
         <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01200704749597883</v>
+        <v>0.0068005622638733</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6059710037229373</v>
+        <v>0.8714167049095849</v>
       </c>
       <c r="J7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>6.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -719,35 +719,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.006322868406578661</v>
+        <v>0.008586265363717871</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>0.006797540172290032</v>
+        <v>0.05082021444524421</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004525107807768625</v>
+        <v>0.00105586038311577</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8723113670408211</v>
+        <v>0.9694040788023274</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>7.25</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="9">
@@ -756,35 +756,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.005621442661865416</v>
+        <v>0.005710278243218773</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01914241201728629</v>
+        <v>0.00433443817214928</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G9" t="n">
-        <v>0.005298272783865155</v>
+        <v>0.002484865916395507</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2717957000954292</v>
+        <v>0.47636999799035</v>
       </c>
       <c r="J9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>7.75</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="10">
@@ -793,35 +793,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.003044858379230276</v>
+        <v>0.005696968220380511</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>0.03151805388149846</v>
+        <v>0.002951505311773142</v>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0003725391789113563</v>
+        <v>0.004291247703178835</v>
       </c>
       <c r="H10" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="I10" t="n">
-        <v>1.032026958462696</v>
+        <v>0.1817267023553764</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K10" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="11">
@@ -830,35 +830,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.003738895770907981</v>
+        <v>0.00302537037209505</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>0.006383871055968616</v>
+        <v>0.004482480251171447</v>
       </c>
       <c r="F11" t="n">
         <v>11</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001006899723146582</v>
+        <v>0.001160984115541563</v>
       </c>
       <c r="H11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2636575744571474</v>
+        <v>0.215175382121823</v>
       </c>
       <c r="J11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K11" t="n">
-        <v>11.5</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="12">
@@ -867,35 +867,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.002699248342943198</v>
+        <v>0.004854647722158108</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>0.001671672701943038</v>
+        <v>0.002997389936709667</v>
       </c>
       <c r="F12" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G12" t="n">
-        <v>0.001066831892333719</v>
+        <v>0.002581567689486497</v>
       </c>
       <c r="H12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1883237605390065</v>
+        <v>0.1200999449624831</v>
       </c>
       <c r="J12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K12" t="n">
-        <v>15.25</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="13">
@@ -904,35 +904,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001648145579726441</v>
+        <v>0.003187194930810727</v>
       </c>
       <c r="D13" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>0.002453077075937192</v>
+        <v>0.002671425196684824</v>
       </c>
       <c r="F13" t="n">
         <v>17</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0005687225825380838</v>
+        <v>0.00211519601732254</v>
       </c>
       <c r="H13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2125263033038287</v>
+        <v>0.1430107500986084</v>
       </c>
       <c r="J13" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K13" t="n">
-        <v>16.25</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="14">
@@ -941,32 +941,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.00401375600794517</v>
+        <v>0.003086284536756752</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>0.002790204142766983</v>
+        <v>0.001709246053542684</v>
       </c>
       <c r="F14" t="n">
+        <v>20</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.0008640450036720093</v>
+      </c>
+      <c r="H14" t="n">
+        <v>17</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1660814131995023</v>
+      </c>
+      <c r="J14" t="n">
         <v>16</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.0002072136151259229</v>
-      </c>
-      <c r="H14" t="n">
-        <v>31</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.4961557840490896</v>
-      </c>
-      <c r="J14" t="n">
-        <v>9</v>
       </c>
       <c r="K14" t="n">
         <v>16.25</v>
@@ -978,32 +978,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.002245715045750216</v>
+        <v>0.001997492757429873</v>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E15" t="n">
-        <v>0.00152358979170372</v>
+        <v>0.003398160462251813</v>
       </c>
       <c r="F15" t="n">
+        <v>13</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.0006637387286543949</v>
+      </c>
+      <c r="H15" t="n">
         <v>21</v>
       </c>
-      <c r="G15" t="n">
-        <v>0.001319066452784934</v>
-      </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
+        <v>0.2255469942945947</v>
+      </c>
+      <c r="J15" t="n">
         <v>10</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.1581573980849016</v>
-      </c>
-      <c r="J15" t="n">
-        <v>21</v>
       </c>
       <c r="K15" t="n">
         <v>16.5</v>
@@ -1015,35 +1015,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.00217139327705321</v>
+        <v>0.002090912399233735</v>
       </c>
       <c r="D16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E16" t="n">
-        <v>0.002930754602353963</v>
+        <v>0.003111102338491835</v>
       </c>
       <c r="F16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G16" t="n">
-        <v>0.001145782448783172</v>
+        <v>0.0005163308746648943</v>
       </c>
       <c r="H16" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1185070533412098</v>
+        <v>0.2340226057029207</v>
       </c>
       <c r="J16" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="K16" t="n">
-        <v>18</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="17">
@@ -1052,35 +1052,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.00172816822723828</v>
+        <v>0.002762273593031033</v>
       </c>
       <c r="D17" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E17" t="n">
-        <v>0.001615668932758181</v>
+        <v>0.001419189509467566</v>
       </c>
       <c r="F17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0003341763919277096</v>
+        <v>0.001418341798518774</v>
       </c>
       <c r="H17" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2099184335506039</v>
+        <v>0.1180221293205901</v>
       </c>
       <c r="J17" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="K17" t="n">
-        <v>19.25</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="18">
@@ -1089,35 +1089,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.001120522902745008</v>
+        <v>0.001286513995876753</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E18" t="n">
-        <v>0.004567903659766977</v>
+        <v>0.004702194856392487</v>
       </c>
       <c r="F18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0002236489103918382</v>
+        <v>0.0008693145273346636</v>
       </c>
       <c r="H18" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2699523346893602</v>
+        <v>0.1735836979765957</v>
       </c>
       <c r="J18" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K18" t="n">
-        <v>19.25</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="19">
@@ -1126,35 +1126,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.002098015267490606</v>
+        <v>0.001054191241998614</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="E19" t="n">
-        <v>0.001007405018429065</v>
+        <v>0.01618550000229439</v>
       </c>
       <c r="F19" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0005098336434348871</v>
+        <v>0.0004423379304002162</v>
       </c>
       <c r="H19" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1970921910273393</v>
+        <v>0.1823608994384267</v>
       </c>
       <c r="J19" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K19" t="n">
-        <v>19.5</v>
+        <v>21.25</v>
       </c>
     </row>
     <row r="20">
@@ -1163,35 +1163,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.002304380354737607</v>
+        <v>0.002810508167941568</v>
       </c>
       <c r="D20" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E20" t="n">
-        <v>0.001390887528241558</v>
+        <v>0.001439214563866091</v>
       </c>
       <c r="F20" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G20" t="n">
-        <v>0.001391474375185242</v>
+        <v>0.0009432406102126811</v>
       </c>
       <c r="H20" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1162677246604455</v>
+        <v>0.07732935516363204</v>
       </c>
       <c r="J20" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K20" t="n">
-        <v>20</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="21">
@@ -1200,35 +1200,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.002070767412814615</v>
+        <v>0.001720089984688739</v>
       </c>
       <c r="D21" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E21" t="n">
-        <v>0.001507996316891902</v>
+        <v>0.0007311182513651744</v>
       </c>
       <c r="F21" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0003862927800954319</v>
+        <v>0.000595107814295226</v>
       </c>
       <c r="H21" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1497267572983745</v>
+        <v>0.1957868200241759</v>
       </c>
       <c r="J21" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="K21" t="n">
-        <v>21.5</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="22">
@@ -1237,35 +1237,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0005362323470610934</v>
+        <v>0.002909470592682274</v>
       </c>
       <c r="D22" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="E22" t="n">
-        <v>0.01125009811016086</v>
+        <v>0.001265407323093007</v>
       </c>
       <c r="F22" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0002159719791944514</v>
+        <v>0.0006929705807025899</v>
       </c>
       <c r="H22" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="I22" t="n">
-        <v>0.164502853842124</v>
+        <v>0.04897320932359284</v>
       </c>
       <c r="J22" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="K22" t="n">
-        <v>25.5</v>
+        <v>23.75</v>
       </c>
     </row>
     <row r="23">
@@ -1274,35 +1274,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.001513857969896613</v>
+        <v>0.000794158586155244</v>
       </c>
       <c r="D23" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E23" t="n">
-        <v>0.001187015199766706</v>
+        <v>0.004727037795364303</v>
       </c>
       <c r="F23" t="n">
+        <v>9</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.0004413010327554368</v>
+      </c>
+      <c r="H23" t="n">
         <v>27</v>
       </c>
-      <c r="G23" t="n">
-        <v>0.0005605871611486068</v>
-      </c>
-      <c r="H23" t="n">
-        <v>16</v>
-      </c>
       <c r="I23" t="n">
-        <v>0.08158316046622227</v>
+        <v>0.1560008877185812</v>
       </c>
       <c r="J23" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="K23" t="n">
-        <v>26.5</v>
+        <v>23.75</v>
       </c>
     </row>
     <row r="24">
@@ -1311,35 +1311,35 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0004363512307099286</v>
+        <v>0.001693948384797109</v>
       </c>
       <c r="D24" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="E24" t="n">
-        <v>0.003702193952719148</v>
+        <v>0.0009289707036896339</v>
       </c>
       <c r="F24" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0002414067048766122</v>
+        <v>0.0008730662985472093</v>
       </c>
       <c r="H24" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1565064608513327</v>
+        <v>0.1130216009059368</v>
       </c>
       <c r="J24" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K24" t="n">
-        <v>27</v>
+        <v>23.75</v>
       </c>
     </row>
     <row r="25">
@@ -1348,35 +1348,35 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.00150882294158987</v>
+        <v>0.002539953446936925</v>
       </c>
       <c r="D25" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0008062156514389453</v>
+        <v>0.002559564591866301</v>
       </c>
       <c r="F25" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0002136535776238402</v>
+        <v>0.0003927869951789398</v>
       </c>
       <c r="H25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1298072021325805</v>
+        <v>0.08489930078051477</v>
       </c>
       <c r="J25" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K25" t="n">
-        <v>27.5</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="26">
@@ -1385,35 +1385,35 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0009522636881491705</v>
+        <v>0.002552982439491429</v>
       </c>
       <c r="D26" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0006732612970896623</v>
+        <v>0.00249512805053121</v>
       </c>
       <c r="F26" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0002883913801752902</v>
+        <v>0.00046241937193372</v>
       </c>
       <c r="H26" t="n">
         <v>25</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1856278187338714</v>
+        <v>0.07462187000962528</v>
       </c>
       <c r="J26" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="K26" t="n">
-        <v>27.75</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27">
@@ -1422,35 +1422,35 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.001515130979630339</v>
+        <v>0.00147717075865967</v>
       </c>
       <c r="D27" t="n">
+        <v>30</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.0008271250420117048</v>
+      </c>
+      <c r="F27" t="n">
+        <v>31</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.0006838526750083229</v>
+      </c>
+      <c r="H27" t="n">
         <v>20</v>
       </c>
-      <c r="E27" t="n">
-        <v>0.001520091012321579</v>
-      </c>
-      <c r="F27" t="n">
-        <v>22</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.0002084405193222505</v>
-      </c>
-      <c r="H27" t="n">
-        <v>30</v>
-      </c>
       <c r="I27" t="n">
-        <v>0.08252037876710538</v>
+        <v>0.1142654146941351</v>
       </c>
       <c r="J27" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="K27" t="n">
-        <v>28.25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28">
@@ -1459,35 +1459,35 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.001341357539773777</v>
+        <v>0.002041988285243256</v>
       </c>
       <c r="D28" t="n">
+        <v>21</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.00099474203484279</v>
+      </c>
+      <c r="F28" t="n">
         <v>24</v>
       </c>
-      <c r="E28" t="n">
-        <v>0.002163976082863802</v>
-      </c>
-      <c r="F28" t="n">
-        <v>18</v>
-      </c>
       <c r="G28" t="n">
-        <v>0.0001532722460015789</v>
+        <v>0.0006375918345603582</v>
       </c>
       <c r="H28" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I28" t="n">
-        <v>0.08700539601290069</v>
+        <v>0.02495406817277646</v>
       </c>
       <c r="J28" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K28" t="n">
-        <v>28.75</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29">
@@ -1496,35 +1496,35 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.001057008366663852</v>
+        <v>0.002757126263052136</v>
       </c>
       <c r="D29" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E29" t="n">
-        <v>0.001314113320092398</v>
+        <v>0.0008611854707114771</v>
       </c>
       <c r="F29" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.0001482043522034182</v>
+        <v>-0.0001493895613445373</v>
       </c>
       <c r="H29" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2445728104993856</v>
+        <v>0.1357969386610014</v>
       </c>
       <c r="J29" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K29" t="n">
-        <v>29.5</v>
+        <v>28.25</v>
       </c>
     </row>
     <row r="30">
@@ -1533,35 +1533,35 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.000377705185052018</v>
+        <v>0.001907087718766144</v>
       </c>
       <c r="D30" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="E30" t="n">
-        <v>0.003742085099515727</v>
+        <v>0.0008962976729432869</v>
       </c>
       <c r="F30" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0001380282076579475</v>
+        <v>0.0003477123464230347</v>
       </c>
       <c r="H30" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1528703251648047</v>
+        <v>0.07635038632091495</v>
       </c>
       <c r="J30" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="K30" t="n">
-        <v>29.5</v>
+        <v>28.75</v>
       </c>
     </row>
     <row r="31">
@@ -1570,35 +1570,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.001454772416828421</v>
+        <v>0.001296050839580883</v>
       </c>
       <c r="D31" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0008447516085020126</v>
+        <v>0.0005305902171772095</v>
       </c>
       <c r="F31" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0003850525447717357</v>
+        <v>0.0002985524944571938</v>
       </c>
       <c r="H31" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="I31" t="n">
-        <v>0.05192730137918167</v>
+        <v>0.1529091726203493</v>
       </c>
       <c r="J31" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="K31" t="n">
-        <v>29.75</v>
+        <v>30.25</v>
       </c>
     </row>
     <row r="32">
@@ -1607,35 +1607,35 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.000916513161122735</v>
+        <v>0.001705798275019369</v>
       </c>
       <c r="D32" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0005541881264318136</v>
+        <v>0.0008746217417649041</v>
       </c>
       <c r="F32" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0005800150786269609</v>
+        <v>-9.266529633634723e-05</v>
       </c>
       <c r="H32" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1206952753538957</v>
+        <v>0.1152474317326098</v>
       </c>
       <c r="J32" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="K32" t="n">
-        <v>30</v>
+        <v>30.25</v>
       </c>
     </row>
     <row r="33">
@@ -1644,35 +1644,35 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0008008563505270567</v>
+        <v>0.001305654385882244</v>
       </c>
       <c r="D33" t="n">
+        <v>32</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.0006584017832055801</v>
+      </c>
+      <c r="F33" t="n">
+        <v>39</v>
+      </c>
+      <c r="G33" t="n">
+        <v>6.726249614478209e-05</v>
+      </c>
+      <c r="H33" t="n">
         <v>37</v>
       </c>
-      <c r="E33" t="n">
-        <v>0.00150957324182963</v>
-      </c>
-      <c r="F33" t="n">
-        <v>23</v>
-      </c>
-      <c r="G33" t="n">
-        <v>-4.068710041987833e-05</v>
-      </c>
-      <c r="H33" t="n">
-        <v>47</v>
-      </c>
       <c r="I33" t="n">
-        <v>0.1922289003748792</v>
+        <v>0.1515377957846171</v>
       </c>
       <c r="J33" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K33" t="n">
-        <v>31</v>
+        <v>31.75</v>
       </c>
     </row>
     <row r="34">
@@ -1681,35 +1681,35 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0008702463468832406</v>
+        <v>0.001708731035198922</v>
       </c>
       <c r="D34" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0006517038630517026</v>
+        <v>0.0008618206941963109</v>
       </c>
       <c r="F34" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0005449226424682596</v>
+        <v>-0.00017887632103607</v>
       </c>
       <c r="H34" t="n">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1085555176625839</v>
+        <v>0.110278035031449</v>
       </c>
       <c r="J34" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="K34" t="n">
-        <v>31.25</v>
+        <v>32.25</v>
       </c>
     </row>
     <row r="35">
@@ -1718,35 +1718,35 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.001138417740080813</v>
+        <v>0.001679927528702336</v>
       </c>
       <c r="D35" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0007635461142474171</v>
+        <v>0.0007680245164467326</v>
       </c>
       <c r="F35" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0004150406246040683</v>
+        <v>2.309187967508564e-08</v>
       </c>
       <c r="H35" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="I35" t="n">
-        <v>0.02854832884313652</v>
+        <v>0.1127681090016961</v>
       </c>
       <c r="J35" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="K35" t="n">
-        <v>31.75</v>
+        <v>32.25</v>
       </c>
     </row>
     <row r="36">
@@ -1755,35 +1755,35 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.001181690860545219</v>
+        <v>0.00161321677024449</v>
       </c>
       <c r="D36" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0008055574988482754</v>
+        <v>0.0008746126141395107</v>
       </c>
       <c r="F36" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0001731946225882352</v>
+        <v>0.0001191017083218338</v>
       </c>
       <c r="H36" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I36" t="n">
-        <v>0.05864846358770226</v>
+        <v>0.04348365168062962</v>
       </c>
       <c r="J36" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="K36" t="n">
-        <v>33.25</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="37">
@@ -1792,35 +1792,35 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.0008376408666977825</v>
+        <v>0.001329182969738892</v>
       </c>
       <c r="D37" t="n">
+        <v>31</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.0007690661926937902</v>
+      </c>
+      <c r="F37" t="n">
+        <v>32</v>
+      </c>
+      <c r="G37" t="n">
+        <v>9.519455031692381e-05</v>
+      </c>
+      <c r="H37" t="n">
         <v>35</v>
       </c>
-      <c r="E37" t="n">
-        <v>0.0007696003419973514</v>
-      </c>
-      <c r="F37" t="n">
+      <c r="I37" t="n">
+        <v>0.08280586501887521</v>
+      </c>
+      <c r="J37" t="n">
+        <v>34</v>
+      </c>
+      <c r="K37" t="n">
         <v>33</v>
-      </c>
-      <c r="G37" t="n">
-        <v>3.591056691265582e-05</v>
-      </c>
-      <c r="H37" t="n">
-        <v>40</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0.1047114309968094</v>
-      </c>
-      <c r="J37" t="n">
-        <v>37</v>
-      </c>
-      <c r="K37" t="n">
-        <v>36.25</v>
       </c>
     </row>
     <row r="38">
@@ -1829,35 +1829,35 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.0007810272148245259</v>
+        <v>0.001270206898598093</v>
       </c>
       <c r="D38" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0008084613405911065</v>
+        <v>0.0006928392236250525</v>
       </c>
       <c r="F38" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G38" t="n">
-        <v>5.232347753778566e-05</v>
+        <v>-0.0001096590214565651</v>
       </c>
       <c r="H38" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I38" t="n">
-        <v>0.09661113621317829</v>
+        <v>0.1374381455440177</v>
       </c>
       <c r="J38" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="K38" t="n">
-        <v>36.75</v>
+        <v>33.75</v>
       </c>
     </row>
     <row r="39">
@@ -1866,35 +1866,35 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.0007886382891927533</v>
+        <v>0.0004743682278885443</v>
       </c>
       <c r="D39" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E39" t="n">
-        <v>0.000473285230597837</v>
+        <v>0.0007527526867759039</v>
       </c>
       <c r="F39" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="G39" t="n">
-        <v>0.000120363968992343</v>
+        <v>0.0007143119240637152</v>
       </c>
       <c r="H39" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1483923472772828</v>
+        <v>0.01945995009064694</v>
       </c>
       <c r="J39" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="K39" t="n">
-        <v>37</v>
+        <v>34.25</v>
       </c>
     </row>
     <row r="40">
@@ -1903,35 +1903,35 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0007627874299100361</v>
+        <v>0.001268981248178545</v>
       </c>
       <c r="D40" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0005991046630545348</v>
+        <v>0.0006612626900219606</v>
       </c>
       <c r="F40" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0001509396737492619</v>
+        <v>0.0001243027744033398</v>
       </c>
       <c r="H40" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1133977684273755</v>
+        <v>0.0971811977419299</v>
       </c>
       <c r="J40" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="K40" t="n">
-        <v>37.75</v>
+        <v>34.25</v>
       </c>
     </row>
     <row r="41">
@@ -1940,35 +1940,35 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.0002408052716201546</v>
+        <v>0.001149302216853362</v>
       </c>
       <c r="D41" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0007577331771416256</v>
+        <v>0.0006819145901886573</v>
       </c>
       <c r="F41" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0003921249062823762</v>
+        <v>0.0002163397078089324</v>
       </c>
       <c r="H41" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="I41" t="n">
-        <v>0.03575821798885048</v>
+        <v>0.09299207544495491</v>
       </c>
       <c r="J41" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="K41" t="n">
-        <v>38</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="42">
@@ -1977,35 +1977,35 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.0008520993791585219</v>
+        <v>0.00115240439237116</v>
       </c>
       <c r="D42" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0006693908937211823</v>
+        <v>0.0004708182292193955</v>
       </c>
       <c r="F42" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G42" t="n">
-        <v>-3.91240558361261e-05</v>
+        <v>-5.299632575959112e-05</v>
       </c>
       <c r="H42" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1105996765571509</v>
+        <v>0.1239600995440173</v>
       </c>
       <c r="J42" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="K42" t="n">
-        <v>38.25</v>
+        <v>35.75</v>
       </c>
     </row>
     <row r="43">
@@ -2014,35 +2014,35 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.0008210796582656164</v>
+        <v>0.0009566632865668383</v>
       </c>
       <c r="D43" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0006060443852796497</v>
+        <v>0.0005189372648662991</v>
       </c>
       <c r="F43" t="n">
         <v>41</v>
       </c>
       <c r="G43" t="n">
-        <v>0.000104602391677211</v>
+        <v>0.0001042134583107202</v>
       </c>
       <c r="H43" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I43" t="n">
-        <v>0.08866143799683179</v>
+        <v>0.08011231981302425</v>
       </c>
       <c r="J43" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="K43" t="n">
-        <v>38.25</v>
+        <v>37.75</v>
       </c>
     </row>
     <row r="44">
@@ -2051,35 +2051,35 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.001008763431202688</v>
+        <v>0.0009749359206845308</v>
       </c>
       <c r="D44" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E44" t="n">
-        <v>0.000678486272436789</v>
+        <v>0.0004536554020301777</v>
       </c>
       <c r="F44" t="n">
+        <v>43</v>
+      </c>
+      <c r="G44" t="n">
+        <v>6.860885122702553e-05</v>
+      </c>
+      <c r="H44" t="n">
         <v>36</v>
       </c>
-      <c r="G44" t="n">
-        <v>-5.288512301337978e-06</v>
-      </c>
-      <c r="H44" t="n">
-        <v>42</v>
-      </c>
       <c r="I44" t="n">
-        <v>0.04812936651390975</v>
+        <v>0.003844176778656117</v>
       </c>
       <c r="J44" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="K44" t="n">
-        <v>38.25</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="45">
@@ -2088,35 +2088,35 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.0008945854852691556</v>
+        <v>0.0001475507005105964</v>
       </c>
       <c r="D45" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0006152696280402195</v>
+        <v>0.0003942476044229266</v>
       </c>
       <c r="F45" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G45" t="n">
-        <v>-9.690869983760563e-05</v>
+        <v>2.999320981821318e-05</v>
       </c>
       <c r="H45" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1163760253988069</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="K45" t="n">
-        <v>38.5</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="46">
@@ -2125,331 +2125,35 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.0007010385881878948</v>
+        <v>5.174296782901289e-05</v>
       </c>
       <c r="D46" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0005032273324813749</v>
+        <v>8.257540495447311e-05</v>
       </c>
       <c r="F46" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G46" t="n">
-        <v>-3.656031711293251e-05</v>
+        <v>-3.20763687813308e-06</v>
       </c>
       <c r="H46" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1465052836719529</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="K46" t="n">
-        <v>40.25</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>boiling_r3_q</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>0.0007860913800429601</v>
-      </c>
-      <c r="D47" t="n">
-        <v>39</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0.0004350090070727275</v>
-      </c>
-      <c r="F47" t="n">
-        <v>50</v>
-      </c>
-      <c r="G47" t="n">
-        <v>-0.0001800433885698061</v>
-      </c>
-      <c r="H47" t="n">
-        <v>52</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0.1250352999412252</v>
-      </c>
-      <c r="J47" t="n">
-        <v>29</v>
-      </c>
-      <c r="K47" t="n">
-        <v>42.5</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>wastewater_r3_q</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>0.0006956934320526728</v>
-      </c>
-      <c r="D48" t="n">
-        <v>44</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0.0005465299748814707</v>
-      </c>
-      <c r="F48" t="n">
-        <v>46</v>
-      </c>
-      <c r="G48" t="n">
-        <v>-0.0003104006152106375</v>
-      </c>
-      <c r="H48" t="n">
-        <v>53</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0.1328690731507498</v>
-      </c>
-      <c r="J48" t="n">
-        <v>27</v>
-      </c>
-      <c r="K48" t="n">
-        <v>42.5</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>boiling_r3_pol</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>0.0007534038063470834</v>
-      </c>
-      <c r="D49" t="n">
-        <v>42</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0.0004753247668537219</v>
-      </c>
-      <c r="F49" t="n">
-        <v>48</v>
-      </c>
-      <c r="G49" t="n">
-        <v>-5.153761794980394e-05</v>
-      </c>
-      <c r="H49" t="n">
-        <v>49</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0.07873252507831374</v>
-      </c>
-      <c r="J49" t="n">
-        <v>43</v>
-      </c>
-      <c r="K49" t="n">
-        <v>45.5</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>white_quality_moisture_2</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>0.0002750096584171437</v>
-      </c>
-      <c r="D50" t="n">
-        <v>48</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0.0005657369744712369</v>
-      </c>
-      <c r="F50" t="n">
-        <v>44</v>
-      </c>
-      <c r="G50" t="n">
-        <v>-1.626303324265832e-05</v>
-      </c>
-      <c r="H50" t="n">
-        <v>43</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0.0006290865065095019</v>
-      </c>
-      <c r="J50" t="n">
-        <v>51</v>
-      </c>
-      <c r="K50" t="n">
-        <v>46.5</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>lime_milk_baume</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>0.0002447343960500336</v>
-      </c>
-      <c r="D51" t="n">
-        <v>49</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0.000252947062030458</v>
-      </c>
-      <c r="F51" t="n">
-        <v>52</v>
-      </c>
-      <c r="G51" t="n">
-        <v>6.202459662519866e-05</v>
-      </c>
-      <c r="H51" t="n">
-        <v>38</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0.004620886376301314</v>
-      </c>
-      <c r="J51" t="n">
-        <v>50</v>
-      </c>
-      <c r="K51" t="n">
-        <v>47.25</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>white_quality_moisture_1</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>0.0002253675461468919</v>
-      </c>
-      <c r="D52" t="n">
-        <v>51</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0.0005806074086627955</v>
-      </c>
-      <c r="F52" t="n">
-        <v>43</v>
-      </c>
-      <c r="G52" t="n">
-        <v>-4.815492907950247e-05</v>
-      </c>
-      <c r="H52" t="n">
-        <v>48</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0.01525040081228823</v>
-      </c>
-      <c r="J52" t="n">
-        <v>49</v>
-      </c>
-      <c r="K52" t="n">
-        <v>47.75</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>boiler_hardness</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>6.689902203393797e-05</v>
-      </c>
-      <c r="D53" t="n">
-        <v>52</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0.0003763646132431509</v>
-      </c>
-      <c r="F53" t="n">
-        <v>51</v>
-      </c>
-      <c r="G53" t="n">
-        <v>1.240458790938703e-05</v>
-      </c>
-      <c r="H53" t="n">
-        <v>41</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="n">
-        <v>52</v>
-      </c>
-      <c r="K53" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>shift_name</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>3.644830138190724e-05</v>
-      </c>
-      <c r="D54" t="n">
-        <v>53</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0.0001688619585249289</v>
-      </c>
-      <c r="F54" t="n">
-        <v>53</v>
-      </c>
-      <c r="G54" t="n">
-        <v>-2.786894234031445e-05</v>
-      </c>
-      <c r="H54" t="n">
-        <v>44</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="n">
-        <v>52</v>
-      </c>
-      <c r="K54" t="n">
-        <v>50.5</v>
+        <v>43.5</v>
       </c>
     </row>
   </sheetData>
@@ -2533,31 +2237,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3509264667099231</v>
+        <v>0.4631551263978727</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3273009785562683</v>
+        <v>0.4354256942335763</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3598793571410547</v>
+        <v>0.7224825652776311</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1.197596762489799</v>
+        <v>1.197226875819409</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -2566,35 +2270,35 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2430083986073938</v>
+        <v>0.1448121411127521</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2341821975658129</v>
+        <v>0.1013739829994583</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2813470101326703</v>
+        <v>0.05593059693425771</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>1.220162286626203</v>
+        <v>0.6036619723165955</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
-        <v>1.75</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="4">
@@ -2603,32 +2307,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1136888176080379</v>
+        <v>0.1396444272155124</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.202284502935228</v>
+        <v>0.01913738835731541</v>
       </c>
       <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.04754782163519602</v>
+      </c>
+      <c r="H4" t="n">
         <v>3</v>
       </c>
-      <c r="G4" t="n">
-        <v>0.03188475108235687</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4</v>
-      </c>
       <c r="I4" t="n">
-        <v>0.6066707781972243</v>
+        <v>0.6141018072778577</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
         <v>4.25</v>
@@ -2640,32 +2344,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.1216747028217113</v>
+        <v>0.02636596662579262</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08437781417749506</v>
+        <v>0.01990592942979598</v>
       </c>
       <c r="F5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.04493023010480252</v>
+      </c>
+      <c r="H5" t="n">
         <v>4</v>
       </c>
-      <c r="G5" t="n">
-        <v>0.04164666952274031</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3</v>
-      </c>
       <c r="I5" t="n">
-        <v>0.595591263334927</v>
+        <v>0.6246955590411227</v>
       </c>
       <c r="J5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
         <v>4.5</v>
@@ -2677,35 +2381,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.09170833013467054</v>
+        <v>0.1331106287933128</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01261148354771118</v>
+        <v>0.2879053195239505</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02157996931448739</v>
+        <v>0.04450525608057554</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6149920332849157</v>
+        <v>0.6022214060763087</v>
       </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="7">
@@ -2714,35 +2418,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01179176619992063</v>
+        <v>0.00828411418578723</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0125716311096866</v>
+        <v>0.009696906563716166</v>
       </c>
       <c r="F7" t="n">
         <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01200704749597883</v>
+        <v>0.0068005622638733</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6059710037229373</v>
+        <v>0.8714167049095849</v>
       </c>
       <c r="J7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>6.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -2751,35 +2455,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.006322868406578661</v>
+        <v>0.008586265363717871</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>0.006797540172290032</v>
+        <v>0.05082021444524421</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004525107807768625</v>
+        <v>0.00105586038311577</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8723113670408211</v>
+        <v>0.9694040788023274</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>7.25</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="9">
@@ -2788,35 +2492,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.005621442661865416</v>
+        <v>0.005710278243218773</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01914241201728629</v>
+        <v>0.00433443817214928</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G9" t="n">
-        <v>0.005298272783865155</v>
+        <v>0.002484865916395507</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2717957000954292</v>
+        <v>0.47636999799035</v>
       </c>
       <c r="J9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>7.75</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="10">
@@ -2825,35 +2529,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.003044858379230276</v>
+        <v>0.005696968220380511</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>0.03151805388149846</v>
+        <v>0.002951505311773142</v>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0003725391789113563</v>
+        <v>0.004291247703178835</v>
       </c>
       <c r="H10" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="I10" t="n">
-        <v>1.032026958462696</v>
+        <v>0.1817267023553764</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K10" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="11">
@@ -2862,35 +2566,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.003738895770907981</v>
+        <v>0.00302537037209505</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>0.006383871055968616</v>
+        <v>0.004482480251171447</v>
       </c>
       <c r="F11" t="n">
         <v>11</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001006899723146582</v>
+        <v>0.001160984115541563</v>
       </c>
       <c r="H11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2636575744571474</v>
+        <v>0.215175382121823</v>
       </c>
       <c r="J11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K11" t="n">
-        <v>11.5</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="12">
@@ -2899,35 +2603,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.002699248342943198</v>
+        <v>0.004854647722158108</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>0.001671672701943038</v>
+        <v>0.002997389936709667</v>
       </c>
       <c r="F12" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G12" t="n">
-        <v>0.001066831892333719</v>
+        <v>0.002581567689486497</v>
       </c>
       <c r="H12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1883237605390065</v>
+        <v>0.1200999449624831</v>
       </c>
       <c r="J12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K12" t="n">
-        <v>15.25</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="13">
@@ -2936,35 +2640,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001648145579726441</v>
+        <v>0.003187194930810727</v>
       </c>
       <c r="D13" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>0.002453077075937192</v>
+        <v>0.002671425196684824</v>
       </c>
       <c r="F13" t="n">
         <v>17</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0005687225825380838</v>
+        <v>0.00211519601732254</v>
       </c>
       <c r="H13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2125263033038287</v>
+        <v>0.1430107500986084</v>
       </c>
       <c r="J13" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K13" t="n">
-        <v>16.25</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="14">
@@ -2973,32 +2677,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.00401375600794517</v>
+        <v>0.003086284536756752</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>0.002790204142766983</v>
+        <v>0.001709246053542684</v>
       </c>
       <c r="F14" t="n">
+        <v>20</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.0008640450036720093</v>
+      </c>
+      <c r="H14" t="n">
+        <v>17</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1660814131995023</v>
+      </c>
+      <c r="J14" t="n">
         <v>16</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.0002072136151259229</v>
-      </c>
-      <c r="H14" t="n">
-        <v>31</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.4961557840490896</v>
-      </c>
-      <c r="J14" t="n">
-        <v>9</v>
       </c>
       <c r="K14" t="n">
         <v>16.25</v>
@@ -3010,32 +2714,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.002245715045750216</v>
+        <v>0.001997492757429873</v>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E15" t="n">
-        <v>0.00152358979170372</v>
+        <v>0.003398160462251813</v>
       </c>
       <c r="F15" t="n">
+        <v>13</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.0006637387286543949</v>
+      </c>
+      <c r="H15" t="n">
         <v>21</v>
       </c>
-      <c r="G15" t="n">
-        <v>0.001319066452784934</v>
-      </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
+        <v>0.2255469942945947</v>
+      </c>
+      <c r="J15" t="n">
         <v>10</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.1581573980849016</v>
-      </c>
-      <c r="J15" t="n">
-        <v>21</v>
       </c>
       <c r="K15" t="n">
         <v>16.5</v>
@@ -3047,35 +2751,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.00217139327705321</v>
+        <v>0.002090912399233735</v>
       </c>
       <c r="D16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E16" t="n">
-        <v>0.002930754602353963</v>
+        <v>0.003111102338491835</v>
       </c>
       <c r="F16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G16" t="n">
-        <v>0.001145782448783172</v>
+        <v>0.0005163308746648943</v>
       </c>
       <c r="H16" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1185070533412098</v>
+        <v>0.2340226057029207</v>
       </c>
       <c r="J16" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="K16" t="n">
-        <v>18</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="17">
@@ -3084,35 +2788,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.00172816822723828</v>
+        <v>0.002762273593031033</v>
       </c>
       <c r="D17" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E17" t="n">
-        <v>0.001615668932758181</v>
+        <v>0.001419189509467566</v>
       </c>
       <c r="F17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0003341763919277096</v>
+        <v>0.001418341798518774</v>
       </c>
       <c r="H17" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2099184335506039</v>
+        <v>0.1180221293205901</v>
       </c>
       <c r="J17" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="K17" t="n">
-        <v>19.25</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="18">
@@ -3121,35 +2825,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.001120522902745008</v>
+        <v>0.001286513995876753</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E18" t="n">
-        <v>0.004567903659766977</v>
+        <v>0.004702194856392487</v>
       </c>
       <c r="F18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0002236489103918382</v>
+        <v>0.0008693145273346636</v>
       </c>
       <c r="H18" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2699523346893602</v>
+        <v>0.1735836979765957</v>
       </c>
       <c r="J18" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K18" t="n">
-        <v>19.25</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="19">
@@ -3158,35 +2862,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.002098015267490606</v>
+        <v>0.001054191241998614</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="E19" t="n">
-        <v>0.001007405018429065</v>
+        <v>0.01618550000229439</v>
       </c>
       <c r="F19" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0005098336434348871</v>
+        <v>0.0004423379304002162</v>
       </c>
       <c r="H19" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1970921910273393</v>
+        <v>0.1823608994384267</v>
       </c>
       <c r="J19" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K19" t="n">
-        <v>19.5</v>
+        <v>21.25</v>
       </c>
     </row>
     <row r="20">
@@ -3195,35 +2899,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.002304380354737607</v>
+        <v>0.002810508167941568</v>
       </c>
       <c r="D20" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E20" t="n">
-        <v>0.001390887528241558</v>
+        <v>0.001439214563866091</v>
       </c>
       <c r="F20" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G20" t="n">
-        <v>0.001391474375185242</v>
+        <v>0.0009432406102126811</v>
       </c>
       <c r="H20" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1162677246604455</v>
+        <v>0.07732935516363204</v>
       </c>
       <c r="J20" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K20" t="n">
-        <v>20</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="21">
@@ -3232,35 +2936,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.002070767412814615</v>
+        <v>0.001720089984688739</v>
       </c>
       <c r="D21" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E21" t="n">
-        <v>0.001507996316891902</v>
+        <v>0.0007311182513651744</v>
       </c>
       <c r="F21" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0003862927800954319</v>
+        <v>0.000595107814295226</v>
       </c>
       <c r="H21" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1497267572983745</v>
+        <v>0.1957868200241759</v>
       </c>
       <c r="J21" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="K21" t="n">
-        <v>21.5</v>
+        <v>23.5</v>
       </c>
     </row>
   </sheetData>
@@ -3274,7 +2978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3304,7 +3008,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3509264667099231</v>
+        <v>0.4631551263978727</v>
       </c>
     </row>
     <row r="3">
@@ -3313,11 +3017,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2430083986073938</v>
+        <v>0.1448121411127521</v>
       </c>
     </row>
     <row r="4">
@@ -3326,11 +3030,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1216747028217113</v>
+        <v>0.1396444272155124</v>
       </c>
     </row>
     <row r="5">
@@ -3343,7 +3047,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.1136888176080379</v>
+        <v>0.1331106287933128</v>
       </c>
     </row>
     <row r="6">
@@ -3352,11 +3056,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.09170833013467054</v>
+        <v>0.02636596662579262</v>
       </c>
     </row>
     <row r="7">
@@ -3365,11 +3069,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01179176619992063</v>
+        <v>0.008586265363717871</v>
       </c>
     </row>
     <row r="8">
@@ -3382,7 +3086,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.006322868406578661</v>
+        <v>0.00828411418578723</v>
       </c>
     </row>
     <row r="9">
@@ -3391,11 +3095,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.005621442661865416</v>
+        <v>0.005710278243218773</v>
       </c>
     </row>
     <row r="10">
@@ -3404,11 +3108,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.00401375600794517</v>
+        <v>0.005696968220380511</v>
       </c>
     </row>
     <row r="11">
@@ -3417,11 +3121,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.003738895770907981</v>
+        <v>0.004854647722158108</v>
       </c>
     </row>
     <row r="12">
@@ -3430,11 +3134,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.003044858379230276</v>
+        <v>0.003187194930810727</v>
       </c>
     </row>
     <row r="13">
@@ -3443,11 +3147,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.002699248342943198</v>
+        <v>0.003086284536756752</v>
       </c>
     </row>
     <row r="14">
@@ -3456,11 +3160,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.002304380354737607</v>
+        <v>0.00302537037209505</v>
       </c>
     </row>
     <row r="15">
@@ -3469,11 +3173,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.002245715045750216</v>
+        <v>0.002909470592682274</v>
       </c>
     </row>
     <row r="16">
@@ -3482,11 +3186,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.00217139327705321</v>
+        <v>0.002810508167941568</v>
       </c>
     </row>
     <row r="17">
@@ -3495,11 +3199,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.002098015267490606</v>
+        <v>0.002762273593031033</v>
       </c>
     </row>
     <row r="18">
@@ -3508,11 +3212,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.002070767412814615</v>
+        <v>0.002757126263052136</v>
       </c>
     </row>
     <row r="19">
@@ -3521,11 +3225,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.00172816822723828</v>
+        <v>0.002552982439491429</v>
       </c>
     </row>
     <row r="20">
@@ -3534,11 +3238,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.001648145579726441</v>
+        <v>0.002539953446936925</v>
       </c>
     </row>
     <row r="21">
@@ -3547,11 +3251,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.001515130979630339</v>
+        <v>0.002090912399233735</v>
       </c>
     </row>
     <row r="22">
@@ -3560,11 +3264,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.001513857969896613</v>
+        <v>0.002041988285243256</v>
       </c>
     </row>
     <row r="23">
@@ -3573,11 +3277,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.00150882294158987</v>
+        <v>0.001997492757429873</v>
       </c>
     </row>
     <row r="24">
@@ -3586,11 +3290,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.001454772416828421</v>
+        <v>0.001907087718766144</v>
       </c>
     </row>
     <row r="25">
@@ -3599,11 +3303,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.001341357539773777</v>
+        <v>0.001720089984688739</v>
       </c>
     </row>
     <row r="26">
@@ -3612,11 +3316,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.001181690860545219</v>
+        <v>0.001708731035198922</v>
       </c>
     </row>
     <row r="27">
@@ -3625,11 +3329,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.001138417740080813</v>
+        <v>0.001705798275019369</v>
       </c>
     </row>
     <row r="28">
@@ -3638,11 +3342,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.001120522902745008</v>
+        <v>0.001693948384797109</v>
       </c>
     </row>
     <row r="29">
@@ -3651,11 +3355,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.001057008366663852</v>
+        <v>0.001679927528702336</v>
       </c>
     </row>
     <row r="30">
@@ -3668,7 +3372,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.001008763431202688</v>
+        <v>0.00161321677024449</v>
       </c>
     </row>
     <row r="31">
@@ -3677,11 +3381,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0009522636881491705</v>
+        <v>0.00147717075865967</v>
       </c>
     </row>
     <row r="32">
@@ -3690,11 +3394,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.000916513161122735</v>
+        <v>0.001329182969738892</v>
       </c>
     </row>
     <row r="33">
@@ -3703,11 +3407,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0008945854852691556</v>
+        <v>0.001305654385882244</v>
       </c>
     </row>
     <row r="34">
@@ -3716,11 +3420,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0008702463468832406</v>
+        <v>0.001296050839580883</v>
       </c>
     </row>
     <row r="35">
@@ -3729,11 +3433,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0008520993791585219</v>
+        <v>0.001286513995876753</v>
       </c>
     </row>
     <row r="36">
@@ -3742,11 +3446,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0008376408666977825</v>
+        <v>0.001270206898598093</v>
       </c>
     </row>
     <row r="37">
@@ -3755,11 +3459,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.0008210796582656164</v>
+        <v>0.001268981248178545</v>
       </c>
     </row>
     <row r="38">
@@ -3768,11 +3472,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.0008008563505270567</v>
+        <v>0.00115240439237116</v>
       </c>
     </row>
     <row r="39">
@@ -3781,11 +3485,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.0007886382891927533</v>
+        <v>0.001149302216853362</v>
       </c>
     </row>
     <row r="40">
@@ -3794,11 +3498,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0007860913800429601</v>
+        <v>0.001054191241998614</v>
       </c>
     </row>
     <row r="41">
@@ -3807,11 +3511,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.0007810272148245259</v>
+        <v>0.0009749359206845308</v>
       </c>
     </row>
     <row r="42">
@@ -3820,11 +3524,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.0007627874299100361</v>
+        <v>0.0009566632865668383</v>
       </c>
     </row>
     <row r="43">
@@ -3833,11 +3537,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.0007534038063470834</v>
+        <v>0.000794158586155244</v>
       </c>
     </row>
     <row r="44">
@@ -3846,11 +3550,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.0007010385881878948</v>
+        <v>0.0004743682278885443</v>
       </c>
     </row>
     <row r="45">
@@ -3859,11 +3563,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.0006956934320526728</v>
+        <v>0.0001475507005105964</v>
       </c>
     </row>
     <row r="46">
@@ -3872,115 +3576,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.0005362323470610934</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>report_date_year</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>0.0004363512307099286</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>report_year</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>0.000377705185052018</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>white_quality_moisture_2</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>0.0002750096584171437</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>lime_milk_baume</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>0.0002447343960500336</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>carbonated_alkalinity</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>0.0002408052716201546</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>white_quality_moisture_1</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>0.0002253675461468919</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>boiler_hardness</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>6.689902203393797e-05</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>shift_name</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>3.644830138190724e-05</v>
+        <v>5.174296782901289e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3994,7 +3594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4024,7 +3624,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3273009785562683</v>
+        <v>0.4354256942335763</v>
       </c>
     </row>
     <row r="3">
@@ -4033,11 +3633,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2341821975658129</v>
+        <v>0.2879053195239505</v>
       </c>
     </row>
     <row r="4">
@@ -4046,11 +3646,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.202284502935228</v>
+        <v>0.1013739829994583</v>
       </c>
     </row>
     <row r="5">
@@ -4059,11 +3659,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.08437781417749506</v>
+        <v>0.05082021444524421</v>
       </c>
     </row>
     <row r="6">
@@ -4072,11 +3672,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03151805388149846</v>
+        <v>0.01990592942979598</v>
       </c>
     </row>
     <row r="7">
@@ -4085,11 +3685,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01914241201728629</v>
+        <v>0.01913738835731541</v>
       </c>
     </row>
     <row r="8">
@@ -4098,11 +3698,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.01261148354771118</v>
+        <v>0.01618550000229439</v>
       </c>
     </row>
     <row r="9">
@@ -4111,11 +3711,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0125716311096866</v>
+        <v>0.009696906563716166</v>
       </c>
     </row>
     <row r="10">
@@ -4124,11 +3724,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.01125009811016086</v>
+        <v>0.004727037795364303</v>
       </c>
     </row>
     <row r="11">
@@ -4137,11 +3737,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.006797540172290032</v>
+        <v>0.004702194856392487</v>
       </c>
     </row>
     <row r="12">
@@ -4150,11 +3750,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.006383871055968616</v>
+        <v>0.004482480251171447</v>
       </c>
     </row>
     <row r="13">
@@ -4163,11 +3763,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.004567903659766977</v>
+        <v>0.00433443817214928</v>
       </c>
     </row>
     <row r="14">
@@ -4176,11 +3776,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.003742085099515727</v>
+        <v>0.003398160462251813</v>
       </c>
     </row>
     <row r="15">
@@ -4189,11 +3789,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.003702193952719148</v>
+        <v>0.003111102338491835</v>
       </c>
     </row>
     <row r="16">
@@ -4206,7 +3806,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.002930754602353963</v>
+        <v>0.002997389936709667</v>
       </c>
     </row>
     <row r="17">
@@ -4215,11 +3815,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.002790204142766983</v>
+        <v>0.002951505311773142</v>
       </c>
     </row>
     <row r="18">
@@ -4228,11 +3828,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.002453077075937192</v>
+        <v>0.002671425196684824</v>
       </c>
     </row>
     <row r="19">
@@ -4245,7 +3845,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.002163976082863802</v>
+        <v>0.002559564591866301</v>
       </c>
     </row>
     <row r="20">
@@ -4254,11 +3854,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.001671672701943038</v>
+        <v>0.00249512805053121</v>
       </c>
     </row>
     <row r="21">
@@ -4267,11 +3867,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.001615668932758181</v>
+        <v>0.001709246053542684</v>
       </c>
     </row>
     <row r="22">
@@ -4280,11 +3880,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.00152358979170372</v>
+        <v>0.001439214563866091</v>
       </c>
     </row>
     <row r="23">
@@ -4293,11 +3893,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.001520091012321579</v>
+        <v>0.001419189509467566</v>
       </c>
     </row>
     <row r="24">
@@ -4306,11 +3906,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.00150957324182963</v>
+        <v>0.001265407323093007</v>
       </c>
     </row>
     <row r="25">
@@ -4319,11 +3919,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.001507996316891902</v>
+        <v>0.00099474203484279</v>
       </c>
     </row>
     <row r="26">
@@ -4332,11 +3932,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.001390887528241558</v>
+        <v>0.0009289707036896339</v>
       </c>
     </row>
     <row r="27">
@@ -4345,11 +3945,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.001314113320092398</v>
+        <v>0.0008962976729432869</v>
       </c>
     </row>
     <row r="28">
@@ -4358,11 +3958,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.001187015199766706</v>
+        <v>0.0008746217417649041</v>
       </c>
     </row>
     <row r="29">
@@ -4371,11 +3971,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.001007405018429065</v>
+        <v>0.0008746126141395107</v>
       </c>
     </row>
     <row r="30">
@@ -4384,11 +3984,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0008447516085020126</v>
+        <v>0.0008618206941963109</v>
       </c>
     </row>
     <row r="31">
@@ -4397,11 +3997,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0008084613405911065</v>
+        <v>0.0008611854707114771</v>
       </c>
     </row>
     <row r="32">
@@ -4410,11 +4010,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0008062156514389453</v>
+        <v>0.0008271250420117048</v>
       </c>
     </row>
     <row r="33">
@@ -4423,11 +4023,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0008055574988482754</v>
+        <v>0.0007690661926937902</v>
       </c>
     </row>
     <row r="34">
@@ -4436,11 +4036,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0007696003419973514</v>
+        <v>0.0007680245164467326</v>
       </c>
     </row>
     <row r="35">
@@ -4449,11 +4049,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0007635461142474171</v>
+        <v>0.0007527526867759039</v>
       </c>
     </row>
     <row r="36">
@@ -4462,11 +4062,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0007577331771416256</v>
+        <v>0.0007311182513651744</v>
       </c>
     </row>
     <row r="37">
@@ -4475,11 +4075,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.000678486272436789</v>
+        <v>0.0006928392236250525</v>
       </c>
     </row>
     <row r="38">
@@ -4488,11 +4088,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.0006732612970896623</v>
+        <v>0.0006819145901886573</v>
       </c>
     </row>
     <row r="39">
@@ -4501,11 +4101,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.0006693908937211823</v>
+        <v>0.0006612626900219606</v>
       </c>
     </row>
     <row r="40">
@@ -4514,11 +4114,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0006517038630517026</v>
+        <v>0.0006584017832055801</v>
       </c>
     </row>
     <row r="41">
@@ -4527,11 +4127,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.0006152696280402195</v>
+        <v>0.0005305902171772095</v>
       </c>
     </row>
     <row r="42">
@@ -4540,11 +4140,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.0006060443852796497</v>
+        <v>0.0005189372648662991</v>
       </c>
     </row>
     <row r="43">
@@ -4553,11 +4153,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.0005991046630545348</v>
+        <v>0.0004708182292193955</v>
       </c>
     </row>
     <row r="44">
@@ -4566,11 +4166,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.0005806074086627955</v>
+        <v>0.0004536554020301777</v>
       </c>
     </row>
     <row r="45">
@@ -4579,11 +4179,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>white_quality_moisture_2</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.0005657369744712369</v>
+        <v>0.0003942476044229266</v>
       </c>
     </row>
     <row r="46">
@@ -4592,115 +4192,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.0005541881264318136</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>wastewater_r3_q</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>0.0005465299748814707</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>standard_liquor_brix</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>0.0005032273324813749</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>boiling_r3_pol</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>0.0004753247668537219</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>filtercake_sugar</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>0.000473285230597837</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>boiling_r3_q</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>0.0004350090070727275</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>boiler_hardness</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>0.0003763646132431509</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>lime_milk_baume</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>0.000252947062030458</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>shift_name</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>0.0001688619585249289</v>
+        <v>8.257540495447311e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4714,7 +4210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4749,10 +4245,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3598793571410547</v>
+        <v>0.7224825652776311</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03041445669921594</v>
+        <v>0.0516945832215863</v>
       </c>
     </row>
     <row r="3">
@@ -4761,14 +4257,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2813470101326703</v>
+        <v>0.05593059693425771</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01524823488966109</v>
+        <v>0.009448084691881783</v>
       </c>
     </row>
     <row r="4">
@@ -4777,14 +4273,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.04164666952274031</v>
+        <v>0.04754782163519602</v>
       </c>
       <c r="D4" t="n">
-        <v>0.007157943070708386</v>
+        <v>0.008710069389801955</v>
       </c>
     </row>
     <row r="5">
@@ -4793,14 +4289,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03188475108235687</v>
+        <v>0.04493023010480252</v>
       </c>
       <c r="D5" t="n">
-        <v>0.007600139502350598</v>
+        <v>0.004371957860247482</v>
       </c>
     </row>
     <row r="6">
@@ -4809,14 +4305,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.02157996931448739</v>
+        <v>0.04450525608057554</v>
       </c>
       <c r="D6" t="n">
-        <v>0.005562400201518328</v>
+        <v>0.008579900271024017</v>
       </c>
     </row>
     <row r="7">
@@ -4825,14 +4321,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01200704749597883</v>
+        <v>0.0068005622638733</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001327194475607489</v>
+        <v>0.0007466510768911303</v>
       </c>
     </row>
     <row r="8">
@@ -4841,14 +4337,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.005298272783865155</v>
+        <v>0.004291247703178835</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0004053558587746051</v>
+        <v>0.001586775880442536</v>
       </c>
     </row>
     <row r="9">
@@ -4857,14 +4353,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.004525107807768625</v>
+        <v>0.002581567689486497</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0004560717475661921</v>
+        <v>0.0007592144915295218</v>
       </c>
     </row>
     <row r="10">
@@ -4873,14 +4369,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.001391474375185242</v>
+        <v>0.002484865916395507</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0001591010685670374</v>
+        <v>0.00077284046657007</v>
       </c>
     </row>
     <row r="11">
@@ -4889,14 +4385,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.001319066452784934</v>
+        <v>0.00211519601732254</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0005414674602246384</v>
+        <v>0.0004114065980895629</v>
       </c>
     </row>
     <row r="12">
@@ -4905,14 +4401,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.001145782448783172</v>
+        <v>0.001418341798518774</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0002168212391676837</v>
+        <v>0.0001648160627100342</v>
       </c>
     </row>
     <row r="13">
@@ -4921,14 +4417,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001066831892333719</v>
+        <v>0.001160984115541563</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0005048358098471721</v>
+        <v>0.0003803570420309235</v>
       </c>
     </row>
     <row r="14">
@@ -4937,14 +4433,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.001006899723146582</v>
+        <v>0.00105586038311577</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0003550951118060907</v>
+        <v>0.0001211352309769819</v>
       </c>
     </row>
     <row r="15">
@@ -4953,14 +4449,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0005800150786269609</v>
+        <v>0.0009432406102126811</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0001644582744382503</v>
+        <v>0.0001822642180616185</v>
       </c>
     </row>
     <row r="16">
@@ -4969,14 +4465,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0005687225825380838</v>
+        <v>0.0008730662985472093</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0001283287493608198</v>
+        <v>0.0003234145684061775</v>
       </c>
     </row>
     <row r="17">
@@ -4985,14 +4481,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0005605871611486068</v>
+        <v>0.0008693145273346636</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0001436236424471791</v>
+        <v>0.0002515792078737236</v>
       </c>
     </row>
     <row r="18">
@@ -5001,14 +4497,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0005449226424682596</v>
+        <v>0.0008640450036720093</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0001626794654960852</v>
+        <v>0.0004487413178161993</v>
       </c>
     </row>
     <row r="19">
@@ -5017,14 +4513,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0005098336434348871</v>
+        <v>0.0007143119240637152</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0001447292561736676</v>
+        <v>9.868470734459545e-05</v>
       </c>
     </row>
     <row r="20">
@@ -5033,14 +4529,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0004150406246040683</v>
+        <v>0.0006929705807025899</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0001287384004968077</v>
+        <v>0.0002580311788129602</v>
       </c>
     </row>
     <row r="21">
@@ -5049,14 +4545,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0003921249062823762</v>
+        <v>0.0006838526750083229</v>
       </c>
       <c r="D21" t="n">
-        <v>4.256663542582924e-05</v>
+        <v>0.0002809105535897509</v>
       </c>
     </row>
     <row r="22">
@@ -5065,14 +4561,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0003862927800954319</v>
+        <v>0.0006637387286543949</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0003116897519392233</v>
+        <v>0.0003898235263571688</v>
       </c>
     </row>
     <row r="23">
@@ -5081,14 +4577,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0003850525447717357</v>
+        <v>0.0006375918345603582</v>
       </c>
       <c r="D23" t="n">
-        <v>7.169897241367817e-05</v>
+        <v>0.0002433019429910688</v>
       </c>
     </row>
     <row r="24">
@@ -5097,14 +4593,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0003725391789113563</v>
+        <v>0.000595107814295226</v>
       </c>
       <c r="D24" t="n">
-        <v>4.731016319609135e-05</v>
+        <v>0.0002037983610412335</v>
       </c>
     </row>
     <row r="25">
@@ -5113,14 +4609,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0003341763919277096</v>
+        <v>0.0005163308746648943</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0001281307850931933</v>
+        <v>0.0002023738909991849</v>
       </c>
     </row>
     <row r="26">
@@ -5129,14 +4625,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0002883913801752902</v>
+        <v>0.00046241937193372</v>
       </c>
       <c r="D26" t="n">
-        <v>6.2612569382424e-05</v>
+        <v>0.0001698541631947211</v>
       </c>
     </row>
     <row r="27">
@@ -5145,14 +4641,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0002414067048766122</v>
+        <v>0.0004423379304002162</v>
       </c>
       <c r="D27" t="n">
-        <v>6.713344377306386e-05</v>
+        <v>0.0001686015545223754</v>
       </c>
     </row>
     <row r="28">
@@ -5161,14 +4657,14 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0002236489103918382</v>
+        <v>0.0004413010327554368</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0001163251040837829</v>
+        <v>0.0001685491573301114</v>
       </c>
     </row>
     <row r="29">
@@ -5177,14 +4673,14 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0002159719791944514</v>
+        <v>0.0003927869951789398</v>
       </c>
       <c r="D29" t="n">
-        <v>6.711420602428067e-05</v>
+        <v>0.0001482324471567263</v>
       </c>
     </row>
     <row r="30">
@@ -5193,14 +4689,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0002136535776238402</v>
+        <v>0.0003477123464230347</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0001950049485494445</v>
+        <v>0.000252225637750875</v>
       </c>
     </row>
     <row r="31">
@@ -5209,14 +4705,14 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0002084405193222505</v>
+        <v>0.0002985524944571938</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0001183540964854376</v>
+        <v>0.0001601589888790742</v>
       </c>
     </row>
     <row r="32">
@@ -5225,14 +4721,14 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0002072136151259229</v>
+        <v>0.0002163397078089324</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0007383849116093184</v>
+        <v>9.850298539976308e-05</v>
       </c>
     </row>
     <row r="33">
@@ -5241,14 +4737,14 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0001731946225882352</v>
+        <v>0.0001243027744033398</v>
       </c>
       <c r="D33" t="n">
-        <v>0.000104421660202034</v>
+        <v>0.0001193076706448909</v>
       </c>
     </row>
     <row r="34">
@@ -5257,14 +4753,14 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0001532722460015789</v>
+        <v>0.0001191017083218338</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0001221877296913792</v>
+        <v>0.0001751925269765577</v>
       </c>
     </row>
     <row r="35">
@@ -5273,14 +4769,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0001509396737492619</v>
+        <v>0.0001042134583107202</v>
       </c>
       <c r="D35" t="n">
-        <v>7.096915534128307e-05</v>
+        <v>9.300655999398834e-05</v>
       </c>
     </row>
     <row r="36">
@@ -5289,14 +4785,14 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0001380282076579475</v>
+        <v>9.519455031692381e-05</v>
       </c>
       <c r="D36" t="n">
-        <v>7.290849629909114e-05</v>
+        <v>0.0001117770238843095</v>
       </c>
     </row>
     <row r="37">
@@ -5305,14 +4801,14 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.000120363968992343</v>
+        <v>6.860885122702553e-05</v>
       </c>
       <c r="D37" t="n">
-        <v>8.059860407533205e-05</v>
+        <v>9.212435746256741e-05</v>
       </c>
     </row>
     <row r="38">
@@ -5321,14 +4817,14 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.000104602391677211</v>
+        <v>6.726249614478209e-05</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0001087672521161225</v>
+        <v>0.000118681498365574</v>
       </c>
     </row>
     <row r="39">
@@ -5337,14 +4833,14 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>6.202459662519866e-05</v>
+        <v>2.999320981821318e-05</v>
       </c>
       <c r="D39" t="n">
-        <v>2.874274511499008e-05</v>
+        <v>1.12363074695628e-05</v>
       </c>
     </row>
     <row r="40">
@@ -5353,14 +4849,14 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5.232347753778566e-05</v>
+        <v>2.309187967508564e-08</v>
       </c>
       <c r="D40" t="n">
-        <v>0.000112030362832724</v>
+        <v>0.000210940304128719</v>
       </c>
     </row>
     <row r="41">
@@ -5369,14 +4865,14 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3.591056691265582e-05</v>
+        <v>-3.20763687813308e-06</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0001434684123433031</v>
+        <v>2.265074732626795e-05</v>
       </c>
     </row>
     <row r="42">
@@ -5385,14 +4881,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>boiler_hardness</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1.240458790938703e-05</v>
+        <v>-5.299632575959112e-05</v>
       </c>
       <c r="D42" t="n">
-        <v>4.605546486449173e-06</v>
+        <v>0.0001598779161756747</v>
       </c>
     </row>
     <row r="43">
@@ -5401,14 +4897,14 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-5.288512301337978e-06</v>
+        <v>-9.266529633634723e-05</v>
       </c>
       <c r="D43" t="n">
-        <v>8.11959886125023e-05</v>
+        <v>0.0002780201690877023</v>
       </c>
     </row>
     <row r="44">
@@ -5417,14 +4913,14 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>white_quality_moisture_2</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-1.626303324265832e-05</v>
+        <v>-0.0001096590214565651</v>
       </c>
       <c r="D44" t="n">
-        <v>3.726211982361448e-05</v>
+        <v>0.0001487004279689503</v>
       </c>
     </row>
     <row r="45">
@@ -5433,14 +4929,14 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>shift_name</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-2.786894234031445e-05</v>
+        <v>-0.0001493895613445373</v>
       </c>
       <c r="D45" t="n">
-        <v>1.777214842172522e-05</v>
+        <v>0.0002621423006976577</v>
       </c>
     </row>
     <row r="46">
@@ -5449,142 +4945,14 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-3.656031711293251e-05</v>
+        <v>-0.00017887632103607</v>
       </c>
       <c r="D46" t="n">
-        <v>4.49923508352163e-05</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>boiling_r1_pol</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>-3.91240558361261e-05</v>
-      </c>
-      <c r="D47" t="n">
-        <v>6.675099540998126e-05</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>white_quality_apparent_color_2</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>-4.068710041987833e-05</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0.0001025101141062979</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>white_quality_moisture_1</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>-4.815492907950247e-05</v>
-      </c>
-      <c r="D49" t="n">
-        <v>2.803255978632049e-05</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>boiling_r3_pol</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>-5.153761794980394e-05</v>
-      </c>
-      <c r="D50" t="n">
-        <v>8.442209553244266e-05</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>sulphited_brix</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>-9.690869983760563e-05</v>
-      </c>
-      <c r="D51" t="n">
-        <v>5.406300750380171e-05</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>raw_syrup_color</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>-0.0001482043522034182</v>
-      </c>
-      <c r="D52" t="n">
-        <v>9.671752472188728e-05</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>boiling_r3_q</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>-0.0001800433885698061</v>
-      </c>
-      <c r="D53" t="n">
-        <v>9.325461665870275e-05</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>wastewater_r3_q</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>-0.0003104006152106375</v>
-      </c>
-      <c r="D54" t="n">
-        <v>9.910782854718644e-05</v>
+        <v>0.0003321550021656594</v>
       </c>
     </row>
   </sheetData>
@@ -5598,7 +4966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5624,11 +4992,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.220162286626203</v>
+        <v>1.197226875819409</v>
       </c>
     </row>
     <row r="3">
@@ -5637,11 +5005,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.197596762489799</v>
+        <v>0.9694040788023274</v>
       </c>
     </row>
     <row r="4">
@@ -5650,11 +5018,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.032026958462696</v>
+        <v>0.8714167049095849</v>
       </c>
     </row>
     <row r="5">
@@ -5663,11 +5031,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8723113670408211</v>
+        <v>0.6246955590411227</v>
       </c>
     </row>
     <row r="6">
@@ -5680,7 +5048,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6149920332849157</v>
+        <v>0.6141018072778577</v>
       </c>
     </row>
     <row r="7">
@@ -5689,11 +5057,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6066707781972243</v>
+        <v>0.6036619723165955</v>
       </c>
     </row>
     <row r="8">
@@ -5702,11 +5070,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.6059710037229373</v>
+        <v>0.6022214060763087</v>
       </c>
     </row>
     <row r="9">
@@ -5715,11 +5083,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.595591263334927</v>
+        <v>0.47636999799035</v>
       </c>
     </row>
     <row r="10">
@@ -5728,11 +5096,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.4961557840490896</v>
+        <v>0.2340226057029207</v>
       </c>
     </row>
     <row r="11">
@@ -5741,11 +5109,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.2717957000954292</v>
+        <v>0.2255469942945947</v>
       </c>
     </row>
     <row r="12">
@@ -5754,11 +5122,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.2699523346893602</v>
+        <v>0.215175382121823</v>
       </c>
     </row>
     <row r="13">
@@ -5767,11 +5135,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.2636575744571474</v>
+        <v>0.1957868200241759</v>
       </c>
     </row>
     <row r="14">
@@ -5780,11 +5148,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.2445728104993856</v>
+        <v>0.1823608994384267</v>
       </c>
     </row>
     <row r="15">
@@ -5793,11 +5161,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.2125263033038287</v>
+        <v>0.1817267023553764</v>
       </c>
     </row>
     <row r="16">
@@ -5806,11 +5174,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.2099184335506039</v>
+        <v>0.1735836979765957</v>
       </c>
     </row>
     <row r="17">
@@ -5819,11 +5187,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.1970921910273393</v>
+        <v>0.1660814131995023</v>
       </c>
     </row>
     <row r="18">
@@ -5832,11 +5200,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.1922289003748792</v>
+        <v>0.1560008877185812</v>
       </c>
     </row>
     <row r="19">
@@ -5845,11 +5213,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.1883237605390065</v>
+        <v>0.1529091726203493</v>
       </c>
     </row>
     <row r="20">
@@ -5858,11 +5226,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.1856278187338714</v>
+        <v>0.1515377957846171</v>
       </c>
     </row>
     <row r="21">
@@ -5871,11 +5239,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.164502853842124</v>
+        <v>0.1430107500986084</v>
       </c>
     </row>
     <row r="22">
@@ -5884,11 +5252,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.1581573980849016</v>
+        <v>0.1374381455440177</v>
       </c>
     </row>
     <row r="23">
@@ -5897,11 +5265,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.1565064608513327</v>
+        <v>0.1357969386610014</v>
       </c>
     </row>
     <row r="24">
@@ -5910,11 +5278,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.1528703251648047</v>
+        <v>0.1239600995440173</v>
       </c>
     </row>
     <row r="25">
@@ -5923,11 +5291,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.1497267572983745</v>
+        <v>0.1200999449624831</v>
       </c>
     </row>
     <row r="26">
@@ -5936,11 +5304,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.1483923472772828</v>
+        <v>0.1180221293205901</v>
       </c>
     </row>
     <row r="27">
@@ -5949,11 +5317,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.1465052836719529</v>
+        <v>0.1152474317326098</v>
       </c>
     </row>
     <row r="28">
@@ -5962,11 +5330,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.1328690731507498</v>
+        <v>0.1142654146941351</v>
       </c>
     </row>
     <row r="29">
@@ -5975,11 +5343,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.1298072021325805</v>
+        <v>0.1130216009059368</v>
       </c>
     </row>
     <row r="30">
@@ -5988,11 +5356,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.1250352999412252</v>
+        <v>0.1127681090016961</v>
       </c>
     </row>
     <row r="31">
@@ -6001,11 +5369,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.1206952753538957</v>
+        <v>0.110278035031449</v>
       </c>
     </row>
     <row r="32">
@@ -6014,11 +5382,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.1185070533412098</v>
+        <v>0.0971811977419299</v>
       </c>
     </row>
     <row r="33">
@@ -6027,11 +5395,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.1163760253988069</v>
+        <v>0.09299207544495491</v>
       </c>
     </row>
     <row r="34">
@@ -6040,11 +5408,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.1162677246604455</v>
+        <v>0.08489930078051477</v>
       </c>
     </row>
     <row r="35">
@@ -6053,11 +5421,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.1133977684273755</v>
+        <v>0.08280586501887521</v>
       </c>
     </row>
     <row r="36">
@@ -6066,11 +5434,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.1105996765571509</v>
+        <v>0.08011231981302425</v>
       </c>
     </row>
     <row r="37">
@@ -6079,11 +5447,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.1085555176625839</v>
+        <v>0.07732935516363204</v>
       </c>
     </row>
     <row r="38">
@@ -6092,11 +5460,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.1047114309968094</v>
+        <v>0.07635038632091495</v>
       </c>
     </row>
     <row r="39">
@@ -6105,11 +5473,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.09661113621317829</v>
+        <v>0.07462187000962528</v>
       </c>
     </row>
     <row r="40">
@@ -6118,11 +5486,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.08866143799683179</v>
+        <v>0.04897320932359284</v>
       </c>
     </row>
     <row r="41">
@@ -6131,11 +5499,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.08700539601290069</v>
+        <v>0.04348365168062962</v>
       </c>
     </row>
     <row r="42">
@@ -6144,11 +5512,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.08252037876710538</v>
+        <v>0.02495406817277646</v>
       </c>
     </row>
     <row r="43">
@@ -6157,11 +5525,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.08158316046622227</v>
+        <v>0.01945995009064694</v>
       </c>
     </row>
     <row r="44">
@@ -6170,11 +5538,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.07873252507831374</v>
+        <v>0.003844176778656117</v>
       </c>
     </row>
     <row r="45">
@@ -6183,127 +5551,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.05864846358770226</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.05192730137918167</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>wastewater_r3_pol</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>0.04812936651390975</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>carbonated_alkalinity</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>0.03575821798885048</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>standard_liquor_pH</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>0.02854832884313652</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>white_quality_moisture_1</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>0.01525040081228823</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>lime_milk_baume</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>0.004620886376301314</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>white_quality_moisture_2</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>0.0006290865065095019</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>shift_name</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>52</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>boiler_hardness</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6379,10 +5643,10 @@
         <v>197</v>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F2" t="n">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -6391,7 +5655,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-15 07:19:38 UTC</t>
+          <t>2026-06-16 11:47:04 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_solution_color.xlsx
+++ b/NN/reports/feature_importance_white_solution_color.xlsx
@@ -550,7 +550,7 @@
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05593059693425771</v>
+        <v>0.05593059693425773</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -624,7 +624,7 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04493023010480252</v>
+        <v>0.0449302301048025</v>
       </c>
       <c r="H5" t="n">
         <v>4</v>
@@ -661,7 +661,7 @@
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04450525608057554</v>
+        <v>0.04450525608057555</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -698,7 +698,7 @@
         <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0068005622638733</v>
+        <v>0.006800562263873278</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
@@ -735,7 +735,7 @@
         <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00105586038311577</v>
+        <v>0.001055860383115947</v>
       </c>
       <c r="H8" t="n">
         <v>13</v>
@@ -772,7 +772,7 @@
         <v>12</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002484865916395507</v>
+        <v>0.002484865916395496</v>
       </c>
       <c r="H9" t="n">
         <v>9</v>
@@ -846,7 +846,7 @@
         <v>11</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001160984115541563</v>
+        <v>0.001160984115541541</v>
       </c>
       <c r="H11" t="n">
         <v>12</v>
@@ -883,7 +883,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="n">
-        <v>0.002581567689486497</v>
+        <v>0.002581567689486519</v>
       </c>
       <c r="H12" t="n">
         <v>8</v>
@@ -957,7 +957,7 @@
         <v>20</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0008640450036720093</v>
+        <v>0.0008640450036720204</v>
       </c>
       <c r="H14" t="n">
         <v>17</v>
@@ -1068,7 +1068,7 @@
         <v>22</v>
       </c>
       <c r="G17" t="n">
-        <v>0.001418341798518774</v>
+        <v>0.001418341798518752</v>
       </c>
       <c r="H17" t="n">
         <v>11</v>
@@ -1142,7 +1142,7 @@
         <v>7</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0004423379304002162</v>
+        <v>0.0004423379304002273</v>
       </c>
       <c r="H19" t="n">
         <v>26</v>
@@ -1216,7 +1216,7 @@
         <v>35</v>
       </c>
       <c r="G21" t="n">
-        <v>0.000595107814295226</v>
+        <v>0.0005951078142952149</v>
       </c>
       <c r="H21" t="n">
         <v>23</v>
@@ -1290,7 +1290,7 @@
         <v>9</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0004413010327554368</v>
+        <v>0.0004413010327554257</v>
       </c>
       <c r="H23" t="n">
         <v>27</v>
@@ -1327,7 +1327,7 @@
         <v>25</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0008730662985472093</v>
+        <v>0.0008730662985471982</v>
       </c>
       <c r="H24" t="n">
         <v>15</v>
@@ -1364,7 +1364,7 @@
         <v>18</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0003927869951789398</v>
+        <v>0.0003927869951789287</v>
       </c>
       <c r="H25" t="n">
         <v>28</v>
@@ -1401,7 +1401,7 @@
         <v>19</v>
       </c>
       <c r="G26" t="n">
-        <v>0.00046241937193372</v>
+        <v>0.0004624193719336978</v>
       </c>
       <c r="H26" t="n">
         <v>25</v>
@@ -1438,7 +1438,7 @@
         <v>31</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0006838526750083229</v>
+        <v>0.000683852675008334</v>
       </c>
       <c r="H27" t="n">
         <v>20</v>
@@ -1475,7 +1475,7 @@
         <v>24</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0006375918345603582</v>
+        <v>0.0006375918345603359</v>
       </c>
       <c r="H28" t="n">
         <v>22</v>
@@ -1512,7 +1512,7 @@
         <v>30</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.0001493895613445373</v>
+        <v>-0.0001493895613445484</v>
       </c>
       <c r="H29" t="n">
         <v>44</v>
@@ -1549,7 +1549,7 @@
         <v>26</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0003477123464230347</v>
+        <v>0.0003477123464230125</v>
       </c>
       <c r="H30" t="n">
         <v>29</v>
@@ -1586,7 +1586,7 @@
         <v>40</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0002985524944571938</v>
+        <v>0.0002985524944571827</v>
       </c>
       <c r="H31" t="n">
         <v>30</v>
@@ -1660,7 +1660,7 @@
         <v>39</v>
       </c>
       <c r="G33" t="n">
-        <v>6.726249614478209e-05</v>
+        <v>6.726249614475987e-05</v>
       </c>
       <c r="H33" t="n">
         <v>37</v>
@@ -1697,7 +1697,7 @@
         <v>29</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.00017887632103607</v>
+        <v>-0.0001788763210360589</v>
       </c>
       <c r="H34" t="n">
         <v>45</v>
@@ -1734,7 +1734,7 @@
         <v>33</v>
       </c>
       <c r="G35" t="n">
-        <v>2.309187967508564e-08</v>
+        <v>2.309187965288117e-08</v>
       </c>
       <c r="H35" t="n">
         <v>39</v>
@@ -1771,7 +1771,7 @@
         <v>28</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0001191017083218338</v>
+        <v>0.000119101708321856</v>
       </c>
       <c r="H36" t="n">
         <v>33</v>
@@ -1808,7 +1808,7 @@
         <v>32</v>
       </c>
       <c r="G37" t="n">
-        <v>9.519455031692381e-05</v>
+        <v>9.519455031691271e-05</v>
       </c>
       <c r="H37" t="n">
         <v>35</v>
@@ -1882,7 +1882,7 @@
         <v>34</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0007143119240637152</v>
+        <v>0.0007143119240637042</v>
       </c>
       <c r="H39" t="n">
         <v>18</v>
@@ -1956,7 +1956,7 @@
         <v>37</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0002163397078089324</v>
+        <v>0.0002163397078089102</v>
       </c>
       <c r="H41" t="n">
         <v>31</v>
@@ -1993,7 +1993,7 @@
         <v>42</v>
       </c>
       <c r="G42" t="n">
-        <v>-5.299632575959112e-05</v>
+        <v>-5.299632575958002e-05</v>
       </c>
       <c r="H42" t="n">
         <v>41</v>
@@ -2030,7 +2030,7 @@
         <v>41</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0001042134583107202</v>
+        <v>0.0001042134583107313</v>
       </c>
       <c r="H43" t="n">
         <v>34</v>
@@ -2104,7 +2104,7 @@
         <v>44</v>
       </c>
       <c r="G45" t="n">
-        <v>2.999320981821318e-05</v>
+        <v>2.999320981820208e-05</v>
       </c>
       <c r="H45" t="n">
         <v>38</v>
@@ -2141,7 +2141,7 @@
         <v>45</v>
       </c>
       <c r="G46" t="n">
-        <v>-3.20763687813308e-06</v>
+        <v>-3.207636878121978e-06</v>
       </c>
       <c r="H46" t="n">
         <v>40</v>
@@ -2286,7 +2286,7 @@
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05593059693425771</v>
+        <v>0.05593059693425773</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -2360,7 +2360,7 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04493023010480252</v>
+        <v>0.0449302301048025</v>
       </c>
       <c r="H5" t="n">
         <v>4</v>
@@ -2397,7 +2397,7 @@
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04450525608057554</v>
+        <v>0.04450525608057555</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -2434,7 +2434,7 @@
         <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0068005622638733</v>
+        <v>0.006800562263873278</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
@@ -2471,7 +2471,7 @@
         <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00105586038311577</v>
+        <v>0.001055860383115947</v>
       </c>
       <c r="H8" t="n">
         <v>13</v>
@@ -2508,7 +2508,7 @@
         <v>12</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002484865916395507</v>
+        <v>0.002484865916395496</v>
       </c>
       <c r="H9" t="n">
         <v>9</v>
@@ -2582,7 +2582,7 @@
         <v>11</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001160984115541563</v>
+        <v>0.001160984115541541</v>
       </c>
       <c r="H11" t="n">
         <v>12</v>
@@ -2619,7 +2619,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="n">
-        <v>0.002581567689486497</v>
+        <v>0.002581567689486519</v>
       </c>
       <c r="H12" t="n">
         <v>8</v>
@@ -2693,7 +2693,7 @@
         <v>20</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0008640450036720093</v>
+        <v>0.0008640450036720204</v>
       </c>
       <c r="H14" t="n">
         <v>17</v>
@@ -2804,7 +2804,7 @@
         <v>22</v>
       </c>
       <c r="G17" t="n">
-        <v>0.001418341798518774</v>
+        <v>0.001418341798518752</v>
       </c>
       <c r="H17" t="n">
         <v>11</v>
@@ -2878,7 +2878,7 @@
         <v>7</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0004423379304002162</v>
+        <v>0.0004423379304002273</v>
       </c>
       <c r="H19" t="n">
         <v>26</v>
@@ -2952,7 +2952,7 @@
         <v>35</v>
       </c>
       <c r="G21" t="n">
-        <v>0.000595107814295226</v>
+        <v>0.0005951078142952149</v>
       </c>
       <c r="H21" t="n">
         <v>23</v>
@@ -4248,7 +4248,7 @@
         <v>0.7224825652776311</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0516945832215863</v>
+        <v>0.05169458322158631</v>
       </c>
     </row>
     <row r="3">
@@ -4261,10 +4261,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.05593059693425771</v>
+        <v>0.05593059693425773</v>
       </c>
       <c r="D3" t="n">
-        <v>0.009448084691881783</v>
+        <v>0.009448084691881771</v>
       </c>
     </row>
     <row r="4">
@@ -4280,7 +4280,7 @@
         <v>0.04754782163519602</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008710069389801955</v>
+        <v>0.008710069389801981</v>
       </c>
     </row>
     <row r="5">
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.04493023010480252</v>
+        <v>0.0449302301048025</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004371957860247482</v>
+        <v>0.004371957860247486</v>
       </c>
     </row>
     <row r="6">
@@ -4309,10 +4309,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.04450525608057554</v>
+        <v>0.04450525608057555</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008579900271024017</v>
+        <v>0.008579900271024019</v>
       </c>
     </row>
     <row r="7">
@@ -4325,10 +4325,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0068005622638733</v>
+        <v>0.006800562263873278</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0007466510768911303</v>
+        <v>0.0007466510768910653</v>
       </c>
     </row>
     <row r="8">
@@ -4344,7 +4344,7 @@
         <v>0.004291247703178835</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001586775880442536</v>
+        <v>0.001586775880442513</v>
       </c>
     </row>
     <row r="9">
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.002581567689486497</v>
+        <v>0.002581567689486519</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0007592144915295218</v>
+        <v>0.0007592144915295148</v>
       </c>
     </row>
     <row r="10">
@@ -4373,10 +4373,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.002484865916395507</v>
+        <v>0.002484865916395496</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00077284046657007</v>
+        <v>0.000772840466570078</v>
       </c>
     </row>
     <row r="11">
@@ -4392,7 +4392,7 @@
         <v>0.00211519601732254</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0004114065980895629</v>
+        <v>0.0004114065980895599</v>
       </c>
     </row>
     <row r="12">
@@ -4405,10 +4405,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.001418341798518774</v>
+        <v>0.001418341798518752</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0001648160627100342</v>
+        <v>0.0001648160627100563</v>
       </c>
     </row>
     <row r="13">
@@ -4421,10 +4421,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001160984115541563</v>
+        <v>0.001160984115541541</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0003803570420309235</v>
+        <v>0.0003803570420309039</v>
       </c>
     </row>
     <row r="14">
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.00105586038311577</v>
+        <v>0.001055860383115947</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0001211352309769819</v>
+        <v>0.0001211352309769301</v>
       </c>
     </row>
     <row r="15">
@@ -4456,7 +4456,7 @@
         <v>0.0009432406102126811</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0001822642180616185</v>
+        <v>0.000182264218061646</v>
       </c>
     </row>
     <row r="16">
@@ -4469,10 +4469,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0008730662985472093</v>
+        <v>0.0008730662985471982</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0003234145684061775</v>
+        <v>0.000323414568406171</v>
       </c>
     </row>
     <row r="17">
@@ -4488,7 +4488,7 @@
         <v>0.0008693145273346636</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0002515792078737236</v>
+        <v>0.000251579207873706</v>
       </c>
     </row>
     <row r="18">
@@ -4501,10 +4501,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0008640450036720093</v>
+        <v>0.0008640450036720204</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0004487413178161993</v>
+        <v>0.0004487413178162064</v>
       </c>
     </row>
     <row r="19">
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0007143119240637152</v>
+        <v>0.0007143119240637042</v>
       </c>
       <c r="D19" t="n">
-        <v>9.868470734459545e-05</v>
+        <v>9.868470734463553e-05</v>
       </c>
     </row>
     <row r="20">
@@ -4536,7 +4536,7 @@
         <v>0.0006929705807025899</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0002580311788129602</v>
+        <v>0.0002580311788129993</v>
       </c>
     </row>
     <row r="21">
@@ -4549,10 +4549,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0006838526750083229</v>
+        <v>0.000683852675008334</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0002809105535897509</v>
+        <v>0.0002809105535897538</v>
       </c>
     </row>
     <row r="22">
@@ -4568,7 +4568,7 @@
         <v>0.0006637387286543949</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0003898235263571688</v>
+        <v>0.0003898235263571774</v>
       </c>
     </row>
     <row r="23">
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0006375918345603582</v>
+        <v>0.0006375918345603359</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0002433019429910688</v>
+        <v>0.0002433019429910695</v>
       </c>
     </row>
     <row r="24">
@@ -4597,10 +4597,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.000595107814295226</v>
+        <v>0.0005951078142952149</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0002037983610412335</v>
+        <v>0.000203798361041216</v>
       </c>
     </row>
     <row r="25">
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.00046241937193372</v>
+        <v>0.0004624193719336978</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0001698541631947211</v>
+        <v>0.0001698541631947191</v>
       </c>
     </row>
     <row r="27">
@@ -4645,10 +4645,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0004423379304002162</v>
+        <v>0.0004423379304002273</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0001686015545223754</v>
+        <v>0.000168601554522366</v>
       </c>
     </row>
     <row r="28">
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0004413010327554368</v>
+        <v>0.0004413010327554257</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0001685491573301114</v>
+        <v>0.0001685491573300985</v>
       </c>
     </row>
     <row r="29">
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0003927869951789398</v>
+        <v>0.0003927869951789287</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0001482324471567263</v>
+        <v>0.0001482324471567214</v>
       </c>
     </row>
     <row r="30">
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0003477123464230347</v>
+        <v>0.0003477123464230125</v>
       </c>
       <c r="D30" t="n">
-        <v>0.000252225637750875</v>
+        <v>0.0002522256377508906</v>
       </c>
     </row>
     <row r="31">
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0002985524944571938</v>
+        <v>0.0002985524944571827</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0001601589888790742</v>
+        <v>0.0001601589888790763</v>
       </c>
     </row>
     <row r="32">
@@ -4725,10 +4725,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0002163397078089324</v>
+        <v>0.0002163397078089102</v>
       </c>
       <c r="D32" t="n">
-        <v>9.850298539976308e-05</v>
+        <v>9.850298539975111e-05</v>
       </c>
     </row>
     <row r="33">
@@ -4744,7 +4744,7 @@
         <v>0.0001243027744033398</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0001193076706448909</v>
+        <v>0.0001193076706448794</v>
       </c>
     </row>
     <row r="34">
@@ -4757,10 +4757,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0001191017083218338</v>
+        <v>0.000119101708321856</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0001751925269765577</v>
+        <v>0.0001751925269765365</v>
       </c>
     </row>
     <row r="35">
@@ -4773,10 +4773,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0001042134583107202</v>
+        <v>0.0001042134583107313</v>
       </c>
       <c r="D35" t="n">
-        <v>9.300655999398834e-05</v>
+        <v>9.300655999397114e-05</v>
       </c>
     </row>
     <row r="36">
@@ -4789,10 +4789,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>9.519455031692381e-05</v>
+        <v>9.519455031691271e-05</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0001117770238843095</v>
+        <v>0.0001117770238842945</v>
       </c>
     </row>
     <row r="37">
@@ -4808,7 +4808,7 @@
         <v>6.860885122702553e-05</v>
       </c>
       <c r="D37" t="n">
-        <v>9.212435746256741e-05</v>
+        <v>9.212435746260697e-05</v>
       </c>
     </row>
     <row r="38">
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6.726249614478209e-05</v>
+        <v>6.726249614475987e-05</v>
       </c>
       <c r="D38" t="n">
-        <v>0.000118681498365574</v>
+        <v>0.0001186814983655725</v>
       </c>
     </row>
     <row r="39">
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2.999320981821318e-05</v>
+        <v>2.999320981820208e-05</v>
       </c>
       <c r="D39" t="n">
-        <v>1.12363074695628e-05</v>
+        <v>1.123630746954218e-05</v>
       </c>
     </row>
     <row r="40">
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2.309187967508564e-08</v>
+        <v>2.309187965288117e-08</v>
       </c>
       <c r="D40" t="n">
-        <v>0.000210940304128719</v>
+        <v>0.0002109403041287341</v>
       </c>
     </row>
     <row r="41">
@@ -4869,10 +4869,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-3.20763687813308e-06</v>
+        <v>-3.207636878121978e-06</v>
       </c>
       <c r="D41" t="n">
-        <v>2.265074732626795e-05</v>
+        <v>2.265074732626281e-05</v>
       </c>
     </row>
     <row r="42">
@@ -4885,10 +4885,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-5.299632575959112e-05</v>
+        <v>-5.299632575958002e-05</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0001598779161756747</v>
+        <v>0.0001598779161756887</v>
       </c>
     </row>
     <row r="43">
@@ -4904,7 +4904,7 @@
         <v>-9.266529633634723e-05</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0002780201690877023</v>
+        <v>0.0002780201690876936</v>
       </c>
     </row>
     <row r="44">
@@ -4920,7 +4920,7 @@
         <v>-0.0001096590214565651</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0001487004279689503</v>
+        <v>0.0001487004279689495</v>
       </c>
     </row>
     <row r="45">
@@ -4933,10 +4933,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-0.0001493895613445373</v>
+        <v>-0.0001493895613445484</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0002621423006976577</v>
+        <v>0.0002621423006976512</v>
       </c>
     </row>
     <row r="46">
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-0.00017887632103607</v>
+        <v>-0.0001788763210360589</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0003321550021656594</v>
+        <v>0.0003321550021656572</v>
       </c>
     </row>
   </sheetData>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-16 11:47:04 UTC</t>
+          <t>2026-06-16 14:05:12 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_solution_color.xlsx
+++ b/NN/reports/feature_importance_white_solution_color.xlsx
@@ -513,7 +513,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7224825652776311</v>
+        <v>0.7224825652776312</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -550,7 +550,7 @@
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05593059693425773</v>
+        <v>0.05593059693425782</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -587,7 +587,7 @@
         <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04754782163519602</v>
+        <v>0.04754782163519613</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -624,7 +624,7 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0449302301048025</v>
+        <v>0.04493023010480263</v>
       </c>
       <c r="H5" t="n">
         <v>4</v>
@@ -661,7 +661,7 @@
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04450525608057555</v>
+        <v>0.04450525608057564</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -698,7 +698,7 @@
         <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006800562263873278</v>
+        <v>0.0068005622638734</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
@@ -735,7 +735,7 @@
         <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001055860383115947</v>
+        <v>0.00105586038315627</v>
       </c>
       <c r="H8" t="n">
         <v>13</v>
@@ -772,7 +772,7 @@
         <v>12</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002484865916395496</v>
+        <v>0.002484865916395607</v>
       </c>
       <c r="H9" t="n">
         <v>9</v>
@@ -809,7 +809,7 @@
         <v>16</v>
       </c>
       <c r="G10" t="n">
-        <v>0.004291247703178835</v>
+        <v>0.004291247703178925</v>
       </c>
       <c r="H10" t="n">
         <v>7</v>
@@ -846,7 +846,7 @@
         <v>11</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001160984115541541</v>
+        <v>0.001160984115541685</v>
       </c>
       <c r="H11" t="n">
         <v>12</v>
@@ -883,7 +883,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="n">
-        <v>0.002581567689486519</v>
+        <v>0.002581567689486597</v>
       </c>
       <c r="H12" t="n">
         <v>8</v>
@@ -920,7 +920,7 @@
         <v>17</v>
       </c>
       <c r="G13" t="n">
-        <v>0.00211519601732254</v>
+        <v>0.002115196017322651</v>
       </c>
       <c r="H13" t="n">
         <v>10</v>
@@ -957,7 +957,7 @@
         <v>20</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0008640450036720204</v>
+        <v>0.0008640450036721092</v>
       </c>
       <c r="H14" t="n">
         <v>17</v>
@@ -994,7 +994,7 @@
         <v>13</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0006637387286543949</v>
+        <v>0.000663738728654506</v>
       </c>
       <c r="H15" t="n">
         <v>21</v>
@@ -1031,7 +1031,7 @@
         <v>14</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0005163308746648943</v>
+        <v>0.0005163308746650164</v>
       </c>
       <c r="H16" t="n">
         <v>24</v>
@@ -1068,7 +1068,7 @@
         <v>22</v>
       </c>
       <c r="G17" t="n">
-        <v>0.001418341798518752</v>
+        <v>0.001418341798518874</v>
       </c>
       <c r="H17" t="n">
         <v>11</v>
@@ -1105,7 +1105,7 @@
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0008693145273346636</v>
+        <v>0.0008693145273347636</v>
       </c>
       <c r="H18" t="n">
         <v>16</v>
@@ -1142,7 +1142,7 @@
         <v>7</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0004423379304002273</v>
+        <v>0.0004423379304003272</v>
       </c>
       <c r="H19" t="n">
         <v>26</v>
@@ -1179,7 +1179,7 @@
         <v>21</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0009432406102126811</v>
+        <v>0.0009432406102128143</v>
       </c>
       <c r="H20" t="n">
         <v>14</v>
@@ -1216,7 +1216,7 @@
         <v>35</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0005951078142952149</v>
+        <v>0.0005951078142953259</v>
       </c>
       <c r="H21" t="n">
         <v>23</v>
@@ -1253,7 +1253,7 @@
         <v>23</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0006929705807025899</v>
+        <v>0.0006929705807026787</v>
       </c>
       <c r="H22" t="n">
         <v>19</v>
@@ -1290,7 +1290,7 @@
         <v>9</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0004413010327554257</v>
+        <v>0.0004413010327555478</v>
       </c>
       <c r="H23" t="n">
         <v>27</v>
@@ -1327,7 +1327,7 @@
         <v>25</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0008730662985471982</v>
+        <v>0.0008730662985473204</v>
       </c>
       <c r="H24" t="n">
         <v>15</v>
@@ -1364,7 +1364,7 @@
         <v>18</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0003927869951789287</v>
+        <v>0.0003927869951790508</v>
       </c>
       <c r="H25" t="n">
         <v>28</v>
@@ -1401,7 +1401,7 @@
         <v>19</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0004624193719336978</v>
+        <v>0.0004624193719338088</v>
       </c>
       <c r="H26" t="n">
         <v>25</v>
@@ -1438,7 +1438,7 @@
         <v>31</v>
       </c>
       <c r="G27" t="n">
-        <v>0.000683852675008334</v>
+        <v>0.0006838526750084561</v>
       </c>
       <c r="H27" t="n">
         <v>20</v>
@@ -1475,7 +1475,7 @@
         <v>24</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0006375918345603359</v>
+        <v>0.0006375918345604581</v>
       </c>
       <c r="H28" t="n">
         <v>22</v>
@@ -1512,7 +1512,7 @@
         <v>30</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.0001493895613445484</v>
+        <v>-0.0001493895613444374</v>
       </c>
       <c r="H29" t="n">
         <v>44</v>
@@ -1549,7 +1549,7 @@
         <v>26</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0003477123464230125</v>
+        <v>0.0003477123464231457</v>
       </c>
       <c r="H30" t="n">
         <v>29</v>
@@ -1586,7 +1586,7 @@
         <v>40</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0002985524944571827</v>
+        <v>0.0002985524944572826</v>
       </c>
       <c r="H31" t="n">
         <v>30</v>
@@ -1623,7 +1623,7 @@
         <v>27</v>
       </c>
       <c r="G32" t="n">
-        <v>-9.266529633634723e-05</v>
+        <v>-9.266529633623621e-05</v>
       </c>
       <c r="H32" t="n">
         <v>42</v>
@@ -1660,7 +1660,7 @@
         <v>39</v>
       </c>
       <c r="G33" t="n">
-        <v>6.726249614475987e-05</v>
+        <v>6.726249614489311e-05</v>
       </c>
       <c r="H33" t="n">
         <v>37</v>
@@ -1697,7 +1697,7 @@
         <v>29</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.0001788763210360589</v>
+        <v>-0.0001788763210359701</v>
       </c>
       <c r="H34" t="n">
         <v>45</v>
@@ -1734,7 +1734,7 @@
         <v>33</v>
       </c>
       <c r="G35" t="n">
-        <v>2.309187965288117e-08</v>
+        <v>2.309187977500571e-08</v>
       </c>
       <c r="H35" t="n">
         <v>39</v>
@@ -1771,7 +1771,7 @@
         <v>28</v>
       </c>
       <c r="G36" t="n">
-        <v>0.000119101708321856</v>
+        <v>0.0001191017083219448</v>
       </c>
       <c r="H36" t="n">
         <v>33</v>
@@ -1808,7 +1808,7 @@
         <v>32</v>
       </c>
       <c r="G37" t="n">
-        <v>9.519455031691271e-05</v>
+        <v>9.519455031703483e-05</v>
       </c>
       <c r="H37" t="n">
         <v>35</v>
@@ -1845,7 +1845,7 @@
         <v>36</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.0001096590214565651</v>
+        <v>-0.0001096590214564541</v>
       </c>
       <c r="H38" t="n">
         <v>43</v>
@@ -1882,7 +1882,7 @@
         <v>34</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0007143119240637042</v>
+        <v>0.0007143119240638152</v>
       </c>
       <c r="H39" t="n">
         <v>18</v>
@@ -1919,7 +1919,7 @@
         <v>38</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0001243027744033398</v>
+        <v>0.0001243027744034397</v>
       </c>
       <c r="H40" t="n">
         <v>32</v>
@@ -1956,7 +1956,7 @@
         <v>37</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0002163397078089102</v>
+        <v>0.0002163397078090323</v>
       </c>
       <c r="H41" t="n">
         <v>31</v>
@@ -1993,7 +1993,7 @@
         <v>42</v>
       </c>
       <c r="G42" t="n">
-        <v>-5.299632575958002e-05</v>
+        <v>-5.299632575949121e-05</v>
       </c>
       <c r="H42" t="n">
         <v>41</v>
@@ -2030,7 +2030,7 @@
         <v>41</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0001042134583107313</v>
+        <v>0.0001042134583108423</v>
       </c>
       <c r="H43" t="n">
         <v>34</v>
@@ -2067,7 +2067,7 @@
         <v>43</v>
       </c>
       <c r="G44" t="n">
-        <v>6.860885122702553e-05</v>
+        <v>6.860885122714767e-05</v>
       </c>
       <c r="H44" t="n">
         <v>36</v>
@@ -2104,7 +2104,7 @@
         <v>44</v>
       </c>
       <c r="G45" t="n">
-        <v>2.999320981820208e-05</v>
+        <v>2.999320981832421e-05</v>
       </c>
       <c r="H45" t="n">
         <v>38</v>
@@ -2141,7 +2141,7 @@
         <v>45</v>
       </c>
       <c r="G46" t="n">
-        <v>-3.207636878121978e-06</v>
+        <v>-3.207636877999853e-06</v>
       </c>
       <c r="H46" t="n">
         <v>40</v>
@@ -2249,7 +2249,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7224825652776311</v>
+        <v>0.7224825652776312</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -2286,7 +2286,7 @@
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05593059693425773</v>
+        <v>0.05593059693425782</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -2323,7 +2323,7 @@
         <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04754782163519602</v>
+        <v>0.04754782163519613</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -2360,7 +2360,7 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0449302301048025</v>
+        <v>0.04493023010480263</v>
       </c>
       <c r="H5" t="n">
         <v>4</v>
@@ -2397,7 +2397,7 @@
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04450525608057555</v>
+        <v>0.04450525608057564</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -2434,7 +2434,7 @@
         <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006800562263873278</v>
+        <v>0.0068005622638734</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
@@ -2471,7 +2471,7 @@
         <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001055860383115947</v>
+        <v>0.00105586038315627</v>
       </c>
       <c r="H8" t="n">
         <v>13</v>
@@ -2508,7 +2508,7 @@
         <v>12</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002484865916395496</v>
+        <v>0.002484865916395607</v>
       </c>
       <c r="H9" t="n">
         <v>9</v>
@@ -2545,7 +2545,7 @@
         <v>16</v>
       </c>
       <c r="G10" t="n">
-        <v>0.004291247703178835</v>
+        <v>0.004291247703178925</v>
       </c>
       <c r="H10" t="n">
         <v>7</v>
@@ -2582,7 +2582,7 @@
         <v>11</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001160984115541541</v>
+        <v>0.001160984115541685</v>
       </c>
       <c r="H11" t="n">
         <v>12</v>
@@ -2619,7 +2619,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="n">
-        <v>0.002581567689486519</v>
+        <v>0.002581567689486597</v>
       </c>
       <c r="H12" t="n">
         <v>8</v>
@@ -2656,7 +2656,7 @@
         <v>17</v>
       </c>
       <c r="G13" t="n">
-        <v>0.00211519601732254</v>
+        <v>0.002115196017322651</v>
       </c>
       <c r="H13" t="n">
         <v>10</v>
@@ -2693,7 +2693,7 @@
         <v>20</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0008640450036720204</v>
+        <v>0.0008640450036721092</v>
       </c>
       <c r="H14" t="n">
         <v>17</v>
@@ -2730,7 +2730,7 @@
         <v>13</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0006637387286543949</v>
+        <v>0.000663738728654506</v>
       </c>
       <c r="H15" t="n">
         <v>21</v>
@@ -2767,7 +2767,7 @@
         <v>14</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0005163308746648943</v>
+        <v>0.0005163308746650164</v>
       </c>
       <c r="H16" t="n">
         <v>24</v>
@@ -2804,7 +2804,7 @@
         <v>22</v>
       </c>
       <c r="G17" t="n">
-        <v>0.001418341798518752</v>
+        <v>0.001418341798518874</v>
       </c>
       <c r="H17" t="n">
         <v>11</v>
@@ -2841,7 +2841,7 @@
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0008693145273346636</v>
+        <v>0.0008693145273347636</v>
       </c>
       <c r="H18" t="n">
         <v>16</v>
@@ -2878,7 +2878,7 @@
         <v>7</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0004423379304002273</v>
+        <v>0.0004423379304003272</v>
       </c>
       <c r="H19" t="n">
         <v>26</v>
@@ -2915,7 +2915,7 @@
         <v>21</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0009432406102126811</v>
+        <v>0.0009432406102128143</v>
       </c>
       <c r="H20" t="n">
         <v>14</v>
@@ -2952,7 +2952,7 @@
         <v>35</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0005951078142952149</v>
+        <v>0.0005951078142953259</v>
       </c>
       <c r="H21" t="n">
         <v>23</v>
@@ -4245,10 +4245,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7224825652776311</v>
+        <v>0.7224825652776312</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05169458322158631</v>
+        <v>0.05169458322158629</v>
       </c>
     </row>
     <row r="3">
@@ -4261,10 +4261,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.05593059693425773</v>
+        <v>0.05593059693425782</v>
       </c>
       <c r="D3" t="n">
-        <v>0.009448084691881771</v>
+        <v>0.009448084691881789</v>
       </c>
     </row>
     <row r="4">
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.04754782163519602</v>
+        <v>0.04754782163519613</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008710069389801981</v>
+        <v>0.00871006938980198</v>
       </c>
     </row>
     <row r="5">
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.0449302301048025</v>
+        <v>0.04493023010480263</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004371957860247486</v>
+        <v>0.004371957860247504</v>
       </c>
     </row>
     <row r="6">
@@ -4309,10 +4309,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.04450525608057555</v>
+        <v>0.04450525608057564</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008579900271024019</v>
+        <v>0.008579900271023988</v>
       </c>
     </row>
     <row r="7">
@@ -4325,10 +4325,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.006800562263873278</v>
+        <v>0.0068005622638734</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0007466510768910653</v>
+        <v>0.0007466510768911025</v>
       </c>
     </row>
     <row r="8">
@@ -4341,10 +4341,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.004291247703178835</v>
+        <v>0.004291247703178925</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001586775880442513</v>
+        <v>0.001586775880442552</v>
       </c>
     </row>
     <row r="9">
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.002581567689486519</v>
+        <v>0.002581567689486597</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0007592144915295148</v>
+        <v>0.0007592144915295035</v>
       </c>
     </row>
     <row r="10">
@@ -4373,10 +4373,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.002484865916395496</v>
+        <v>0.002484865916395607</v>
       </c>
       <c r="D10" t="n">
-        <v>0.000772840466570078</v>
+        <v>0.000772840466570083</v>
       </c>
     </row>
     <row r="11">
@@ -4389,10 +4389,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.00211519601732254</v>
+        <v>0.002115196017322651</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0004114065980895599</v>
+        <v>0.0004114065980895556</v>
       </c>
     </row>
     <row r="12">
@@ -4405,10 +4405,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.001418341798518752</v>
+        <v>0.001418341798518874</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0001648160627100563</v>
+        <v>0.0001648160627100433</v>
       </c>
     </row>
     <row r="13">
@@ -4421,10 +4421,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001160984115541541</v>
+        <v>0.001160984115541685</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0003803570420309039</v>
+        <v>0.000380357042030909</v>
       </c>
     </row>
     <row r="14">
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.001055860383115947</v>
+        <v>0.00105586038315627</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0001211352309769301</v>
+        <v>0.000121135230976673</v>
       </c>
     </row>
     <row r="15">
@@ -4453,10 +4453,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0009432406102126811</v>
+        <v>0.0009432406102128143</v>
       </c>
       <c r="D15" t="n">
-        <v>0.000182264218061646</v>
+        <v>0.0001822642180616445</v>
       </c>
     </row>
     <row r="16">
@@ -4469,10 +4469,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0008730662985471982</v>
+        <v>0.0008730662985473204</v>
       </c>
       <c r="D16" t="n">
-        <v>0.000323414568406171</v>
+        <v>0.0003234145684061721</v>
       </c>
     </row>
     <row r="17">
@@ -4485,10 +4485,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0008693145273346636</v>
+        <v>0.0008693145273347636</v>
       </c>
       <c r="D17" t="n">
-        <v>0.000251579207873706</v>
+        <v>0.000251579207873712</v>
       </c>
     </row>
     <row r="18">
@@ -4501,10 +4501,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0008640450036720204</v>
+        <v>0.0008640450036721092</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0004487413178162064</v>
+        <v>0.0004487413178161921</v>
       </c>
     </row>
     <row r="19">
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0007143119240637042</v>
+        <v>0.0007143119240638152</v>
       </c>
       <c r="D19" t="n">
-        <v>9.868470734463553e-05</v>
+        <v>9.868470734460054e-05</v>
       </c>
     </row>
     <row r="20">
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0006929705807025899</v>
+        <v>0.0006929705807026787</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0002580311788129993</v>
+        <v>0.0002580311788129853</v>
       </c>
     </row>
     <row r="21">
@@ -4549,10 +4549,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.000683852675008334</v>
+        <v>0.0006838526750084561</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0002809105535897538</v>
+        <v>0.0002809105535897735</v>
       </c>
     </row>
     <row r="22">
@@ -4565,7 +4565,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0006637387286543949</v>
+        <v>0.000663738728654506</v>
       </c>
       <c r="D22" t="n">
         <v>0.0003898235263571774</v>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0006375918345603359</v>
+        <v>0.0006375918345604581</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0002433019429910695</v>
+        <v>0.0002433019429910827</v>
       </c>
     </row>
     <row r="24">
@@ -4597,10 +4597,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0005951078142952149</v>
+        <v>0.0005951078142953259</v>
       </c>
       <c r="D24" t="n">
-        <v>0.000203798361041216</v>
+        <v>0.0002037983610412282</v>
       </c>
     </row>
     <row r="25">
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0005163308746648943</v>
+        <v>0.0005163308746650164</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0002023738909991849</v>
+        <v>0.0002023738909991671</v>
       </c>
     </row>
     <row r="26">
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0004624193719336978</v>
+        <v>0.0004624193719338088</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0001698541631947191</v>
+        <v>0.0001698541631947367</v>
       </c>
     </row>
     <row r="27">
@@ -4645,10 +4645,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0004423379304002273</v>
+        <v>0.0004423379304003272</v>
       </c>
       <c r="D27" t="n">
-        <v>0.000168601554522366</v>
+        <v>0.0001686015545223867</v>
       </c>
     </row>
     <row r="28">
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0004413010327554257</v>
+        <v>0.0004413010327555478</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0001685491573300985</v>
+        <v>0.0001685491573301114</v>
       </c>
     </row>
     <row r="29">
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0003927869951789287</v>
+        <v>0.0003927869951790508</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0001482324471567214</v>
+        <v>0.0001482324471567217</v>
       </c>
     </row>
     <row r="30">
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0003477123464230125</v>
+        <v>0.0003477123464231457</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0002522256377508906</v>
+        <v>0.0002522256377508623</v>
       </c>
     </row>
     <row r="31">
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0002985524944571827</v>
+        <v>0.0002985524944572826</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0001601589888790763</v>
+        <v>0.0001601589888790968</v>
       </c>
     </row>
     <row r="32">
@@ -4725,10 +4725,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0002163397078089102</v>
+        <v>0.0002163397078090323</v>
       </c>
       <c r="D32" t="n">
-        <v>9.850298539975111e-05</v>
+        <v>9.850298539976528e-05</v>
       </c>
     </row>
     <row r="33">
@@ -4741,10 +4741,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0001243027744033398</v>
+        <v>0.0001243027744034397</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0001193076706448794</v>
+        <v>0.0001193076706448721</v>
       </c>
     </row>
     <row r="34">
@@ -4757,10 +4757,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.000119101708321856</v>
+        <v>0.0001191017083219448</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0001751925269765365</v>
+        <v>0.0001751925269765577</v>
       </c>
     </row>
     <row r="35">
@@ -4773,10 +4773,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0001042134583107313</v>
+        <v>0.0001042134583108423</v>
       </c>
       <c r="D35" t="n">
-        <v>9.300655999397114e-05</v>
+        <v>9.300655999396176e-05</v>
       </c>
     </row>
     <row r="36">
@@ -4789,10 +4789,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>9.519455031691271e-05</v>
+        <v>9.519455031703483e-05</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0001117770238842945</v>
+        <v>0.0001117770238843095</v>
       </c>
     </row>
     <row r="37">
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>6.860885122702553e-05</v>
+        <v>6.860885122714767e-05</v>
       </c>
       <c r="D37" t="n">
-        <v>9.212435746260697e-05</v>
+        <v>9.212435746256522e-05</v>
       </c>
     </row>
     <row r="38">
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6.726249614475987e-05</v>
+        <v>6.726249614489311e-05</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0001186814983655725</v>
+        <v>0.0001186814983655638</v>
       </c>
     </row>
     <row r="39">
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2.999320981820208e-05</v>
+        <v>2.999320981832421e-05</v>
       </c>
       <c r="D39" t="n">
-        <v>1.123630746954218e-05</v>
+        <v>1.123630746957503e-05</v>
       </c>
     </row>
     <row r="40">
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2.309187965288117e-08</v>
+        <v>2.309187977500571e-08</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0002109403041287341</v>
+        <v>0.0002109403041287458</v>
       </c>
     </row>
     <row r="41">
@@ -4869,10 +4869,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-3.207636878121978e-06</v>
+        <v>-3.207636877999853e-06</v>
       </c>
       <c r="D41" t="n">
-        <v>2.265074732626281e-05</v>
+        <v>2.265074732628137e-05</v>
       </c>
     </row>
     <row r="42">
@@ -4885,10 +4885,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-5.299632575958002e-05</v>
+        <v>-5.299632575949121e-05</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0001598779161756887</v>
+        <v>0.0001598779161756809</v>
       </c>
     </row>
     <row r="43">
@@ -4901,7 +4901,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-9.266529633634723e-05</v>
+        <v>-9.266529633623621e-05</v>
       </c>
       <c r="D43" t="n">
         <v>0.0002780201690876936</v>
@@ -4917,10 +4917,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-0.0001096590214565651</v>
+        <v>-0.0001096590214564541</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0001487004279689495</v>
+        <v>0.0001487004279689806</v>
       </c>
     </row>
     <row r="45">
@@ -4933,10 +4933,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-0.0001493895613445484</v>
+        <v>-0.0001493895613444374</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0002621423006976512</v>
+        <v>0.0002621423006976988</v>
       </c>
     </row>
     <row r="46">
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-0.0001788763210360589</v>
+        <v>-0.0001788763210359701</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0003321550021656572</v>
+        <v>0.0003321550021656728</v>
       </c>
     </row>
   </sheetData>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-16 14:05:12 UTC</t>
+          <t>2026-06-16 15:17:02 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_solution_color.xlsx
+++ b/NN/reports/feature_importance_white_solution_color.xlsx
@@ -513,7 +513,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3598793571410549</v>
+        <v>0.3598793571410548</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -550,7 +550,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2813470101326704</v>
+        <v>0.2813470101326703</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -587,7 +587,7 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03188475108235696</v>
+        <v>0.03188475108235687</v>
       </c>
       <c r="H4" t="n">
         <v>4</v>
@@ -624,7 +624,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0416466695227404</v>
+        <v>0.0416466695227403</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
@@ -661,7 +661,7 @@
         <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02157996931448751</v>
+        <v>0.0215799693144874</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -698,7 +698,7 @@
         <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01200704749597893</v>
+        <v>0.01200704749597881</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
@@ -735,7 +735,7 @@
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004525107807768736</v>
+        <v>0.004525107807768625</v>
       </c>
       <c r="H8" t="n">
         <v>8</v>
@@ -772,7 +772,7 @@
         <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.005298272783865276</v>
+        <v>0.005298272783865155</v>
       </c>
       <c r="H9" t="n">
         <v>7</v>
@@ -809,7 +809,7 @@
         <v>5</v>
       </c>
       <c r="G10" t="n">
-        <v>0.000372539178951691</v>
+        <v>0.0003725391789115345</v>
       </c>
       <c r="H10" t="n">
         <v>23</v>
@@ -846,7 +846,7 @@
         <v>11</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001006899723146704</v>
+        <v>0.001006899723146593</v>
       </c>
       <c r="H11" t="n">
         <v>13</v>
@@ -883,7 +883,7 @@
         <v>19</v>
       </c>
       <c r="G12" t="n">
-        <v>0.001066831892333842</v>
+        <v>0.001066831892333708</v>
       </c>
       <c r="H12" t="n">
         <v>12</v>
@@ -920,7 +920,7 @@
         <v>17</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0005687225825382169</v>
+        <v>0.0005687225825381281</v>
       </c>
       <c r="H13" t="n">
         <v>15</v>
@@ -957,7 +957,7 @@
         <v>16</v>
       </c>
       <c r="G14" t="n">
-        <v>0.000207213615126034</v>
+        <v>0.0002072136151259229</v>
       </c>
       <c r="H14" t="n">
         <v>31</v>
@@ -994,7 +994,7 @@
         <v>21</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001319066452785034</v>
+        <v>0.001319066452784956</v>
       </c>
       <c r="H15" t="n">
         <v>10</v>
@@ -1031,7 +1031,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="n">
-        <v>0.001145782448783261</v>
+        <v>0.001145782448783161</v>
       </c>
       <c r="H16" t="n">
         <v>11</v>
@@ -1068,7 +1068,7 @@
         <v>20</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0003341763919278318</v>
+        <v>0.0003341763919277207</v>
       </c>
       <c r="H17" t="n">
         <v>24</v>
@@ -1105,7 +1105,7 @@
         <v>12</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0002236489103919825</v>
+        <v>0.0002236489103918604</v>
       </c>
       <c r="H18" t="n">
         <v>27</v>
@@ -1142,7 +1142,7 @@
         <v>28</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0005098336434349981</v>
+        <v>0.0005098336434348871</v>
       </c>
       <c r="H19" t="n">
         <v>18</v>
@@ -1179,7 +1179,7 @@
         <v>25</v>
       </c>
       <c r="G20" t="n">
-        <v>0.001391474375185364</v>
+        <v>0.001391474375185242</v>
       </c>
       <c r="H20" t="n">
         <v>9</v>
@@ -1216,7 +1216,7 @@
         <v>24</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0003862927800955651</v>
+        <v>0.000386292780095443</v>
       </c>
       <c r="H21" t="n">
         <v>21</v>
@@ -1253,7 +1253,7 @@
         <v>9</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0002159719791945736</v>
+        <v>0.0002159719791944625</v>
       </c>
       <c r="H22" t="n">
         <v>28</v>
@@ -1290,7 +1290,7 @@
         <v>27</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0005605871611487178</v>
+        <v>0.0005605871611486068</v>
       </c>
       <c r="H23" t="n">
         <v>16</v>
@@ -1327,7 +1327,7 @@
         <v>14</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0002414067048767232</v>
+        <v>0.0002414067048766011</v>
       </c>
       <c r="H24" t="n">
         <v>26</v>
@@ -1364,7 +1364,7 @@
         <v>31</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0002136535776239623</v>
+        <v>0.0002136535776238291</v>
       </c>
       <c r="H25" t="n">
         <v>29</v>
@@ -1401,7 +1401,7 @@
         <v>37</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0002883913801753901</v>
+        <v>0.000288391380175268</v>
       </c>
       <c r="H26" t="n">
         <v>25</v>
@@ -1438,7 +1438,7 @@
         <v>22</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0002084405193223504</v>
+        <v>0.0002084405193222505</v>
       </c>
       <c r="H27" t="n">
         <v>30</v>
@@ -1475,7 +1475,7 @@
         <v>18</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0001532722460016789</v>
+        <v>0.0001532722460016012</v>
       </c>
       <c r="H28" t="n">
         <v>33</v>
@@ -1512,7 +1512,7 @@
         <v>26</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.0001482043522033183</v>
+        <v>-0.0001482043522034071</v>
       </c>
       <c r="H29" t="n">
         <v>51</v>
@@ -1549,7 +1549,7 @@
         <v>13</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0001380282076580475</v>
+        <v>0.0001380282076579253</v>
       </c>
       <c r="H30" t="n">
         <v>35</v>
@@ -1586,7 +1586,7 @@
         <v>29</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0003850525447718689</v>
+        <v>0.0003850525447717468</v>
       </c>
       <c r="H31" t="n">
         <v>22</v>
@@ -1623,7 +1623,7 @@
         <v>45</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0005800150786270831</v>
+        <v>0.0005800150786269609</v>
       </c>
       <c r="H32" t="n">
         <v>14</v>
@@ -1660,7 +1660,7 @@
         <v>23</v>
       </c>
       <c r="G33" t="n">
-        <v>-4.068710041975621e-05</v>
+        <v>-4.068710041987833e-05</v>
       </c>
       <c r="H33" t="n">
         <v>47</v>
@@ -1697,7 +1697,7 @@
         <v>39</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0005449226424683595</v>
+        <v>0.0005449226424682485</v>
       </c>
       <c r="H34" t="n">
         <v>17</v>
@@ -1734,7 +1734,7 @@
         <v>34</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0004150406246041682</v>
+        <v>0.0004150406246040683</v>
       </c>
       <c r="H35" t="n">
         <v>19</v>
@@ -1771,7 +1771,7 @@
         <v>32</v>
       </c>
       <c r="G36" t="n">
-        <v>0.000173194622588313</v>
+        <v>0.0001731946225882352</v>
       </c>
       <c r="H36" t="n">
         <v>32</v>
@@ -1808,7 +1808,7 @@
         <v>33</v>
       </c>
       <c r="G37" t="n">
-        <v>3.591056691276684e-05</v>
+        <v>3.591056691266692e-05</v>
       </c>
       <c r="H37" t="n">
         <v>40</v>
@@ -1845,7 +1845,7 @@
         <v>30</v>
       </c>
       <c r="G38" t="n">
-        <v>5.232347753792998e-05</v>
+        <v>5.232347753780786e-05</v>
       </c>
       <c r="H38" t="n">
         <v>39</v>
@@ -1882,7 +1882,7 @@
         <v>49</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0001203639689924652</v>
+        <v>0.0001203639689923541</v>
       </c>
       <c r="H39" t="n">
         <v>36</v>
@@ -1919,7 +1919,7 @@
         <v>42</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0001509396737493618</v>
+        <v>0.0001509396737492619</v>
       </c>
       <c r="H40" t="n">
         <v>34</v>
@@ -1956,7 +1956,7 @@
         <v>35</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0003921249062824983</v>
+        <v>0.0003921249062823762</v>
       </c>
       <c r="H41" t="n">
         <v>20</v>
@@ -1993,7 +1993,7 @@
         <v>38</v>
       </c>
       <c r="G42" t="n">
-        <v>-3.912405583600398e-05</v>
+        <v>-3.912405583613721e-05</v>
       </c>
       <c r="H42" t="n">
         <v>46</v>
@@ -2030,7 +2030,7 @@
         <v>41</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0001046023916772998</v>
+        <v>0.0001046023916771777</v>
       </c>
       <c r="H43" t="n">
         <v>37</v>
@@ -2067,7 +2067,7 @@
         <v>36</v>
       </c>
       <c r="G44" t="n">
-        <v>-5.288512301215853e-06</v>
+        <v>-5.288512301315773e-06</v>
       </c>
       <c r="H44" t="n">
         <v>42</v>
@@ -2104,7 +2104,7 @@
         <v>40</v>
       </c>
       <c r="G45" t="n">
-        <v>-9.690869983747241e-05</v>
+        <v>-9.690869983758343e-05</v>
       </c>
       <c r="H45" t="n">
         <v>50</v>
@@ -2141,7 +2141,7 @@
         <v>47</v>
       </c>
       <c r="G46" t="n">
-        <v>-3.656031711283258e-05</v>
+        <v>-3.656031711293251e-05</v>
       </c>
       <c r="H46" t="n">
         <v>45</v>
@@ -2178,7 +2178,7 @@
         <v>50</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.0001800433885696839</v>
+        <v>-0.0001800433885697949</v>
       </c>
       <c r="H47" t="n">
         <v>52</v>
@@ -2215,7 +2215,7 @@
         <v>46</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.0003104006152105487</v>
+        <v>-0.0003104006152106598</v>
       </c>
       <c r="H48" t="n">
         <v>53</v>
@@ -2252,7 +2252,7 @@
         <v>48</v>
       </c>
       <c r="G49" t="n">
-        <v>-5.153761794967071e-05</v>
+        <v>-5.153761794977063e-05</v>
       </c>
       <c r="H49" t="n">
         <v>49</v>
@@ -2289,7 +2289,7 @@
         <v>44</v>
       </c>
       <c r="G50" t="n">
-        <v>-1.62630332425584e-05</v>
+        <v>-1.626303324264722e-05</v>
       </c>
       <c r="H50" t="n">
         <v>43</v>
@@ -2326,7 +2326,7 @@
         <v>52</v>
       </c>
       <c r="G51" t="n">
-        <v>6.202459662529858e-05</v>
+        <v>6.202459662518756e-05</v>
       </c>
       <c r="H51" t="n">
         <v>38</v>
@@ -2363,7 +2363,7 @@
         <v>43</v>
       </c>
       <c r="G52" t="n">
-        <v>-4.815492907939145e-05</v>
+        <v>-4.815492907951357e-05</v>
       </c>
       <c r="H52" t="n">
         <v>48</v>
@@ -2400,7 +2400,7 @@
         <v>51</v>
       </c>
       <c r="G53" t="n">
-        <v>1.240458790952026e-05</v>
+        <v>1.240458790939813e-05</v>
       </c>
       <c r="H53" t="n">
         <v>41</v>
@@ -2437,7 +2437,7 @@
         <v>53</v>
       </c>
       <c r="G54" t="n">
-        <v>-2.786894234019233e-05</v>
+        <v>-2.786894234030335e-05</v>
       </c>
       <c r="H54" t="n">
         <v>44</v>
@@ -2545,7 +2545,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3598793571410549</v>
+        <v>0.3598793571410548</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -2582,7 +2582,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2813470101326704</v>
+        <v>0.2813470101326703</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -2619,7 +2619,7 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03188475108235696</v>
+        <v>0.03188475108235687</v>
       </c>
       <c r="H4" t="n">
         <v>4</v>
@@ -2656,7 +2656,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0416466695227404</v>
+        <v>0.0416466695227403</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
@@ -2693,7 +2693,7 @@
         <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02157996931448751</v>
+        <v>0.0215799693144874</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -2730,7 +2730,7 @@
         <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01200704749597893</v>
+        <v>0.01200704749597881</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
@@ -2767,7 +2767,7 @@
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004525107807768736</v>
+        <v>0.004525107807768625</v>
       </c>
       <c r="H8" t="n">
         <v>8</v>
@@ -2804,7 +2804,7 @@
         <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.005298272783865276</v>
+        <v>0.005298272783865155</v>
       </c>
       <c r="H9" t="n">
         <v>7</v>
@@ -2841,7 +2841,7 @@
         <v>5</v>
       </c>
       <c r="G10" t="n">
-        <v>0.000372539178951691</v>
+        <v>0.0003725391789115345</v>
       </c>
       <c r="H10" t="n">
         <v>23</v>
@@ -2878,7 +2878,7 @@
         <v>11</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001006899723146704</v>
+        <v>0.001006899723146593</v>
       </c>
       <c r="H11" t="n">
         <v>13</v>
@@ -2915,7 +2915,7 @@
         <v>19</v>
       </c>
       <c r="G12" t="n">
-        <v>0.001066831892333842</v>
+        <v>0.001066831892333708</v>
       </c>
       <c r="H12" t="n">
         <v>12</v>
@@ -2952,7 +2952,7 @@
         <v>17</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0005687225825382169</v>
+        <v>0.0005687225825381281</v>
       </c>
       <c r="H13" t="n">
         <v>15</v>
@@ -2989,7 +2989,7 @@
         <v>16</v>
       </c>
       <c r="G14" t="n">
-        <v>0.000207213615126034</v>
+        <v>0.0002072136151259229</v>
       </c>
       <c r="H14" t="n">
         <v>31</v>
@@ -3026,7 +3026,7 @@
         <v>21</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001319066452785034</v>
+        <v>0.001319066452784956</v>
       </c>
       <c r="H15" t="n">
         <v>10</v>
@@ -3063,7 +3063,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="n">
-        <v>0.001145782448783261</v>
+        <v>0.001145782448783161</v>
       </c>
       <c r="H16" t="n">
         <v>11</v>
@@ -3100,7 +3100,7 @@
         <v>20</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0003341763919278318</v>
+        <v>0.0003341763919277207</v>
       </c>
       <c r="H17" t="n">
         <v>24</v>
@@ -3137,7 +3137,7 @@
         <v>12</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0002236489103919825</v>
+        <v>0.0002236489103918604</v>
       </c>
       <c r="H18" t="n">
         <v>27</v>
@@ -3174,7 +3174,7 @@
         <v>28</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0005098336434349981</v>
+        <v>0.0005098336434348871</v>
       </c>
       <c r="H19" t="n">
         <v>18</v>
@@ -3211,7 +3211,7 @@
         <v>25</v>
       </c>
       <c r="G20" t="n">
-        <v>0.001391474375185364</v>
+        <v>0.001391474375185242</v>
       </c>
       <c r="H20" t="n">
         <v>9</v>
@@ -3248,7 +3248,7 @@
         <v>24</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0003862927800955651</v>
+        <v>0.000386292780095443</v>
       </c>
       <c r="H21" t="n">
         <v>21</v>
@@ -4749,10 +4749,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3598793571410549</v>
+        <v>0.3598793571410548</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03041445669921597</v>
+        <v>0.03041445669921598</v>
       </c>
     </row>
     <row r="3">
@@ -4765,10 +4765,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2813470101326704</v>
+        <v>0.2813470101326703</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01524823488966109</v>
+        <v>0.01524823488966112</v>
       </c>
     </row>
     <row r="4">
@@ -4781,10 +4781,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0416466695227404</v>
+        <v>0.0416466695227403</v>
       </c>
       <c r="D4" t="n">
-        <v>0.007157943070708389</v>
+        <v>0.007157943070708394</v>
       </c>
     </row>
     <row r="5">
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03188475108235696</v>
+        <v>0.03188475108235687</v>
       </c>
       <c r="D5" t="n">
-        <v>0.007600139502350577</v>
+        <v>0.007600139502350601</v>
       </c>
     </row>
     <row r="6">
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.02157996931448751</v>
+        <v>0.0215799693144874</v>
       </c>
       <c r="D6" t="n">
-        <v>0.005562400201518326</v>
+        <v>0.005562400201518337</v>
       </c>
     </row>
     <row r="7">
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01200704749597893</v>
+        <v>0.01200704749597881</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001327194475607478</v>
+        <v>0.001327194475607491</v>
       </c>
     </row>
     <row r="8">
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.005298272783865276</v>
+        <v>0.005298272783865155</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0004053558587745954</v>
+        <v>0.0004053558587746051</v>
       </c>
     </row>
     <row r="9">
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.004525107807768736</v>
+        <v>0.004525107807768625</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0004560717475661853</v>
+        <v>0.0004560717475662096</v>
       </c>
     </row>
     <row r="10">
@@ -4877,10 +4877,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.001391474375185364</v>
+        <v>0.001391474375185242</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0001591010685670372</v>
+        <v>0.000159101068567029</v>
       </c>
     </row>
     <row r="11">
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.001319066452785034</v>
+        <v>0.001319066452784956</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0005414674602246542</v>
+        <v>0.0005414674602246441</v>
       </c>
     </row>
     <row r="12">
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.001145782448783261</v>
+        <v>0.001145782448783161</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0002168212391677222</v>
+        <v>0.0002168212391676927</v>
       </c>
     </row>
     <row r="13">
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001066831892333842</v>
+        <v>0.001066831892333708</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0005048358098471679</v>
+        <v>0.0005048358098471627</v>
       </c>
     </row>
     <row r="14">
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.001006899723146704</v>
+        <v>0.001006899723146593</v>
       </c>
       <c r="D14" t="n">
-        <v>0.000355095111806079</v>
+        <v>0.0003550951118060868</v>
       </c>
     </row>
     <row r="15">
@@ -4957,10 +4957,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0005800150786270831</v>
+        <v>0.0005800150786269609</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0001644582744382722</v>
+        <v>0.0001644582744382599</v>
       </c>
     </row>
     <row r="16">
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0005687225825382169</v>
+        <v>0.0005687225825381281</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0001283287493608244</v>
+        <v>0.0001283287493608571</v>
       </c>
     </row>
     <row r="17">
@@ -4989,7 +4989,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0005605871611487178</v>
+        <v>0.0005605871611486068</v>
       </c>
       <c r="D17" t="n">
         <v>0.0001436236424471595</v>
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0005449226424683595</v>
+        <v>0.0005449226424682485</v>
       </c>
       <c r="D18" t="n">
         <v>0.0001626794654960903</v>
@@ -5021,10 +5021,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0005098336434349981</v>
+        <v>0.0005098336434348871</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0001447292561736676</v>
+        <v>0.0001447292561736646</v>
       </c>
     </row>
     <row r="20">
@@ -5037,10 +5037,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0004150406246041682</v>
+        <v>0.0004150406246040683</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0001287384004968305</v>
+        <v>0.0001287384004968198</v>
       </c>
     </row>
     <row r="21">
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0003921249062824983</v>
+        <v>0.0003921249062823762</v>
       </c>
       <c r="D21" t="n">
-        <v>4.256663542581737e-05</v>
+        <v>4.256663542582981e-05</v>
       </c>
     </row>
     <row r="22">
@@ -5069,10 +5069,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0003862927800955651</v>
+        <v>0.000386292780095443</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0003116897519392526</v>
+        <v>0.0003116897519392234</v>
       </c>
     </row>
     <row r="23">
@@ -5085,10 +5085,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0003850525447718689</v>
+        <v>0.0003850525447717468</v>
       </c>
       <c r="D23" t="n">
-        <v>7.169897241367991e-05</v>
+        <v>7.169897241366756e-05</v>
       </c>
     </row>
     <row r="24">
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.000372539178951691</v>
+        <v>0.0003725391789115345</v>
       </c>
       <c r="D24" t="n">
-        <v>4.731016319563441e-05</v>
+        <v>4.731016319536368e-05</v>
       </c>
     </row>
     <row r="25">
@@ -5117,7 +5117,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0003341763919278318</v>
+        <v>0.0003341763919277207</v>
       </c>
       <c r="D25" t="n">
         <v>0.0001281307850932167</v>
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0002883913801753901</v>
+        <v>0.000288391380175268</v>
       </c>
       <c r="D26" t="n">
-        <v>6.261256938241649e-05</v>
+        <v>6.261256938243453e-05</v>
       </c>
     </row>
     <row r="27">
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0002414067048767232</v>
+        <v>0.0002414067048766011</v>
       </c>
       <c r="D27" t="n">
-        <v>6.713344377306386e-05</v>
+        <v>6.713344377305392e-05</v>
       </c>
     </row>
     <row r="28">
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0002236489103919825</v>
+        <v>0.0002236489103918604</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0001163251040838036</v>
+        <v>0.0001163251040837851</v>
       </c>
     </row>
     <row r="29">
@@ -5181,7 +5181,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0002159719791945736</v>
+        <v>0.0002159719791944625</v>
       </c>
       <c r="D29" t="n">
         <v>6.71142060242558e-05</v>
@@ -5197,10 +5197,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0002136535776239623</v>
+        <v>0.0002136535776238291</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0001950049485494441</v>
+        <v>0.0001950049485494488</v>
       </c>
     </row>
     <row r="31">
@@ -5213,10 +5213,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0002084405193223504</v>
+        <v>0.0002084405193222505</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0001183540964854371</v>
+        <v>0.0001183540964854376</v>
       </c>
     </row>
     <row r="32">
@@ -5229,7 +5229,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.000207213615126034</v>
+        <v>0.0002072136151259229</v>
       </c>
       <c r="D32" t="n">
         <v>0.0007383849116093184</v>
@@ -5245,10 +5245,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.000173194622588313</v>
+        <v>0.0001731946225882352</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0001044216602020246</v>
+        <v>0.0001044216602020067</v>
       </c>
     </row>
     <row r="34">
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0001532722460016789</v>
+        <v>0.0001532722460016012</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0001221877296913883</v>
+        <v>0.0001221877296913745</v>
       </c>
     </row>
     <row r="35">
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0001509396737493618</v>
+        <v>0.0001509396737492619</v>
       </c>
       <c r="D35" t="n">
-        <v>7.09691553413078e-05</v>
+        <v>7.09691553413161e-05</v>
       </c>
     </row>
     <row r="36">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0001380282076580475</v>
+        <v>0.0001380282076579253</v>
       </c>
       <c r="D36" t="n">
-        <v>7.290849629907503e-05</v>
+        <v>7.2908496299079e-05</v>
       </c>
     </row>
     <row r="37">
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.0001203639689924652</v>
+        <v>0.0001203639689923541</v>
       </c>
       <c r="D37" t="n">
         <v>8.059860407535291e-05</v>
@@ -5325,10 +5325,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.0001046023916772998</v>
+        <v>0.0001046023916771777</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0001087672521161095</v>
+        <v>0.0001087672521161128</v>
       </c>
     </row>
     <row r="39">
@@ -5341,7 +5341,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>6.202459662529858e-05</v>
+        <v>6.202459662518756e-05</v>
       </c>
       <c r="D39" t="n">
         <v>2.874274511499105e-05</v>
@@ -5357,10 +5357,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5.232347753792998e-05</v>
+        <v>5.232347753780786e-05</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0001120303628327273</v>
+        <v>0.0001120303628327267</v>
       </c>
     </row>
     <row r="41">
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3.591056691276684e-05</v>
+        <v>3.591056691266692e-05</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0001434684123433035</v>
+        <v>0.0001434684123432954</v>
       </c>
     </row>
     <row r="42">
@@ -5389,10 +5389,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1.240458790952026e-05</v>
+        <v>1.240458790939813e-05</v>
       </c>
       <c r="D42" t="n">
-        <v>4.605546486457779e-06</v>
+        <v>4.60554648646588e-06</v>
       </c>
     </row>
     <row r="43">
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-5.288512301215853e-06</v>
+        <v>-5.288512301315773e-06</v>
       </c>
       <c r="D43" t="n">
-        <v>8.119598861249887e-05</v>
+        <v>8.119598861247759e-05</v>
       </c>
     </row>
     <row r="44">
@@ -5421,10 +5421,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-1.62630332425584e-05</v>
+        <v>-1.626303324264722e-05</v>
       </c>
       <c r="D44" t="n">
-        <v>3.726211982360197e-05</v>
+        <v>3.726211982360938e-05</v>
       </c>
     </row>
     <row r="45">
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-2.786894234019233e-05</v>
+        <v>-2.786894234030335e-05</v>
       </c>
       <c r="D45" t="n">
-        <v>1.777214842172435e-05</v>
+        <v>1.77721484217315e-05</v>
       </c>
     </row>
     <row r="46">
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-3.656031711283258e-05</v>
+        <v>-3.656031711293251e-05</v>
       </c>
       <c r="D46" t="n">
-        <v>4.499235083519608e-05</v>
+        <v>4.4992350835189e-05</v>
       </c>
     </row>
     <row r="47">
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-3.912405583600398e-05</v>
+        <v>-3.912405583613721e-05</v>
       </c>
       <c r="D47" t="n">
-        <v>6.675099540998198e-05</v>
+        <v>6.67509954099831e-05</v>
       </c>
     </row>
     <row r="48">
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-4.068710041975621e-05</v>
+        <v>-4.068710041987833e-05</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0001025101141063102</v>
+        <v>0.0001025101141063166</v>
       </c>
     </row>
     <row r="49">
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-4.815492907939145e-05</v>
+        <v>-4.815492907951357e-05</v>
       </c>
       <c r="D49" t="n">
-        <v>2.803255978632049e-05</v>
+        <v>2.803255978632897e-05</v>
       </c>
     </row>
     <row r="50">
@@ -5517,10 +5517,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-5.153761794967071e-05</v>
+        <v>-5.153761794977063e-05</v>
       </c>
       <c r="D50" t="n">
-        <v>8.442209553245845e-05</v>
+        <v>8.442209553246448e-05</v>
       </c>
     </row>
     <row r="51">
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-9.690869983747241e-05</v>
+        <v>-9.690869983758343e-05</v>
       </c>
       <c r="D51" t="n">
         <v>5.406300750381862e-05</v>
@@ -5549,10 +5549,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-0.0001482043522033183</v>
+        <v>-0.0001482043522034071</v>
       </c>
       <c r="D52" t="n">
-        <v>9.671752472189063e-05</v>
+        <v>9.671752472187653e-05</v>
       </c>
     </row>
     <row r="53">
@@ -5565,7 +5565,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-0.0001800433885696839</v>
+        <v>-0.0001800433885697949</v>
       </c>
       <c r="D53" t="n">
         <v>9.325461665867935e-05</v>
@@ -5581,7 +5581,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-0.0003104006152105487</v>
+        <v>-0.0003104006152106598</v>
       </c>
       <c r="D54" t="n">
         <v>9.910782854720545e-05</v>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-14 21:56:19 UTC</t>
+          <t>2026-06-16 19:24:08 UTC</t>
         </is>
       </c>
     </row>
